--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918642</v>
+        <v>126918430</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656705</v>
+        <v>656876</v>
       </c>
       <c r="R2" t="n">
-        <v>7122438</v>
+        <v>7122472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +748,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126915089</v>
+        <v>126920134</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656872</v>
+        <v>656826</v>
       </c>
       <c r="R3" t="n">
-        <v>7122285</v>
+        <v>7122263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -882,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126916294</v>
+        <v>126920138</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656807</v>
+        <v>656779</v>
       </c>
       <c r="R4" t="n">
-        <v>7122365</v>
+        <v>7122366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -983,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126916734</v>
+        <v>126917810</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656577</v>
+        <v>656710</v>
       </c>
       <c r="R5" t="n">
-        <v>7122682</v>
+        <v>7122344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1084,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918676</v>
+        <v>126919823</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656580</v>
+        <v>656549</v>
       </c>
       <c r="R6" t="n">
-        <v>7122580</v>
+        <v>7122696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126918430</v>
+        <v>126920132</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656876</v>
+        <v>656728</v>
       </c>
       <c r="R7" t="n">
-        <v>7122472</v>
+        <v>7122652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,12 +1265,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1286,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126920138</v>
+        <v>126918642</v>
       </c>
       <c r="B8" t="n">
-        <v>78681</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656779</v>
+        <v>656705</v>
       </c>
       <c r="R8" t="n">
-        <v>7122366</v>
+        <v>7122438</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,6 +1354,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1371,12 +1371,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1387,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126917810</v>
+        <v>126915089</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,34 +1398,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656710</v>
+        <v>656872</v>
       </c>
       <c r="R9" t="n">
-        <v>7122344</v>
+        <v>7122285</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,12 +1472,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1488,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126920134</v>
+        <v>126916294</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656826</v>
+        <v>656807</v>
       </c>
       <c r="R10" t="n">
-        <v>7122263</v>
+        <v>7122365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,12 +1573,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919823</v>
+        <v>126916734</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656549</v>
+        <v>656577</v>
       </c>
       <c r="R11" t="n">
-        <v>7122696</v>
+        <v>7122682</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126920132</v>
+        <v>126918676</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656728</v>
+        <v>656580</v>
       </c>
       <c r="R12" t="n">
-        <v>7122652</v>
+        <v>7122580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,12 +1775,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -3167,32 +3167,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126918701</v>
+        <v>126918659</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>656649</v>
+        <v>656834</v>
       </c>
       <c r="R26" t="n">
-        <v>7122554</v>
+        <v>7122225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,6 +3238,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3268,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918662</v>
+        <v>126918020</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>92808</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3279,34 +3284,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656760</v>
+        <v>656722</v>
       </c>
       <c r="R27" t="n">
-        <v>7122309</v>
+        <v>7122528</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3350,15 +3355,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3369,32 +3389,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126920129</v>
+        <v>126918701</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3424,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656727</v>
+        <v>656649</v>
       </c>
       <c r="R28" t="n">
-        <v>7122637</v>
+        <v>7122554</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,12 +3474,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3470,10 +3490,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918020</v>
+        <v>126918662</v>
       </c>
       <c r="B29" t="n">
-        <v>92808</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,34 +3501,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656722</v>
+        <v>656760</v>
       </c>
       <c r="R29" t="n">
-        <v>7122528</v>
+        <v>7122309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3552,30 +3572,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3586,45 +3591,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918659</v>
+        <v>126918695</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656834</v>
+        <v>656654</v>
       </c>
       <c r="R30" t="n">
-        <v>7122225</v>
+        <v>7122550</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3659,17 +3676,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3692,57 +3705,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918695</v>
+        <v>126920129</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656654</v>
+        <v>656727</v>
       </c>
       <c r="R31" t="n">
-        <v>7122550</v>
+        <v>7122637</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3783,19 +3784,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4528,10 +4528,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126916279</v>
+        <v>126916388</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>92808</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,45 +4539,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>656878</v>
+        <v>656716</v>
       </c>
       <c r="R39" t="n">
-        <v>7122337</v>
+        <v>7122710</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4607,11 +4599,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4626,12 +4613,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4642,10 +4629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126916388</v>
+        <v>126915092</v>
       </c>
       <c r="B40" t="n">
-        <v>92808</v>
+        <v>80117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4653,37 +4640,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>656716</v>
+        <v>656867</v>
       </c>
       <c r="R40" t="n">
-        <v>7122710</v>
+        <v>7122430</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4727,12 +4714,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4743,7 +4730,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126915092</v>
+        <v>126915679</v>
       </c>
       <c r="B41" t="n">
         <v>80117</v>
@@ -4774,14 +4761,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656867</v>
+        <v>656688</v>
       </c>
       <c r="R41" t="n">
-        <v>7122430</v>
+        <v>7122595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4828,12 +4815,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4844,7 +4831,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126915679</v>
+        <v>126905646</v>
       </c>
       <c r="B42" t="n">
         <v>80117</v>
@@ -4875,14 +4862,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656688</v>
+        <v>656789</v>
       </c>
       <c r="R42" t="n">
-        <v>7122595</v>
+        <v>7122441</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4929,12 +4916,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4945,10 +4932,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126905646</v>
+        <v>126918031</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4956,34 +4943,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656789</v>
+        <v>656542</v>
       </c>
       <c r="R43" t="n">
-        <v>7122441</v>
+        <v>7122741</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5027,15 +5014,30 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5046,10 +5048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126918031</v>
+        <v>126917816</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5057,34 +5059,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656542</v>
+        <v>656764</v>
       </c>
       <c r="R44" t="n">
-        <v>7122741</v>
+        <v>7122303</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5128,30 +5130,15 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,7 +5149,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126917816</v>
+        <v>126920133</v>
       </c>
       <c r="B45" t="n">
         <v>78772</v>
@@ -5197,10 +5184,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656764</v>
+        <v>656724</v>
       </c>
       <c r="R45" t="n">
-        <v>7122303</v>
+        <v>7122581</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5234,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,10 +5250,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126920133</v>
+        <v>126916279</v>
       </c>
       <c r="B46" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,34 +5261,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656724</v>
+        <v>656878</v>
       </c>
       <c r="R46" t="n">
-        <v>7122581</v>
+        <v>7122337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,6 +5331,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -8220,10 +8220,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126916855</v>
+        <v>126916732</v>
       </c>
       <c r="B74" t="n">
-        <v>78681</v>
+        <v>57654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8231,34 +8231,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656803</v>
+        <v>656599</v>
       </c>
       <c r="R74" t="n">
-        <v>7122276</v>
+        <v>7122660</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8288,19 +8292,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:59</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8311,36 +8310,16 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>Gammal tallåga</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallåga</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8351,49 +8330,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126916732</v>
+        <v>126920135</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656599</v>
+        <v>656718</v>
       </c>
       <c r="R75" t="n">
-        <v>7122660</v>
+        <v>7122587</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8428,11 +8403,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8445,12 +8415,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8461,10 +8431,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916735</v>
+        <v>126916855</v>
       </c>
       <c r="B76" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8472,21 +8442,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8496,10 +8466,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656861</v>
+        <v>656803</v>
       </c>
       <c r="R76" t="n">
-        <v>7122418</v>
+        <v>7122276</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,11 +8499,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8542,16 +8522,36 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallåga</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8562,7 +8562,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126916291</v>
+        <v>126916735</v>
       </c>
       <c r="B77" t="n">
         <v>78773</v>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656585</v>
+        <v>656861</v>
       </c>
       <c r="R77" t="n">
-        <v>7122741</v>
+        <v>7122418</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8647,12 +8647,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8663,7 +8663,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915678</v>
+        <v>126916291</v>
       </c>
       <c r="B78" t="n">
         <v>78773</v>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656958</v>
+        <v>656585</v>
       </c>
       <c r="R78" t="n">
-        <v>7122264</v>
+        <v>7122741</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8748,12 +8748,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8764,32 +8764,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126920135</v>
+        <v>126915678</v>
       </c>
       <c r="B79" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656718</v>
+        <v>656958</v>
       </c>
       <c r="R79" t="n">
-        <v>7122587</v>
+        <v>7122264</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8849,12 +8849,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -12951,10 +12951,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126917777</v>
+        <v>126918409</v>
       </c>
       <c r="B119" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12962,21 +12962,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12986,10 +12986,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>656802</v>
+        <v>656757</v>
       </c>
       <c r="R119" t="n">
-        <v>7122279</v>
+        <v>7122638</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13036,12 +13036,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13052,32 +13052,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126919836</v>
+        <v>126920121</v>
       </c>
       <c r="B120" t="n">
-        <v>80152</v>
+        <v>57657</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13087,10 +13087,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>656698</v>
+        <v>656620</v>
       </c>
       <c r="R120" t="n">
-        <v>7122588</v>
+        <v>7122729</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13125,6 +13125,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Äldre hack på tall</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13137,12 +13142,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13153,32 +13158,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126915958</v>
+        <v>126917777</v>
       </c>
       <c r="B121" t="n">
-        <v>80146</v>
+        <v>92808</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13188,13 +13193,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>656674</v>
+        <v>656802</v>
       </c>
       <c r="R121" t="n">
-        <v>7122583</v>
+        <v>7122279</v>
       </c>
       <c r="S121" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13238,12 +13243,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13254,10 +13259,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126919796</v>
+        <v>126919836</v>
       </c>
       <c r="B122" t="n">
-        <v>80146</v>
+        <v>80152</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13265,21 +13270,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13289,10 +13294,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>656716</v>
+        <v>656698</v>
       </c>
       <c r="R122" t="n">
-        <v>7122559</v>
+        <v>7122588</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13355,48 +13360,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126918005</v>
+        <v>126915958</v>
       </c>
       <c r="B123" t="n">
-        <v>79632</v>
+        <v>80146</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>656873</v>
+        <v>656674</v>
       </c>
       <c r="R123" t="n">
-        <v>7122259</v>
+        <v>7122583</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13436,31 +13441,16 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Peter Andersson, Torbjörn Söderquist, Elin Kannerby, Beke Regelin, Elke Blöhbaum, Anders Heggestad, Klas Magnusson, Miriam Schenk, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Lise Mortensen, Rolf Nylinder, Lisa Requin, Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13471,32 +13461,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126918409</v>
+        <v>126919796</v>
       </c>
       <c r="B124" t="n">
-        <v>78681</v>
+        <v>80146</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13506,10 +13496,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>656757</v>
+        <v>656716</v>
       </c>
       <c r="R124" t="n">
-        <v>7122638</v>
+        <v>7122559</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13556,12 +13546,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13572,10 +13562,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126920121</v>
+        <v>126918005</v>
       </c>
       <c r="B125" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13583,34 +13573,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>656620</v>
+        <v>656873</v>
       </c>
       <c r="R125" t="n">
-        <v>7122729</v>
+        <v>7122259</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13645,11 +13635,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Äldre hack på tall</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13658,16 +13643,31 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Mattias Dalkvist, Peter Andersson, Torbjörn Söderquist, Elin Kannerby, Beke Regelin, Elke Blöhbaum, Anders Heggestad, Klas Magnusson, Miriam Schenk, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Lise Mortensen, Rolf Nylinder, Lisa Requin, Peder Winding</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -16902,10 +16902,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126914195</v>
+        <v>126914193</v>
       </c>
       <c r="B157" t="n">
-        <v>78420</v>
+        <v>79603</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16913,21 +16913,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16937,10 +16937,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>656646</v>
+        <v>656723</v>
       </c>
       <c r="R157" t="n">
-        <v>7122721</v>
+        <v>7122565</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17013,10 +17013,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126916728</v>
+        <v>126917795</v>
       </c>
       <c r="B158" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17024,21 +17024,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17048,10 +17048,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>656908</v>
+        <v>656507</v>
       </c>
       <c r="R158" t="n">
-        <v>7122278</v>
+        <v>7122604</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17098,12 +17098,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17114,10 +17114,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126916273</v>
+        <v>126915091</v>
       </c>
       <c r="B159" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17125,34 +17125,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>656727</v>
+        <v>656836</v>
       </c>
       <c r="R159" t="n">
-        <v>7122571</v>
+        <v>7122254</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17199,12 +17199,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17215,60 +17215,48 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126915954</v>
+        <v>126920131</v>
       </c>
       <c r="B160" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>656828</v>
+        <v>656819</v>
       </c>
       <c r="R160" t="n">
-        <v>7122387</v>
+        <v>7122264</v>
       </c>
       <c r="S160" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17298,6 +17286,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På kolad tallraka.</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17312,12 +17305,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17328,10 +17321,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126914193</v>
+        <v>126916295</v>
       </c>
       <c r="B161" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17339,37 +17332,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>656723</v>
+        <v>656824</v>
       </c>
       <c r="R161" t="n">
-        <v>7122565</v>
+        <v>7122248</v>
       </c>
       <c r="S161" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17396,19 +17389,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17423,12 +17406,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17439,7 +17422,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126917795</v>
+        <v>126918022</v>
       </c>
       <c r="B162" t="n">
         <v>78773</v>
@@ -17470,14 +17453,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>656507</v>
+        <v>656755</v>
       </c>
       <c r="R162" t="n">
-        <v>7122604</v>
+        <v>7122605</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17521,15 +17504,30 @@
       <c r="AG162" t="b">
         <v>0</v>
       </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17540,7 +17538,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126915091</v>
+        <v>126917794</v>
       </c>
       <c r="B163" t="n">
         <v>78773</v>
@@ -17571,14 +17569,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>656836</v>
+        <v>656498</v>
       </c>
       <c r="R163" t="n">
-        <v>7122254</v>
+        <v>7122598</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17625,12 +17623,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Elke Blöhbaum, Jennica Andersson, Gunilla R Burke, Nicklas Gustavsson, Lise Mortensen, Miriam Schenk</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17641,10 +17639,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126920131</v>
+        <v>126918028</v>
       </c>
       <c r="B164" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17652,34 +17650,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>656819</v>
+        <v>656576</v>
       </c>
       <c r="R164" t="n">
-        <v>7122264</v>
+        <v>7122734</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17714,11 +17712,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>På kolad tallraka.</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17727,16 +17720,31 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17747,32 +17755,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126916295</v>
+        <v>126916320</v>
       </c>
       <c r="B165" t="n">
-        <v>78773</v>
+        <v>92615</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17782,10 +17790,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>656824</v>
+        <v>656843</v>
       </c>
       <c r="R165" t="n">
-        <v>7122248</v>
+        <v>7122356</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17848,10 +17856,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126918022</v>
+        <v>126914195</v>
       </c>
       <c r="B166" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17859,37 +17867,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>656755</v>
+        <v>656646</v>
       </c>
       <c r="R166" t="n">
-        <v>7122605</v>
+        <v>7122721</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17916,11 +17924,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
@@ -17929,31 +17947,16 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17964,10 +17967,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126917794</v>
+        <v>126916728</v>
       </c>
       <c r="B167" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17975,21 +17978,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17999,10 +18002,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>656498</v>
+        <v>656908</v>
       </c>
       <c r="R167" t="n">
-        <v>7122598</v>
+        <v>7122278</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18049,12 +18052,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -18065,10 +18068,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126918028</v>
+        <v>126916273</v>
       </c>
       <c r="B168" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18076,34 +18079,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>656576</v>
+        <v>656727</v>
       </c>
       <c r="R168" t="n">
-        <v>7122734</v>
+        <v>7122571</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18147,30 +18150,15 @@
       <c r="AG168" t="b">
         <v>0</v>
       </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18181,10 +18169,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126916320</v>
+        <v>126915954</v>
       </c>
       <c r="B169" t="n">
-        <v>92615</v>
+        <v>56849</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18192,37 +18180,49 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>656843</v>
+        <v>656828</v>
       </c>
       <c r="R169" t="n">
-        <v>7122356</v>
+        <v>7122387</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18266,12 +18266,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -20822,32 +20822,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126916318</v>
+        <v>126919817</v>
       </c>
       <c r="B194" t="n">
-        <v>92615</v>
+        <v>80117</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20857,10 +20857,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>656775</v>
+        <v>656807</v>
       </c>
       <c r="R194" t="n">
-        <v>7122386</v>
+        <v>7122335</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20907,12 +20907,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20923,10 +20923,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126919817</v>
+        <v>126915953</v>
       </c>
       <c r="B195" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20934,37 +20934,45 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>656807</v>
+        <v>656846</v>
       </c>
       <c r="R195" t="n">
-        <v>7122335</v>
+        <v>7122377</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21008,12 +21016,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21024,10 +21032,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126914189</v>
+        <v>126918413</v>
       </c>
       <c r="B196" t="n">
-        <v>78772</v>
+        <v>57817</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21035,37 +21043,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>656908</v>
+        <v>656867</v>
       </c>
       <c r="R196" t="n">
-        <v>7122416</v>
+        <v>7122465</v>
       </c>
       <c r="S196" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21092,19 +21100,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21119,12 +21117,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -21135,10 +21133,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126918030</v>
+        <v>126918411</v>
       </c>
       <c r="B197" t="n">
-        <v>78420</v>
+        <v>79603</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21146,34 +21144,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>656564</v>
+        <v>656974</v>
       </c>
       <c r="R197" t="n">
-        <v>7122730</v>
+        <v>7122390</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21217,30 +21215,15 @@
       <c r="AG197" t="b">
         <v>0</v>
       </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21251,10 +21234,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126915953</v>
+        <v>126918099</v>
       </c>
       <c r="B198" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21262,45 +21245,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>656846</v>
+        <v>656966</v>
       </c>
       <c r="R198" t="n">
-        <v>7122377</v>
+        <v>7122301</v>
       </c>
       <c r="S198" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21344,12 +21319,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21360,32 +21335,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126918413</v>
+        <v>126916318</v>
       </c>
       <c r="B199" t="n">
-        <v>57817</v>
+        <v>92615</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21395,10 +21370,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>656867</v>
+        <v>656775</v>
       </c>
       <c r="R199" t="n">
-        <v>7122465</v>
+        <v>7122386</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21445,12 +21420,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21461,10 +21436,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126918411</v>
+        <v>126914189</v>
       </c>
       <c r="B200" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21472,37 +21447,37 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>656974</v>
+        <v>656908</v>
       </c>
       <c r="R200" t="n">
-        <v>7122390</v>
+        <v>7122416</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21529,9 +21504,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21546,12 +21531,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21562,10 +21547,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126918099</v>
+        <v>126918030</v>
       </c>
       <c r="B201" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21573,37 +21558,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>656966</v>
+        <v>656564</v>
       </c>
       <c r="R201" t="n">
-        <v>7122301</v>
+        <v>7122730</v>
       </c>
       <c r="S201" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21643,16 +21628,31 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917810</v>
+        <v>126920134</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656710</v>
+        <v>656826</v>
       </c>
       <c r="R4" t="n">
-        <v>7122344</v>
+        <v>7122263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918642</v>
+        <v>126920132</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656705</v>
+        <v>656728</v>
       </c>
       <c r="R5" t="n">
-        <v>7122438</v>
+        <v>7122652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1051,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1068,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1084,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126915089</v>
+        <v>126917810</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656872</v>
+        <v>656710</v>
       </c>
       <c r="R6" t="n">
-        <v>7122285</v>
+        <v>7122344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126916294</v>
+        <v>126918642</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656807</v>
+        <v>656705</v>
       </c>
       <c r="R7" t="n">
-        <v>7122365</v>
+        <v>7122438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,6 +1253,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1270,12 +1270,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126916734</v>
+        <v>126915089</v>
       </c>
       <c r="B8" t="n">
         <v>78773</v>
@@ -1317,14 +1317,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656577</v>
+        <v>656872</v>
       </c>
       <c r="R8" t="n">
-        <v>7122682</v>
+        <v>7122285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,12 +1371,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918676</v>
+        <v>126916294</v>
       </c>
       <c r="B9" t="n">
         <v>78773</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656580</v>
+        <v>656807</v>
       </c>
       <c r="R9" t="n">
-        <v>7122580</v>
+        <v>7122365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,12 +1472,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918430</v>
+        <v>126916734</v>
       </c>
       <c r="B10" t="n">
         <v>78773</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656876</v>
+        <v>656577</v>
       </c>
       <c r="R10" t="n">
-        <v>7122472</v>
+        <v>7122682</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,12 +1573,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126920134</v>
+        <v>126918676</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,21 +1600,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656826</v>
+        <v>656580</v>
       </c>
       <c r="R11" t="n">
-        <v>7122263</v>
+        <v>7122580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126920132</v>
+        <v>126918430</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656728</v>
+        <v>656876</v>
       </c>
       <c r="R12" t="n">
-        <v>7122652</v>
+        <v>7122472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,12 +1775,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1892,32 +1892,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916383</v>
+        <v>126917832</v>
       </c>
       <c r="B14" t="n">
-        <v>91291</v>
+        <v>78420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656948</v>
+        <v>656438</v>
       </c>
       <c r="R14" t="n">
-        <v>7122441</v>
+        <v>7122610</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,12 +1977,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126917832</v>
+        <v>126914186</v>
       </c>
       <c r="B15" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656438</v>
+        <v>656923</v>
       </c>
       <c r="R15" t="n">
-        <v>7122610</v>
+        <v>7122382</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2061,9 +2061,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,12 +2088,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2094,7 +2104,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126914186</v>
+        <v>126914182</v>
       </c>
       <c r="B16" t="n">
         <v>78772</v>
@@ -2129,10 +2139,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656923</v>
+        <v>656885</v>
       </c>
       <c r="R16" t="n">
-        <v>7122382</v>
+        <v>7122248</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2164,7 +2174,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2174,7 +2184,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2194,7 +2204,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126914182</v>
+        <v>126918013</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,37 +2226,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656885</v>
+        <v>656943</v>
       </c>
       <c r="R17" t="n">
-        <v>7122248</v>
+        <v>7122347</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2273,21 +2283,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2296,16 +2296,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2316,53 +2331,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126915952</v>
+        <v>126916383</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>91291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656836</v>
+        <v>656948</v>
       </c>
       <c r="R18" t="n">
-        <v>7122343</v>
+        <v>7122441</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2414,7 +2421,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2425,7 +2432,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918641</v>
+        <v>126915952</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2454,19 +2461,27 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656495</v>
+        <v>656836</v>
       </c>
       <c r="R19" t="n">
-        <v>7122596</v>
+        <v>7122343</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2496,11 +2511,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,12 +2525,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2531,32 +2541,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918442</v>
+        <v>126918641</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656598</v>
+        <v>656495</v>
       </c>
       <c r="R20" t="n">
-        <v>7122760</v>
+        <v>7122596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,6 +2614,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2612,31 +2627,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2647,45 +2647,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918013</v>
+        <v>126918442</v>
       </c>
       <c r="B21" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656943</v>
+        <v>656598</v>
       </c>
       <c r="R21" t="n">
-        <v>7122347</v>
+        <v>7122760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,12 +2747,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2879,45 +2879,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918025</v>
+        <v>126917768</v>
       </c>
       <c r="B23" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656722</v>
+        <v>656842</v>
       </c>
       <c r="R23" t="n">
-        <v>7122706</v>
+        <v>7122270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,12 +2964,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2980,7 +2980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917768</v>
+        <v>126917766</v>
       </c>
       <c r="B24" t="n">
         <v>79632</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656842</v>
+        <v>656527</v>
       </c>
       <c r="R24" t="n">
-        <v>7122270</v>
+        <v>7122602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917766</v>
+        <v>126916302</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656527</v>
+        <v>656815</v>
       </c>
       <c r="R25" t="n">
-        <v>7122602</v>
+        <v>7122359</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3166,12 +3166,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3182,10 +3182,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126916302</v>
+        <v>126918659</v>
       </c>
       <c r="B26" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>656815</v>
+        <v>656834</v>
       </c>
       <c r="R26" t="n">
-        <v>7122359</v>
+        <v>7122225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,6 +3255,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3267,12 +3272,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3700,45 +3705,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918659</v>
+        <v>126918025</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656834</v>
+        <v>656722</v>
       </c>
       <c r="R31" t="n">
-        <v>7122225</v>
+        <v>7122706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3773,11 +3778,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126917826</v>
+        <v>126919828</v>
       </c>
       <c r="B33" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>656423</v>
+        <v>656650</v>
       </c>
       <c r="R33" t="n">
-        <v>7122703</v>
+        <v>7122658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,32 +4008,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918652</v>
+        <v>126914183</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>656722</v>
+        <v>656891</v>
       </c>
       <c r="R34" t="n">
-        <v>7122539</v>
+        <v>7122271</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4076,9 +4076,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4093,12 +4103,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,10 +4119,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126919815</v>
+        <v>126917826</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>77992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,21 +4130,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4154,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>656787</v>
+        <v>656423</v>
       </c>
       <c r="R35" t="n">
-        <v>7122330</v>
+        <v>7122703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,11 +4192,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4199,12 +4204,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4215,32 +4220,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919828</v>
+        <v>126918652</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>656650</v>
+        <v>656722</v>
       </c>
       <c r="R36" t="n">
-        <v>7122658</v>
+        <v>7122539</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4300,12 +4305,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4316,10 +4321,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126914183</v>
+        <v>126919815</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4327,21 +4332,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4351,13 +4356,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>656891</v>
+        <v>656787</v>
       </c>
       <c r="R37" t="n">
-        <v>7122271</v>
+        <v>7122330</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4384,19 +4389,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Liten</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4411,12 +4411,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4528,10 +4528,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126917816</v>
+        <v>126916388</v>
       </c>
       <c r="B39" t="n">
-        <v>78772</v>
+        <v>92809</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,21 +4539,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4563,13 +4563,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>656764</v>
+        <v>656716</v>
       </c>
       <c r="R39" t="n">
-        <v>7122303</v>
+        <v>7122710</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4613,12 +4613,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126920133</v>
+        <v>126918031</v>
       </c>
       <c r="B40" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,34 +4640,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>656724</v>
+        <v>656542</v>
       </c>
       <c r="R40" t="n">
-        <v>7122581</v>
+        <v>7122741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,15 +4711,30 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4730,10 +4745,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126915092</v>
+        <v>126916279</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4741,34 +4756,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656867</v>
+        <v>656878</v>
       </c>
       <c r="R41" t="n">
-        <v>7122430</v>
+        <v>7122337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,6 +4826,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4815,12 +4843,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4831,10 +4859,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126915679</v>
+        <v>126917816</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4842,21 +4870,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4866,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656688</v>
+        <v>656764</v>
       </c>
       <c r="R42" t="n">
-        <v>7122595</v>
+        <v>7122303</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4916,12 +4944,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4932,10 +4960,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126905646</v>
+        <v>126920133</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4943,34 +4971,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656789</v>
+        <v>656724</v>
       </c>
       <c r="R43" t="n">
-        <v>7122441</v>
+        <v>7122581</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5017,12 +5045,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5033,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126916388</v>
+        <v>126915092</v>
       </c>
       <c r="B44" t="n">
-        <v>92809</v>
+        <v>80117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5044,37 +5072,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656716</v>
+        <v>656867</v>
       </c>
       <c r="R44" t="n">
-        <v>7122710</v>
+        <v>7122430</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5118,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5134,10 +5162,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126918031</v>
+        <v>126915679</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5145,34 +5173,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656542</v>
+        <v>656688</v>
       </c>
       <c r="R45" t="n">
-        <v>7122741</v>
+        <v>7122595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5216,30 +5244,15 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5250,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916279</v>
+        <v>126905646</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5261,42 +5274,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656878</v>
+        <v>656789</v>
       </c>
       <c r="R46" t="n">
-        <v>7122337</v>
+        <v>7122441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5331,11 +5336,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5480,10 +5480,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126918431</v>
+        <v>126915676</v>
       </c>
       <c r="B48" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,21 +5491,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>656876</v>
+        <v>656642</v>
       </c>
       <c r="R48" t="n">
-        <v>7122472</v>
+        <v>7122633</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5565,12 +5565,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,32 +5581,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919798</v>
+        <v>126918440</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>656706</v>
+        <v>656962</v>
       </c>
       <c r="R49" t="n">
-        <v>7122542</v>
+        <v>7122294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,11 +5654,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På mossbelupen liggande sälg</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5671,12 +5666,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5788,10 +5783,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126915676</v>
+        <v>126918431</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,21 +5794,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5823,10 +5818,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>656642</v>
+        <v>656876</v>
       </c>
       <c r="R51" t="n">
-        <v>7122633</v>
+        <v>7122472</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5873,12 +5868,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5889,32 +5884,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126918440</v>
+        <v>126919798</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5924,10 +5919,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>656962</v>
+        <v>656706</v>
       </c>
       <c r="R52" t="n">
-        <v>7122294</v>
+        <v>7122542</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5962,6 +5957,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På mossbelupen liggande sälg</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5974,12 +5974,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5990,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915094</v>
+        <v>126916389</v>
       </c>
       <c r="B53" t="n">
-        <v>78681</v>
+        <v>92809</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6001,37 +6001,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>656850</v>
+        <v>656885</v>
       </c>
       <c r="R53" t="n">
-        <v>7122254</v>
+        <v>7122464</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6075,12 +6075,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6091,10 +6091,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126916389</v>
+        <v>126918021</v>
       </c>
       <c r="B54" t="n">
-        <v>92809</v>
+        <v>78772</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6102,37 +6102,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>656885</v>
+        <v>656754</v>
       </c>
       <c r="R54" t="n">
-        <v>7122464</v>
+        <v>7122604</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6172,16 +6172,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6192,48 +6207,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126918096</v>
+        <v>126917776</v>
       </c>
       <c r="B55" t="n">
-        <v>80118</v>
+        <v>79038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>656703</v>
+        <v>656736</v>
       </c>
       <c r="R55" t="n">
-        <v>7122538</v>
+        <v>7122322</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6277,12 +6292,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6293,32 +6308,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918417</v>
+        <v>126916301</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6328,10 +6343,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>656750</v>
+        <v>656717</v>
       </c>
       <c r="R56" t="n">
-        <v>7122529</v>
+        <v>7122549</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6375,30 +6390,15 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6409,45 +6409,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126915093</v>
+        <v>126918694</v>
       </c>
       <c r="B57" t="n">
-        <v>57761</v>
+        <v>78772</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>656892</v>
+        <v>656559</v>
       </c>
       <c r="R57" t="n">
-        <v>7122431</v>
+        <v>7122606</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6494,12 +6494,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6510,10 +6510,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919830</v>
+        <v>126916850</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>656689</v>
+        <v>656628</v>
       </c>
       <c r="R58" t="n">
-        <v>7122578</v>
+        <v>7122610</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6578,14 +6578,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6596,16 +6601,36 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Brandhögstubbe</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6616,32 +6641,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919826</v>
+        <v>126918417</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6651,10 +6676,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656575</v>
+        <v>656750</v>
       </c>
       <c r="R59" t="n">
-        <v>7122664</v>
+        <v>7122529</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6698,15 +6723,30 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6717,10 +6757,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918021</v>
+        <v>126915094</v>
       </c>
       <c r="B60" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6728,34 +6768,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656754</v>
+        <v>656850</v>
       </c>
       <c r="R60" t="n">
-        <v>7122604</v>
+        <v>7122254</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6799,30 +6839,15 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6833,32 +6858,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917776</v>
+        <v>126919830</v>
       </c>
       <c r="B61" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6868,10 +6893,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656736</v>
+        <v>656689</v>
       </c>
       <c r="R61" t="n">
-        <v>7122322</v>
+        <v>7122578</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6906,6 +6931,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6918,12 +6948,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6934,10 +6964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126916301</v>
+        <v>126919826</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6945,21 +6975,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6969,10 +6999,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656717</v>
+        <v>656575</v>
       </c>
       <c r="R62" t="n">
-        <v>7122549</v>
+        <v>7122664</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7019,12 +7049,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7035,45 +7065,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918694</v>
+        <v>126915093</v>
       </c>
       <c r="B63" t="n">
-        <v>78772</v>
+        <v>57761</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656559</v>
+        <v>656892</v>
       </c>
       <c r="R63" t="n">
-        <v>7122606</v>
+        <v>7122431</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7120,12 +7150,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7136,10 +7166,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126916850</v>
+        <v>126918096</v>
       </c>
       <c r="B64" t="n">
-        <v>78772</v>
+        <v>80118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7147,37 +7177,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656628</v>
+        <v>656703</v>
       </c>
       <c r="R64" t="n">
-        <v>7122610</v>
+        <v>7122538</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7204,21 +7234,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7227,36 +7247,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>Brandhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Brandhögstubbe</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7888,32 +7888,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126916855</v>
+        <v>126920135</v>
       </c>
       <c r="B71" t="n">
-        <v>78681</v>
+        <v>98443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>656803</v>
+        <v>656718</v>
       </c>
       <c r="R71" t="n">
-        <v>7122276</v>
+        <v>7122587</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7956,21 +7956,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7979,36 +7969,16 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Gammal tallåga</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallåga</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8019,45 +7989,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126915087</v>
+        <v>126916735</v>
       </c>
       <c r="B72" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656629</v>
+        <v>656861</v>
       </c>
       <c r="R72" t="n">
-        <v>7122746</v>
+        <v>7122418</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8104,12 +8074,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8120,48 +8090,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918448</v>
+        <v>126916291</v>
       </c>
       <c r="B73" t="n">
-        <v>80052</v>
+        <v>78773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6457</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656939</v>
+        <v>656585</v>
       </c>
       <c r="R73" t="n">
-        <v>7122290</v>
+        <v>7122741</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8202,34 +8169,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8240,32 +8191,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126914184</v>
+        <v>126915678</v>
       </c>
       <c r="B74" t="n">
-        <v>80021</v>
+        <v>78773</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8275,13 +8226,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656943</v>
+        <v>656958</v>
       </c>
       <c r="R74" t="n">
-        <v>7122285</v>
+        <v>7122264</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8308,19 +8259,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8335,12 +8276,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8351,10 +8292,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126916732</v>
+        <v>126916855</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>78681</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8362,38 +8303,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656599</v>
+        <v>656803</v>
       </c>
       <c r="R75" t="n">
-        <v>7122660</v>
+        <v>7122276</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8423,14 +8360,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8441,16 +8383,36 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallåga</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8461,45 +8423,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126920135</v>
+        <v>126915087</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656718</v>
+        <v>656629</v>
       </c>
       <c r="R76" t="n">
-        <v>7122587</v>
+        <v>7122746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8546,12 +8508,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8562,45 +8524,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126916735</v>
+        <v>126918448</v>
       </c>
       <c r="B77" t="n">
-        <v>78773</v>
+        <v>80052</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6457</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656861</v>
+        <v>656939</v>
       </c>
       <c r="R77" t="n">
-        <v>7122418</v>
+        <v>7122290</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8641,18 +8606,34 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8663,32 +8644,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126916291</v>
+        <v>126914184</v>
       </c>
       <c r="B78" t="n">
-        <v>78773</v>
+        <v>80021</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8698,13 +8679,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656585</v>
+        <v>656943</v>
       </c>
       <c r="R78" t="n">
-        <v>7122741</v>
+        <v>7122285</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8731,9 +8712,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8748,12 +8739,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8764,10 +8755,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126915678</v>
+        <v>126916732</v>
       </c>
       <c r="B79" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8775,34 +8766,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656958</v>
+        <v>656599</v>
       </c>
       <c r="R79" t="n">
-        <v>7122264</v>
+        <v>7122660</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8837,6 +8832,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8849,12 +8849,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8865,32 +8865,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126915973</v>
+        <v>126918696</v>
       </c>
       <c r="B80" t="n">
-        <v>78681</v>
+        <v>98443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>656870</v>
+        <v>656642</v>
       </c>
       <c r="R80" t="n">
-        <v>7122229</v>
+        <v>7122586</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8950,12 +8950,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8966,7 +8966,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126916311</v>
+        <v>126915973</v>
       </c>
       <c r="B81" t="n">
         <v>78681</v>
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>656790</v>
+        <v>656870</v>
       </c>
       <c r="R81" t="n">
-        <v>7122393</v>
+        <v>7122229</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9051,12 +9051,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9067,32 +9067,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126916319</v>
+        <v>126916311</v>
       </c>
       <c r="B82" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9102,10 +9102,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>656795</v>
+        <v>656790</v>
       </c>
       <c r="R82" t="n">
-        <v>7122394</v>
+        <v>7122393</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9138,11 +9138,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Flertal ex</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9173,32 +9168,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126918457</v>
+        <v>126916319</v>
       </c>
       <c r="B83" t="n">
-        <v>75138</v>
+        <v>92616</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9208,10 +9203,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>656761</v>
+        <v>656795</v>
       </c>
       <c r="R83" t="n">
-        <v>7122534</v>
+        <v>7122394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9246,6 +9241,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Flertal ex</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9254,31 +9254,16 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9289,10 +9274,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916300</v>
+        <v>126918457</v>
       </c>
       <c r="B84" t="n">
-        <v>78772</v>
+        <v>75138</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9300,21 +9285,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9324,10 +9309,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>656721</v>
+        <v>656761</v>
       </c>
       <c r="R84" t="n">
-        <v>7122598</v>
+        <v>7122534</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9371,15 +9356,30 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9390,10 +9390,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126915969</v>
+        <v>126916300</v>
       </c>
       <c r="B85" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9401,21 +9401,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9425,13 +9425,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>656832</v>
+        <v>656721</v>
       </c>
       <c r="R85" t="n">
-        <v>7122445</v>
+        <v>7122598</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9475,12 +9475,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9491,32 +9491,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126919794</v>
+        <v>126915969</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>656670</v>
+        <v>656832</v>
       </c>
       <c r="R86" t="n">
-        <v>7122632</v>
+        <v>7122445</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9576,12 +9576,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9592,32 +9592,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126918432</v>
+        <v>126919794</v>
       </c>
       <c r="B87" t="n">
-        <v>77992</v>
+        <v>80146</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>656876</v>
+        <v>656670</v>
       </c>
       <c r="R87" t="n">
-        <v>7122472</v>
+        <v>7122632</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9677,12 +9677,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9693,10 +9693,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126918691</v>
+        <v>126918432</v>
       </c>
       <c r="B88" t="n">
-        <v>80117</v>
+        <v>77992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,21 +9704,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9728,10 +9728,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>656840</v>
+        <v>656876</v>
       </c>
       <c r="R88" t="n">
-        <v>7122313</v>
+        <v>7122472</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9778,12 +9778,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9794,7 +9794,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126918101</v>
+        <v>126918691</v>
       </c>
       <c r="B89" t="n">
         <v>80117</v>
@@ -9825,17 +9825,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>656660</v>
+        <v>656840</v>
       </c>
       <c r="R89" t="n">
-        <v>7122590</v>
+        <v>7122313</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9879,12 +9879,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9895,48 +9895,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918698</v>
+        <v>126918101</v>
       </c>
       <c r="B90" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>656614</v>
+        <v>656660</v>
       </c>
       <c r="R90" t="n">
-        <v>7122574</v>
+        <v>7122590</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9980,12 +9980,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9996,32 +9996,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126919783</v>
+        <v>126918698</v>
       </c>
       <c r="B91" t="n">
-        <v>79603</v>
+        <v>98443</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>656746</v>
+        <v>656614</v>
       </c>
       <c r="R91" t="n">
-        <v>7122340</v>
+        <v>7122574</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10075,19 +10075,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10098,10 +10097,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126916290</v>
+        <v>126919783</v>
       </c>
       <c r="B92" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10109,21 +10108,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10133,10 +10132,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>656517</v>
+        <v>656746</v>
       </c>
       <c r="R92" t="n">
-        <v>7122763</v>
+        <v>7122340</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10177,18 +10176,19 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10199,7 +10199,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126915677</v>
+        <v>126916290</v>
       </c>
       <c r="B93" t="n">
         <v>78773</v>
@@ -10234,10 +10234,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>656789</v>
+        <v>656517</v>
       </c>
       <c r="R93" t="n">
-        <v>7122426</v>
+        <v>7122763</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10284,12 +10284,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10300,7 +10300,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126917800</v>
+        <v>126915677</v>
       </c>
       <c r="B94" t="n">
         <v>78773</v>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>656842</v>
+        <v>656789</v>
       </c>
       <c r="R94" t="n">
-        <v>7122270</v>
+        <v>7122426</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10385,12 +10385,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10401,32 +10401,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918696</v>
+        <v>126917800</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656642</v>
+        <v>656842</v>
       </c>
       <c r="R95" t="n">
-        <v>7122586</v>
+        <v>7122270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10486,12 +10486,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10502,32 +10502,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918700</v>
+        <v>126918408</v>
       </c>
       <c r="B96" t="n">
-        <v>98443</v>
+        <v>79603</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656657</v>
+        <v>656757</v>
       </c>
       <c r="R96" t="n">
-        <v>7122544</v>
+        <v>7122638</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10587,12 +10587,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10603,10 +10603,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918408</v>
+        <v>126915960</v>
       </c>
       <c r="B97" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10614,21 +10614,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>656757</v>
+        <v>656871</v>
       </c>
       <c r="R97" t="n">
-        <v>7122638</v>
+        <v>7122287</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10682,18 +10682,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10704,10 +10705,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126915960</v>
+        <v>126916307</v>
       </c>
       <c r="B98" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10715,21 +10716,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10739,13 +10740,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656871</v>
+        <v>656532</v>
       </c>
       <c r="R98" t="n">
-        <v>7122287</v>
+        <v>7122751</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10783,19 +10784,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10806,45 +10806,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126916307</v>
+        <v>126918449</v>
       </c>
       <c r="B99" t="n">
-        <v>78681</v>
+        <v>79984</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>656532</v>
+        <v>656939</v>
       </c>
       <c r="R99" t="n">
-        <v>7122751</v>
+        <v>7122290</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10885,18 +10888,34 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10907,48 +10926,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918449</v>
+        <v>126918400</v>
       </c>
       <c r="B100" t="n">
-        <v>79984</v>
+        <v>79632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>385</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656939</v>
+        <v>656591</v>
       </c>
       <c r="R100" t="n">
-        <v>7122290</v>
+        <v>7122782</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10989,24 +11005,8 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11027,7 +11027,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918400</v>
+        <v>126919780</v>
       </c>
       <c r="B101" t="n">
         <v>79632</v>
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656591</v>
+        <v>656724</v>
       </c>
       <c r="R101" t="n">
-        <v>7122782</v>
+        <v>7122461</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11112,12 +11112,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11128,7 +11128,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126919780</v>
+        <v>126918017</v>
       </c>
       <c r="B102" t="n">
         <v>79632</v>
@@ -11159,14 +11159,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656724</v>
+        <v>656803</v>
       </c>
       <c r="R102" t="n">
-        <v>7122461</v>
+        <v>7122418</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11210,15 +11210,30 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11229,10 +11244,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918017</v>
+        <v>126914187</v>
       </c>
       <c r="B103" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11240,37 +11255,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>656803</v>
+        <v>656898</v>
       </c>
       <c r="R103" t="n">
-        <v>7122418</v>
+        <v>7122390</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11297,11 +11312,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11310,31 +11335,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11345,7 +11355,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126914187</v>
+        <v>126915971</v>
       </c>
       <c r="B104" t="n">
         <v>78772</v>
@@ -11376,17 +11386,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656898</v>
+        <v>656619</v>
       </c>
       <c r="R104" t="n">
-        <v>7122390</v>
+        <v>7122605</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11413,19 +11423,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11440,12 +11440,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11456,32 +11456,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126915971</v>
+        <v>126918456</v>
       </c>
       <c r="B105" t="n">
-        <v>78772</v>
+        <v>80152</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11491,13 +11491,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656619</v>
+        <v>656761</v>
       </c>
       <c r="R105" t="n">
-        <v>7122605</v>
+        <v>7122534</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11537,16 +11537,31 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11557,32 +11572,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126918456</v>
+        <v>126915968</v>
       </c>
       <c r="B106" t="n">
-        <v>80152</v>
+        <v>80117</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11592,13 +11607,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>656761</v>
+        <v>656665</v>
       </c>
       <c r="R106" t="n">
-        <v>7122534</v>
+        <v>7122588</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11638,31 +11653,16 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11673,10 +11673,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126915968</v>
+        <v>126918006</v>
       </c>
       <c r="B107" t="n">
-        <v>80117</v>
+        <v>79632</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11684,37 +11684,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>656665</v>
+        <v>656933</v>
       </c>
       <c r="R107" t="n">
-        <v>7122588</v>
+        <v>7122272</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11754,16 +11754,31 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11774,45 +11789,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126918006</v>
+        <v>126918700</v>
       </c>
       <c r="B108" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>656933</v>
+        <v>656657</v>
       </c>
       <c r="R108" t="n">
-        <v>7122272</v>
+        <v>7122544</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11856,30 +11871,15 @@
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11991,45 +11991,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126918009</v>
+        <v>126918027</v>
       </c>
       <c r="B110" t="n">
-        <v>78420</v>
+        <v>8447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6437</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656932</v>
+        <v>656588</v>
       </c>
       <c r="R110" t="n">
-        <v>7122271</v>
+        <v>7122739</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12070,6 +12079,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12107,7 +12117,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126914190</v>
+        <v>126918009</v>
       </c>
       <c r="B111" t="n">
         <v>78420</v>
@@ -12138,17 +12148,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>656890</v>
+        <v>656932</v>
       </c>
       <c r="R111" t="n">
-        <v>7122423</v>
+        <v>7122271</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12175,21 +12185,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12198,16 +12198,31 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12218,10 +12233,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918433</v>
+        <v>126914190</v>
       </c>
       <c r="B112" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12229,37 +12244,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>656876</v>
+        <v>656890</v>
       </c>
       <c r="R112" t="n">
-        <v>7122472</v>
+        <v>7122423</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12286,9 +12301,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12303,12 +12328,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12319,10 +12344,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126916739</v>
+        <v>126918433</v>
       </c>
       <c r="B113" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12330,21 +12355,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12354,10 +12379,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>656871</v>
+        <v>656876</v>
       </c>
       <c r="R113" t="n">
-        <v>7122392</v>
+        <v>7122472</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12404,12 +12429,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12420,10 +12445,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126917827</v>
+        <v>126916739</v>
       </c>
       <c r="B114" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12431,21 +12456,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12455,10 +12480,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>656736</v>
+        <v>656871</v>
       </c>
       <c r="R114" t="n">
-        <v>7122322</v>
+        <v>7122392</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12505,12 +12530,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12521,54 +12546,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918027</v>
+        <v>126917827</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>78420</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6437</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>656588</v>
+        <v>656736</v>
       </c>
       <c r="R115" t="n">
-        <v>7122739</v>
+        <v>7122322</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12609,34 +12625,18 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12647,10 +12647,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126919787</v>
+        <v>126916737</v>
       </c>
       <c r="B116" t="n">
-        <v>79603</v>
+        <v>80117</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12658,21 +12658,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>656835</v>
+        <v>656677</v>
       </c>
       <c r="R116" t="n">
-        <v>7122312</v>
+        <v>7122575</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12726,19 +12726,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12749,7 +12748,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126916737</v>
+        <v>126919819</v>
       </c>
       <c r="B117" t="n">
         <v>80117</v>
@@ -12784,10 +12783,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>656677</v>
+        <v>656821</v>
       </c>
       <c r="R117" t="n">
-        <v>7122575</v>
+        <v>7122322</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12834,12 +12833,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12850,10 +12849,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126919819</v>
+        <v>126919787</v>
       </c>
       <c r="B118" t="n">
-        <v>80117</v>
+        <v>79603</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12861,21 +12860,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12885,10 +12884,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>656821</v>
+        <v>656835</v>
       </c>
       <c r="R118" t="n">
-        <v>7122322</v>
+        <v>7122312</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12929,6 +12928,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12951,10 +12951,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126918005</v>
+        <v>126918409</v>
       </c>
       <c r="B119" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12962,34 +12962,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>656873</v>
+        <v>656757</v>
       </c>
       <c r="R119" t="n">
-        <v>7122259</v>
+        <v>7122638</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13033,30 +13033,15 @@
       <c r="AG119" t="b">
         <v>0</v>
       </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13067,32 +13052,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126917777</v>
+        <v>126919836</v>
       </c>
       <c r="B120" t="n">
-        <v>92809</v>
+        <v>80152</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2079</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13102,10 +13087,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>656802</v>
+        <v>656698</v>
       </c>
       <c r="R120" t="n">
-        <v>7122279</v>
+        <v>7122588</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13152,12 +13137,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13168,32 +13153,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126918409</v>
+        <v>126915958</v>
       </c>
       <c r="B121" t="n">
-        <v>78681</v>
+        <v>80146</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13203,13 +13188,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>656757</v>
+        <v>656674</v>
       </c>
       <c r="R121" t="n">
-        <v>7122638</v>
+        <v>7122583</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13253,12 +13238,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13269,10 +13254,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126919836</v>
+        <v>126919796</v>
       </c>
       <c r="B122" t="n">
-        <v>80152</v>
+        <v>80146</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13280,21 +13265,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13304,10 +13289,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>656698</v>
+        <v>656716</v>
       </c>
       <c r="R122" t="n">
-        <v>7122588</v>
+        <v>7122559</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13370,32 +13355,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126915958</v>
+        <v>126920121</v>
       </c>
       <c r="B123" t="n">
-        <v>80146</v>
+        <v>57657</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13405,13 +13390,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>656674</v>
+        <v>656620</v>
       </c>
       <c r="R123" t="n">
-        <v>7122583</v>
+        <v>7122729</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13441,6 +13426,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre hack på tall</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13455,12 +13445,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13471,45 +13461,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126919796</v>
+        <v>126918005</v>
       </c>
       <c r="B124" t="n">
-        <v>80146</v>
+        <v>79632</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>656716</v>
+        <v>656873</v>
       </c>
       <c r="R124" t="n">
-        <v>7122559</v>
+        <v>7122259</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13553,15 +13543,30 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13572,10 +13577,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126920121</v>
+        <v>126917777</v>
       </c>
       <c r="B125" t="n">
-        <v>57657</v>
+        <v>92809</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13583,21 +13588,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13607,10 +13612,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>656620</v>
+        <v>656802</v>
       </c>
       <c r="R125" t="n">
-        <v>7122729</v>
+        <v>7122279</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13645,11 +13650,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Äldre hack på tall</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13662,12 +13662,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13678,10 +13678,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126919834</v>
+        <v>126915967</v>
       </c>
       <c r="B126" t="n">
-        <v>78681</v>
+        <v>80117</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13689,21 +13689,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13713,13 +13713,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>656603</v>
+        <v>656638</v>
       </c>
       <c r="R126" t="n">
-        <v>7122669</v>
+        <v>7122587</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13763,12 +13763,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13779,10 +13779,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126916740</v>
+        <v>126918690</v>
       </c>
       <c r="B127" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13790,21 +13790,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13814,10 +13814,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>656621</v>
+        <v>656714</v>
       </c>
       <c r="R127" t="n">
-        <v>7122631</v>
+        <v>7122343</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13852,11 +13852,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>På bruten sälgstam</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13869,12 +13864,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13885,32 +13880,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126917831</v>
+        <v>126919838</v>
       </c>
       <c r="B128" t="n">
-        <v>78420</v>
+        <v>80152</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13920,10 +13915,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>656423</v>
+        <v>656821</v>
       </c>
       <c r="R128" t="n">
-        <v>7122703</v>
+        <v>7122315</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13970,12 +13965,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13986,10 +13981,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126918398</v>
+        <v>126917806</v>
       </c>
       <c r="B129" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13997,21 +13992,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14021,10 +14016,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>656669</v>
+        <v>656656</v>
       </c>
       <c r="R129" t="n">
-        <v>7122738</v>
+        <v>7122558</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14071,12 +14066,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14087,10 +14082,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126918093</v>
+        <v>126918098</v>
       </c>
       <c r="B130" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14098,21 +14093,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14122,7 +14117,7 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>656895</v>
+        <v>656894</v>
       </c>
       <c r="R130" t="n">
         <v>7122420</v>
@@ -14188,10 +14183,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126915967</v>
+        <v>126915961</v>
       </c>
       <c r="B131" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14199,21 +14194,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14223,10 +14218,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>656638</v>
+        <v>656616</v>
       </c>
       <c r="R131" t="n">
-        <v>7122587</v>
+        <v>7122600</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -14267,6 +14262,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14289,10 +14285,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126918690</v>
+        <v>126919810</v>
       </c>
       <c r="B132" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14300,21 +14296,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14324,10 +14320,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>656714</v>
+        <v>656586</v>
       </c>
       <c r="R132" t="n">
-        <v>7122343</v>
+        <v>7122656</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14374,12 +14370,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14390,32 +14386,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126919838</v>
+        <v>126919813</v>
       </c>
       <c r="B133" t="n">
-        <v>80152</v>
+        <v>78773</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14425,10 +14421,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>656821</v>
+        <v>656834</v>
       </c>
       <c r="R133" t="n">
-        <v>7122315</v>
+        <v>7122245</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14461,6 +14457,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Mycket på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14491,10 +14492,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126917806</v>
+        <v>126919834</v>
       </c>
       <c r="B134" t="n">
-        <v>80117</v>
+        <v>78681</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14502,21 +14503,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14526,10 +14527,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>656656</v>
+        <v>656603</v>
       </c>
       <c r="R134" t="n">
-        <v>7122558</v>
+        <v>7122669</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14576,12 +14577,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14592,10 +14593,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126918098</v>
+        <v>126916740</v>
       </c>
       <c r="B135" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14603,37 +14604,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>656894</v>
+        <v>656621</v>
       </c>
       <c r="R135" t="n">
-        <v>7122420</v>
+        <v>7122631</v>
       </c>
       <c r="S135" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14663,6 +14664,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På bruten sälgstam</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14677,12 +14683,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14693,10 +14699,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126915961</v>
+        <v>126917831</v>
       </c>
       <c r="B136" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14704,21 +14710,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14728,13 +14734,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>656616</v>
+        <v>656423</v>
       </c>
       <c r="R136" t="n">
-        <v>7122600</v>
+        <v>7122703</v>
       </c>
       <c r="S136" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14772,19 +14778,18 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14795,10 +14800,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126919810</v>
+        <v>126918398</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14806,21 +14811,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14830,10 +14835,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>656586</v>
+        <v>656669</v>
       </c>
       <c r="R137" t="n">
-        <v>7122656</v>
+        <v>7122738</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14880,12 +14885,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14896,10 +14901,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126919813</v>
+        <v>126918093</v>
       </c>
       <c r="B138" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14907,37 +14912,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>656834</v>
+        <v>656895</v>
       </c>
       <c r="R138" t="n">
-        <v>7122245</v>
+        <v>7122420</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14967,11 +14972,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Mycket på kolad högstubbe</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14986,12 +14986,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -15002,10 +15002,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126916738</v>
+        <v>126918452</v>
       </c>
       <c r="B139" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15013,21 +15013,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15037,10 +15037,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>656861</v>
+        <v>656913</v>
       </c>
       <c r="R139" t="n">
-        <v>7122416</v>
+        <v>7122287</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15087,12 +15087,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15103,10 +15103,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126914192</v>
+        <v>126914185</v>
       </c>
       <c r="B140" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15114,34 +15114,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>656722</v>
+        <v>656953</v>
       </c>
       <c r="R140" t="n">
-        <v>7122564</v>
+        <v>7122354</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15214,10 +15214,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126917767</v>
+        <v>126916738</v>
       </c>
       <c r="B141" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15225,21 +15225,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>656581</v>
+        <v>656861</v>
       </c>
       <c r="R141" t="n">
-        <v>7122603</v>
+        <v>7122416</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15299,12 +15299,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15315,10 +15315,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126918452</v>
+        <v>126914192</v>
       </c>
       <c r="B142" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15326,37 +15326,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>656913</v>
+        <v>656722</v>
       </c>
       <c r="R142" t="n">
-        <v>7122287</v>
+        <v>7122564</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15383,9 +15383,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15400,12 +15410,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15416,10 +15426,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126914185</v>
+        <v>126917767</v>
       </c>
       <c r="B143" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15427,21 +15437,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15451,13 +15461,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>656953</v>
+        <v>656581</v>
       </c>
       <c r="R143" t="n">
-        <v>7122354</v>
+        <v>7122603</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15484,19 +15494,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15511,12 +15511,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -16072,48 +16072,48 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126918454</v>
+        <v>126914196</v>
       </c>
       <c r="B149" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>656914</v>
+        <v>656646</v>
       </c>
       <c r="R149" t="n">
-        <v>7122277</v>
+        <v>7122720</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16140,9 +16140,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16157,12 +16167,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -16173,10 +16183,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126914196</v>
+        <v>126916750</v>
       </c>
       <c r="B150" t="n">
-        <v>78772</v>
+        <v>78420</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16184,37 +16194,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>656646</v>
+        <v>656863</v>
       </c>
       <c r="R150" t="n">
-        <v>7122720</v>
+        <v>7122416</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16241,19 +16251,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16268,48 +16268,44 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Beke Regelin, Miriam Schenk, Carl Jansson, Nicklas Gustavsson, Gunilla R Burke, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Elke Blöhbaum, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126916750</v>
+        <v>126918418</v>
       </c>
       <c r="B151" t="n">
-        <v>78420</v>
+        <v>80152</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16319,10 +16315,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>656863</v>
+        <v>656750</v>
       </c>
       <c r="R151" t="n">
-        <v>7122416</v>
+        <v>7122529</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16366,47 +16362,66 @@
       <c r="AG151" t="b">
         <v>0</v>
       </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126918418</v>
+        <v>126919784</v>
       </c>
       <c r="B152" t="n">
-        <v>80152</v>
+        <v>79603</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16416,10 +16431,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>656750</v>
+        <v>656794</v>
       </c>
       <c r="R152" t="n">
-        <v>7122529</v>
+        <v>7122337</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16460,33 +16475,19 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16497,10 +16498,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126919784</v>
+        <v>126920130</v>
       </c>
       <c r="B153" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16508,21 +16509,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16532,10 +16533,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>656794</v>
+        <v>656722</v>
       </c>
       <c r="R153" t="n">
-        <v>7122337</v>
+        <v>7122579</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16576,19 +16577,18 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16599,7 +16599,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126920130</v>
+        <v>126917797</v>
       </c>
       <c r="B154" t="n">
         <v>78773</v>
@@ -16634,10 +16634,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>656722</v>
+        <v>656581</v>
       </c>
       <c r="R154" t="n">
-        <v>7122579</v>
+        <v>7122603</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16684,12 +16684,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16700,7 +16700,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126917797</v>
+        <v>126917793</v>
       </c>
       <c r="B155" t="n">
         <v>78773</v>
@@ -16735,10 +16735,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>656581</v>
+        <v>656447</v>
       </c>
       <c r="R155" t="n">
-        <v>7122603</v>
+        <v>7122672</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16801,32 +16801,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126917793</v>
+        <v>126918454</v>
       </c>
       <c r="B156" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16836,10 +16836,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>656447</v>
+        <v>656914</v>
       </c>
       <c r="R156" t="n">
-        <v>7122672</v>
+        <v>7122277</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16886,12 +16886,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126920138</v>
+        <v>126919823</v>
       </c>
       <c r="B2" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656779</v>
+        <v>656549</v>
       </c>
       <c r="R2" t="n">
-        <v>7122366</v>
+        <v>7122696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126919823</v>
+        <v>126920134</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656549</v>
+        <v>656826</v>
       </c>
       <c r="R3" t="n">
-        <v>7122696</v>
+        <v>7122263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126920134</v>
+        <v>126917810</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656826</v>
+        <v>656710</v>
       </c>
       <c r="R4" t="n">
-        <v>7122263</v>
+        <v>7122344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917810</v>
+        <v>126920132</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656710</v>
+        <v>656728</v>
       </c>
       <c r="R5" t="n">
-        <v>7122344</v>
+        <v>7122652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126920132</v>
+        <v>126918642</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656728</v>
+        <v>656705</v>
       </c>
       <c r="R6" t="n">
-        <v>7122652</v>
+        <v>7122438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1152,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1164,12 +1169,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126918642</v>
+        <v>126920138</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>78681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656705</v>
+        <v>656779</v>
       </c>
       <c r="R7" t="n">
-        <v>7122438</v>
+        <v>7122366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,11 +1258,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1270,12 +1270,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126918430</v>
+        <v>126915089</v>
       </c>
       <c r="B8" t="n">
         <v>78773</v>
@@ -1317,14 +1317,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656876</v>
+        <v>656872</v>
       </c>
       <c r="R8" t="n">
-        <v>7122472</v>
+        <v>7122285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,12 +1371,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126915089</v>
+        <v>126916294</v>
       </c>
       <c r="B9" t="n">
         <v>78773</v>
@@ -1418,14 +1418,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656872</v>
+        <v>656807</v>
       </c>
       <c r="R9" t="n">
-        <v>7122285</v>
+        <v>7122365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,12 +1472,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916294</v>
+        <v>126916734</v>
       </c>
       <c r="B10" t="n">
         <v>78773</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656807</v>
+        <v>656577</v>
       </c>
       <c r="R10" t="n">
-        <v>7122365</v>
+        <v>7122682</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,12 +1573,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1589,7 +1589,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916734</v>
+        <v>126918676</v>
       </c>
       <c r="B11" t="n">
         <v>78773</v>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656577</v>
+        <v>656580</v>
       </c>
       <c r="R11" t="n">
-        <v>7122682</v>
+        <v>7122580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1690,7 +1690,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918676</v>
+        <v>126918430</v>
       </c>
       <c r="B12" t="n">
         <v>78773</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656580</v>
+        <v>656876</v>
       </c>
       <c r="R12" t="n">
-        <v>7122580</v>
+        <v>7122472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,12 +1775,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918453</v>
+        <v>126914186</v>
       </c>
       <c r="B13" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656917</v>
+        <v>656923</v>
       </c>
       <c r="R13" t="n">
-        <v>7122456</v>
+        <v>7122382</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1859,9 +1859,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1876,12 +1886,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1892,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126917832</v>
+        <v>126914182</v>
       </c>
       <c r="B14" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1913,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,13 +1937,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656438</v>
+        <v>656885</v>
       </c>
       <c r="R14" t="n">
-        <v>7122610</v>
+        <v>7122248</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1960,9 +1970,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1977,12 +1997,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1993,32 +2013,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126914186</v>
+        <v>126916383</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>91291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,13 +2048,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656923</v>
+        <v>656948</v>
       </c>
       <c r="R15" t="n">
-        <v>7122382</v>
+        <v>7122441</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2061,19 +2081,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,12 +2098,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2104,32 +2114,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126914182</v>
+        <v>126918453</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2139,13 +2149,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656885</v>
+        <v>656917</v>
       </c>
       <c r="R16" t="n">
-        <v>7122248</v>
+        <v>7122456</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2172,19 +2182,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2199,12 +2199,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2215,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126916383</v>
+        <v>126917832</v>
       </c>
       <c r="B17" t="n">
-        <v>91291</v>
+        <v>78420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656948</v>
+        <v>656438</v>
       </c>
       <c r="R17" t="n">
-        <v>7122441</v>
+        <v>7122610</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2300,12 +2300,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3283,45 +3283,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918659</v>
+        <v>126918695</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656834</v>
+        <v>656654</v>
       </c>
       <c r="R27" t="n">
-        <v>7122225</v>
+        <v>7122550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,17 +3368,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3389,32 +3397,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918662</v>
+        <v>126918701</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3424,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656760</v>
+        <v>656649</v>
       </c>
       <c r="R28" t="n">
-        <v>7122309</v>
+        <v>7122554</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3490,10 +3498,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126920129</v>
+        <v>126918659</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3501,21 +3509,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3525,10 +3533,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656727</v>
+        <v>656834</v>
       </c>
       <c r="R29" t="n">
-        <v>7122637</v>
+        <v>7122225</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3563,6 +3571,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3575,12 +3588,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3591,57 +3604,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918695</v>
+        <v>126918662</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656654</v>
+        <v>656760</v>
       </c>
       <c r="R30" t="n">
-        <v>7122550</v>
+        <v>7122309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,7 +3683,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918701</v>
+        <v>126920129</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656649</v>
+        <v>656727</v>
       </c>
       <c r="R31" t="n">
-        <v>7122554</v>
+        <v>7122637</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4745,10 +4745,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126917816</v>
+        <v>126916279</v>
       </c>
       <c r="B41" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4756,34 +4756,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656764</v>
+        <v>656878</v>
       </c>
       <c r="R41" t="n">
-        <v>7122303</v>
+        <v>7122337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4818,6 +4826,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4830,12 +4843,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4846,7 +4859,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126920133</v>
+        <v>126917816</v>
       </c>
       <c r="B42" t="n">
         <v>78772</v>
@@ -4881,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656724</v>
+        <v>656764</v>
       </c>
       <c r="R42" t="n">
-        <v>7122581</v>
+        <v>7122303</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4931,12 +4944,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4947,10 +4960,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126915092</v>
+        <v>126920133</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4958,34 +4971,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656867</v>
+        <v>656724</v>
       </c>
       <c r="R43" t="n">
-        <v>7122430</v>
+        <v>7122581</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5032,12 +5045,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5048,7 +5061,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126915679</v>
+        <v>126915092</v>
       </c>
       <c r="B44" t="n">
         <v>80117</v>
@@ -5079,14 +5092,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656688</v>
+        <v>656867</v>
       </c>
       <c r="R44" t="n">
-        <v>7122595</v>
+        <v>7122430</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5133,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5149,7 +5162,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126905646</v>
+        <v>126915679</v>
       </c>
       <c r="B45" t="n">
         <v>80117</v>
@@ -5180,14 +5193,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656789</v>
+        <v>656688</v>
       </c>
       <c r="R45" t="n">
-        <v>7122441</v>
+        <v>7122595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5234,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5250,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916279</v>
+        <v>126905646</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5261,42 +5274,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656878</v>
+        <v>656789</v>
       </c>
       <c r="R46" t="n">
-        <v>7122337</v>
+        <v>7122441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5331,11 +5336,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5465,10 +5465,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126918014</v>
+        <v>126915676</v>
       </c>
       <c r="B48" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5476,34 +5476,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>656944</v>
+        <v>656642</v>
       </c>
       <c r="R48" t="n">
-        <v>7122345</v>
+        <v>7122633</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5547,30 +5547,15 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,32 +5566,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919798</v>
+        <v>126918440</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5616,10 +5601,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>656706</v>
+        <v>656962</v>
       </c>
       <c r="R49" t="n">
-        <v>7122542</v>
+        <v>7122294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,11 +5639,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På mossbelupen liggande sälg</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5671,12 +5651,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5687,10 +5667,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918445</v>
+        <v>126918014</v>
       </c>
       <c r="B50" t="n">
-        <v>41361</v>
+        <v>78681</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5698,34 +5678,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>215713</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>656978</v>
+        <v>656944</v>
       </c>
       <c r="R50" t="n">
-        <v>7122381</v>
+        <v>7122345</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5769,15 +5749,30 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5788,32 +5783,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126915676</v>
+        <v>126919798</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5823,10 +5818,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>656642</v>
+        <v>656706</v>
       </c>
       <c r="R51" t="n">
-        <v>7122633</v>
+        <v>7122542</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5861,6 +5856,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På mossbelupen liggande sälg</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5873,12 +5873,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5889,10 +5889,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126918440</v>
+        <v>126918445</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>41361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5900,21 +5900,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>215713</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5924,10 +5924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>656962</v>
+        <v>656978</v>
       </c>
       <c r="R52" t="n">
-        <v>7122294</v>
+        <v>7122381</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918403</v>
+        <v>126918658</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7278,21 +7278,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656749</v>
+        <v>656664</v>
       </c>
       <c r="R65" t="n">
-        <v>7122643</v>
+        <v>7122576</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7340,6 +7340,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7352,12 +7357,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7368,32 +7373,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126917775</v>
+        <v>126917799</v>
       </c>
       <c r="B66" t="n">
-        <v>79038</v>
+        <v>78773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7403,10 +7408,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656581</v>
+        <v>656764</v>
       </c>
       <c r="R66" t="n">
-        <v>7122603</v>
+        <v>7122303</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7469,10 +7474,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126919837</v>
+        <v>126917775</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>79038</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7480,21 +7485,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7509,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656726</v>
+        <v>656581</v>
       </c>
       <c r="R67" t="n">
-        <v>7122533</v>
+        <v>7122603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7554,12 +7559,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7570,10 +7575,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918658</v>
+        <v>126918403</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,21 +7586,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7605,10 +7610,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656664</v>
+        <v>656749</v>
       </c>
       <c r="R68" t="n">
-        <v>7122576</v>
+        <v>7122643</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7643,11 +7648,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7676,10 +7676,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126914197</v>
+        <v>126919837</v>
       </c>
       <c r="B69" t="n">
-        <v>8447</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7687,37 +7687,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>656647</v>
+        <v>656726</v>
       </c>
       <c r="R69" t="n">
-        <v>7122722</v>
+        <v>7122533</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7744,19 +7744,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7771,12 +7761,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7787,48 +7777,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126917799</v>
+        <v>126914197</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>656764</v>
+        <v>656647</v>
       </c>
       <c r="R70" t="n">
-        <v>7122303</v>
+        <v>7122722</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7855,9 +7845,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7872,12 +7872,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8019,45 +8019,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126916735</v>
+        <v>126915087</v>
       </c>
       <c r="B72" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656861</v>
+        <v>656629</v>
       </c>
       <c r="R72" t="n">
-        <v>7122418</v>
+        <v>7122746</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8104,12 +8104,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8120,45 +8120,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126916291</v>
+        <v>126918448</v>
       </c>
       <c r="B73" t="n">
-        <v>78773</v>
+        <v>80052</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6457</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656585</v>
+        <v>656939</v>
       </c>
       <c r="R73" t="n">
-        <v>7122741</v>
+        <v>7122290</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8199,18 +8202,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8221,32 +8240,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126915678</v>
+        <v>126914184</v>
       </c>
       <c r="B74" t="n">
-        <v>78773</v>
+        <v>80021</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8256,13 +8275,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656958</v>
+        <v>656943</v>
       </c>
       <c r="R74" t="n">
-        <v>7122264</v>
+        <v>7122285</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8289,9 +8308,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8306,12 +8335,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8322,45 +8351,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126920135</v>
+        <v>126916732</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656718</v>
+        <v>656599</v>
       </c>
       <c r="R75" t="n">
-        <v>7122587</v>
+        <v>7122660</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8395,6 +8428,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8407,12 +8445,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8423,45 +8461,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126915087</v>
+        <v>126916735</v>
       </c>
       <c r="B76" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656629</v>
+        <v>656861</v>
       </c>
       <c r="R76" t="n">
-        <v>7122746</v>
+        <v>7122418</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8508,12 +8546,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8524,48 +8562,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126918448</v>
+        <v>126916291</v>
       </c>
       <c r="B77" t="n">
-        <v>80052</v>
+        <v>78773</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6457</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656939</v>
+        <v>656585</v>
       </c>
       <c r="R77" t="n">
-        <v>7122290</v>
+        <v>7122741</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8606,34 +8641,18 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8644,32 +8663,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126914184</v>
+        <v>126915678</v>
       </c>
       <c r="B78" t="n">
-        <v>80021</v>
+        <v>78773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8679,13 +8698,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656943</v>
+        <v>656958</v>
       </c>
       <c r="R78" t="n">
-        <v>7122285</v>
+        <v>7122264</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8712,19 +8731,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8739,12 +8748,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8755,49 +8764,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126916732</v>
+        <v>126920135</v>
       </c>
       <c r="B79" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656599</v>
+        <v>656718</v>
       </c>
       <c r="R79" t="n">
-        <v>7122660</v>
+        <v>7122587</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8832,11 +8837,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8849,12 +8849,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8865,32 +8865,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916319</v>
+        <v>126918457</v>
       </c>
       <c r="B80" t="n">
-        <v>92616</v>
+        <v>75138</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>656795</v>
+        <v>656761</v>
       </c>
       <c r="R80" t="n">
-        <v>7122394</v>
+        <v>7122534</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8938,11 +8938,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Flertal ex</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8951,16 +8946,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8971,10 +8981,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918457</v>
+        <v>126915969</v>
       </c>
       <c r="B81" t="n">
-        <v>75138</v>
+        <v>80117</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8982,21 +8992,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9006,13 +9016,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>656761</v>
+        <v>656832</v>
       </c>
       <c r="R81" t="n">
-        <v>7122534</v>
+        <v>7122445</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9052,31 +9062,16 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9087,32 +9082,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126915969</v>
+        <v>126919794</v>
       </c>
       <c r="B82" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9122,13 +9117,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>656832</v>
+        <v>656670</v>
       </c>
       <c r="R82" t="n">
-        <v>7122445</v>
+        <v>7122632</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9172,12 +9167,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9188,32 +9183,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126919794</v>
+        <v>126916300</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9223,10 +9218,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>656670</v>
+        <v>656721</v>
       </c>
       <c r="R83" t="n">
-        <v>7122632</v>
+        <v>7122598</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9273,12 +9268,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9289,10 +9284,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126916300</v>
+        <v>126918432</v>
       </c>
       <c r="B84" t="n">
-        <v>78772</v>
+        <v>77992</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9300,21 +9295,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9324,10 +9319,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>656721</v>
+        <v>656876</v>
       </c>
       <c r="R84" t="n">
-        <v>7122598</v>
+        <v>7122472</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9374,12 +9369,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9390,10 +9385,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126918432</v>
+        <v>126918691</v>
       </c>
       <c r="B85" t="n">
-        <v>77992</v>
+        <v>80117</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9401,21 +9396,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9425,10 +9420,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>656876</v>
+        <v>656840</v>
       </c>
       <c r="R85" t="n">
-        <v>7122472</v>
+        <v>7122313</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9475,12 +9470,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9491,7 +9486,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918691</v>
+        <v>126918101</v>
       </c>
       <c r="B86" t="n">
         <v>80117</v>
@@ -9522,17 +9517,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>656840</v>
+        <v>656660</v>
       </c>
       <c r="R86" t="n">
-        <v>7122313</v>
+        <v>7122590</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9576,12 +9571,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9592,10 +9587,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126918101</v>
+        <v>126915973</v>
       </c>
       <c r="B87" t="n">
-        <v>80117</v>
+        <v>78681</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9603,37 +9598,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>656660</v>
+        <v>656870</v>
       </c>
       <c r="R87" t="n">
-        <v>7122590</v>
+        <v>7122229</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9677,12 +9672,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9693,10 +9688,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126919783</v>
+        <v>126916311</v>
       </c>
       <c r="B88" t="n">
-        <v>79603</v>
+        <v>78681</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9704,21 +9699,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9728,10 +9723,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>656746</v>
+        <v>656790</v>
       </c>
       <c r="R88" t="n">
-        <v>7122340</v>
+        <v>7122393</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9772,19 +9767,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9795,32 +9789,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126916290</v>
+        <v>126916319</v>
       </c>
       <c r="B89" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9830,10 +9824,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>656517</v>
+        <v>656795</v>
       </c>
       <c r="R89" t="n">
-        <v>7122763</v>
+        <v>7122394</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9866,6 +9860,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Flertal ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9896,10 +9895,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126915677</v>
+        <v>126919783</v>
       </c>
       <c r="B90" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9907,21 +9906,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9931,10 +9930,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>656789</v>
+        <v>656746</v>
       </c>
       <c r="R90" t="n">
-        <v>7122426</v>
+        <v>7122340</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9975,18 +9974,19 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9997,7 +9997,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126917800</v>
+        <v>126916290</v>
       </c>
       <c r="B91" t="n">
         <v>78773</v>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>656842</v>
+        <v>656517</v>
       </c>
       <c r="R91" t="n">
-        <v>7122270</v>
+        <v>7122763</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10082,12 +10082,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10098,32 +10098,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918698</v>
+        <v>126915677</v>
       </c>
       <c r="B92" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>656614</v>
+        <v>656789</v>
       </c>
       <c r="R92" t="n">
-        <v>7122574</v>
+        <v>7122426</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10183,12 +10183,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10199,32 +10199,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126918696</v>
+        <v>126917800</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10234,10 +10234,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>656642</v>
+        <v>656842</v>
       </c>
       <c r="R93" t="n">
-        <v>7122586</v>
+        <v>7122270</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10284,12 +10284,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10300,32 +10300,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126915973</v>
+        <v>126918698</v>
       </c>
       <c r="B94" t="n">
-        <v>78681</v>
+        <v>98443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10335,13 +10335,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>656870</v>
+        <v>656614</v>
       </c>
       <c r="R94" t="n">
-        <v>7122229</v>
+        <v>7122574</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10385,12 +10385,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10401,32 +10401,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126916311</v>
+        <v>126918696</v>
       </c>
       <c r="B95" t="n">
-        <v>78681</v>
+        <v>98443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656790</v>
+        <v>656642</v>
       </c>
       <c r="R95" t="n">
-        <v>7122393</v>
+        <v>7122586</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10486,12 +10486,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11890,45 +11890,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126916737</v>
+        <v>126918027</v>
       </c>
       <c r="B109" t="n">
-        <v>80117</v>
+        <v>8447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>656677</v>
+        <v>656588</v>
       </c>
       <c r="R109" t="n">
-        <v>7122575</v>
+        <v>7122739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11969,18 +11978,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11991,10 +12016,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126918433</v>
+        <v>126919787</v>
       </c>
       <c r="B110" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12002,21 +12027,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12026,10 +12051,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>656876</v>
+        <v>656835</v>
       </c>
       <c r="R110" t="n">
-        <v>7122472</v>
+        <v>7122312</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12070,18 +12095,19 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12092,7 +12118,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126919819</v>
+        <v>126916737</v>
       </c>
       <c r="B111" t="n">
         <v>80117</v>
@@ -12127,10 +12153,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>656821</v>
+        <v>656677</v>
       </c>
       <c r="R111" t="n">
-        <v>7122322</v>
+        <v>7122575</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12177,12 +12203,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12193,10 +12219,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126916739</v>
+        <v>126918433</v>
       </c>
       <c r="B112" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,21 +12230,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12228,10 +12254,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>656871</v>
+        <v>656876</v>
       </c>
       <c r="R112" t="n">
-        <v>7122392</v>
+        <v>7122472</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12278,12 +12304,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12294,10 +12320,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918009</v>
+        <v>126919819</v>
       </c>
       <c r="B113" t="n">
-        <v>78420</v>
+        <v>80117</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12305,34 +12331,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>656932</v>
+        <v>656821</v>
       </c>
       <c r="R113" t="n">
-        <v>7122271</v>
+        <v>7122322</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12376,30 +12402,15 @@
       <c r="AG113" t="b">
         <v>0</v>
       </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12410,10 +12421,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126914190</v>
+        <v>126916739</v>
       </c>
       <c r="B114" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12421,37 +12432,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>656890</v>
+        <v>656871</v>
       </c>
       <c r="R114" t="n">
-        <v>7122423</v>
+        <v>7122392</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12478,19 +12489,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12505,12 +12506,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12521,45 +12522,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918420</v>
+        <v>126918009</v>
       </c>
       <c r="B115" t="n">
-        <v>79038</v>
+        <v>78420</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>656973</v>
+        <v>656932</v>
       </c>
       <c r="R115" t="n">
-        <v>7122312</v>
+        <v>7122271</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12603,15 +12604,30 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12622,7 +12638,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126917827</v>
+        <v>126914190</v>
       </c>
       <c r="B116" t="n">
         <v>78420</v>
@@ -12653,17 +12669,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>656736</v>
+        <v>656890</v>
       </c>
       <c r="R116" t="n">
-        <v>7122322</v>
+        <v>7122423</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12690,9 +12706,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12707,12 +12733,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12723,10 +12749,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918027</v>
+        <v>126918420</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>79038</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12734,43 +12760,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>656588</v>
+        <v>656973</v>
       </c>
       <c r="R117" t="n">
-        <v>7122739</v>
+        <v>7122312</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12811,34 +12828,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12849,10 +12850,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126919787</v>
+        <v>126917827</v>
       </c>
       <c r="B118" t="n">
-        <v>79603</v>
+        <v>78420</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12860,21 +12861,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12884,10 +12885,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>656835</v>
+        <v>656736</v>
       </c>
       <c r="R118" t="n">
-        <v>7122312</v>
+        <v>7122322</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12928,19 +12929,18 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126919823</v>
+        <v>126920138</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656549</v>
+        <v>656779</v>
       </c>
       <c r="R2" t="n">
-        <v>7122696</v>
+        <v>7122366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126920134</v>
+        <v>126919823</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656826</v>
+        <v>656549</v>
       </c>
       <c r="R3" t="n">
-        <v>7122263</v>
+        <v>7122696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917810</v>
+        <v>126920134</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656710</v>
+        <v>656826</v>
       </c>
       <c r="R4" t="n">
-        <v>7122344</v>
+        <v>7122263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126920132</v>
+        <v>126917810</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656728</v>
+        <v>656710</v>
       </c>
       <c r="R5" t="n">
-        <v>7122652</v>
+        <v>7122344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918642</v>
+        <v>126920132</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656705</v>
+        <v>656728</v>
       </c>
       <c r="R6" t="n">
-        <v>7122438</v>
+        <v>7122652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,11 +1152,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1169,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126920138</v>
+        <v>126918642</v>
       </c>
       <c r="B7" t="n">
-        <v>78681</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656779</v>
+        <v>656705</v>
       </c>
       <c r="R7" t="n">
-        <v>7122366</v>
+        <v>7122438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,6 +1253,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1270,12 +1270,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126914186</v>
+        <v>126918453</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,13 +1826,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656923</v>
+        <v>656917</v>
       </c>
       <c r="R13" t="n">
-        <v>7122382</v>
+        <v>7122456</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1859,19 +1859,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1886,12 +1876,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1902,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126914182</v>
+        <v>126917832</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1913,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,13 +1927,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656885</v>
+        <v>656438</v>
       </c>
       <c r="R14" t="n">
-        <v>7122248</v>
+        <v>7122610</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,19 +1960,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,12 +1977,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2013,32 +1993,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916383</v>
+        <v>126914186</v>
       </c>
       <c r="B15" t="n">
-        <v>91291</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2048,13 +2028,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656948</v>
+        <v>656923</v>
       </c>
       <c r="R15" t="n">
-        <v>7122441</v>
+        <v>7122382</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2081,9 +2061,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2098,12 +2088,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2114,32 +2104,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918453</v>
+        <v>126914182</v>
       </c>
       <c r="B16" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2149,13 +2139,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656917</v>
+        <v>656885</v>
       </c>
       <c r="R16" t="n">
-        <v>7122456</v>
+        <v>7122248</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2182,9 +2172,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2199,12 +2199,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2215,32 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917832</v>
+        <v>126916383</v>
       </c>
       <c r="B17" t="n">
-        <v>78420</v>
+        <v>91291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656438</v>
+        <v>656948</v>
       </c>
       <c r="R17" t="n">
-        <v>7122610</v>
+        <v>7122441</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2300,12 +2300,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -4745,10 +4745,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126916279</v>
+        <v>126917816</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4756,42 +4756,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656878</v>
+        <v>656764</v>
       </c>
       <c r="R41" t="n">
-        <v>7122337</v>
+        <v>7122303</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4826,11 +4818,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4843,12 +4830,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4859,7 +4846,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126917816</v>
+        <v>126920133</v>
       </c>
       <c r="B42" t="n">
         <v>78772</v>
@@ -4894,10 +4881,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656764</v>
+        <v>656724</v>
       </c>
       <c r="R42" t="n">
-        <v>7122303</v>
+        <v>7122581</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4944,12 +4931,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4960,10 +4947,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126920133</v>
+        <v>126915092</v>
       </c>
       <c r="B43" t="n">
-        <v>78772</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4971,34 +4958,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656724</v>
+        <v>656867</v>
       </c>
       <c r="R43" t="n">
-        <v>7122581</v>
+        <v>7122430</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5045,12 +5032,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5061,7 +5048,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126915092</v>
+        <v>126915679</v>
       </c>
       <c r="B44" t="n">
         <v>80117</v>
@@ -5092,14 +5079,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656867</v>
+        <v>656688</v>
       </c>
       <c r="R44" t="n">
-        <v>7122430</v>
+        <v>7122595</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5133,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,7 +5149,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126915679</v>
+        <v>126905646</v>
       </c>
       <c r="B45" t="n">
         <v>80117</v>
@@ -5193,14 +5180,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656688</v>
+        <v>656789</v>
       </c>
       <c r="R45" t="n">
-        <v>7122595</v>
+        <v>7122441</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5234,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,10 +5250,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126905646</v>
+        <v>126916279</v>
       </c>
       <c r="B46" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,34 +5261,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656789</v>
+        <v>656878</v>
       </c>
       <c r="R46" t="n">
-        <v>7122441</v>
+        <v>7122337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,6 +5331,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5990,32 +5990,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915094</v>
+        <v>126915093</v>
       </c>
       <c r="B53" t="n">
-        <v>78681</v>
+        <v>57761</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>656850</v>
+        <v>656892</v>
       </c>
       <c r="R53" t="n">
-        <v>7122254</v>
+        <v>7122431</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126916389</v>
+        <v>126915094</v>
       </c>
       <c r="B54" t="n">
-        <v>92809</v>
+        <v>78681</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6102,37 +6102,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>656885</v>
+        <v>656850</v>
       </c>
       <c r="R54" t="n">
-        <v>7122464</v>
+        <v>7122254</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6176,12 +6176,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126918096</v>
+        <v>126918021</v>
       </c>
       <c r="B55" t="n">
-        <v>80118</v>
+        <v>78772</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6203,37 +6203,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>656703</v>
+        <v>656754</v>
       </c>
       <c r="R55" t="n">
-        <v>7122538</v>
+        <v>7122604</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6273,16 +6273,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6293,10 +6308,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126917776</v>
+        <v>126918417</v>
       </c>
       <c r="B56" t="n">
-        <v>79038</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6304,21 +6319,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6434</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6328,10 +6343,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>656736</v>
+        <v>656750</v>
       </c>
       <c r="R56" t="n">
-        <v>7122322</v>
+        <v>7122529</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6375,15 +6390,30 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6394,10 +6424,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126919830</v>
+        <v>126916301</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6405,21 +6435,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6429,10 +6459,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>656689</v>
+        <v>656717</v>
       </c>
       <c r="R57" t="n">
-        <v>7122578</v>
+        <v>7122549</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6467,11 +6497,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6484,12 +6509,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6500,10 +6525,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919826</v>
+        <v>126918694</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6511,21 +6536,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6535,10 +6560,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>656575</v>
+        <v>656559</v>
       </c>
       <c r="R58" t="n">
-        <v>7122664</v>
+        <v>7122606</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6585,12 +6610,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6601,7 +6626,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126918021</v>
+        <v>126916850</v>
       </c>
       <c r="B59" t="n">
         <v>78772</v>
@@ -6632,14 +6657,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656754</v>
+        <v>656628</v>
       </c>
       <c r="R59" t="n">
-        <v>7122604</v>
+        <v>7122610</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6669,11 +6694,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6693,20 +6728,25 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Brandhögstubbe</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Brandhögstubbe</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6717,32 +6757,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918417</v>
+        <v>126916389</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>92809</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6752,13 +6792,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656750</v>
+        <v>656885</v>
       </c>
       <c r="R60" t="n">
-        <v>7122529</v>
+        <v>7122464</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6798,31 +6838,16 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6833,10 +6858,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126916301</v>
+        <v>126918096</v>
       </c>
       <c r="B61" t="n">
-        <v>78772</v>
+        <v>80118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6844,37 +6869,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656717</v>
+        <v>656703</v>
       </c>
       <c r="R61" t="n">
-        <v>7122549</v>
+        <v>7122538</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6918,12 +6943,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6934,32 +6959,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918694</v>
+        <v>126917776</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>79038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6969,10 +6994,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656559</v>
+        <v>656736</v>
       </c>
       <c r="R62" t="n">
-        <v>7122606</v>
+        <v>7122322</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7019,12 +7044,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7035,10 +7060,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126916850</v>
+        <v>126919830</v>
       </c>
       <c r="B63" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7046,21 +7071,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7070,10 +7095,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656628</v>
+        <v>656689</v>
       </c>
       <c r="R63" t="n">
-        <v>7122610</v>
+        <v>7122578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,19 +7128,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:33</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7126,36 +7146,16 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Brandhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Brandhögstubbe</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7166,45 +7166,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126915093</v>
+        <v>126919826</v>
       </c>
       <c r="B64" t="n">
-        <v>57761</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656892</v>
+        <v>656575</v>
       </c>
       <c r="R64" t="n">
-        <v>7122431</v>
+        <v>7122664</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7251,12 +7251,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -8865,32 +8865,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918457</v>
+        <v>126916319</v>
       </c>
       <c r="B80" t="n">
-        <v>75138</v>
+        <v>92616</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>656761</v>
+        <v>656795</v>
       </c>
       <c r="R80" t="n">
-        <v>7122534</v>
+        <v>7122394</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8938,6 +8938,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Flertal ex</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8946,31 +8951,16 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8981,10 +8971,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126915969</v>
+        <v>126918457</v>
       </c>
       <c r="B81" t="n">
-        <v>80117</v>
+        <v>75138</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8992,21 +8982,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9016,13 +9006,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>656832</v>
+        <v>656761</v>
       </c>
       <c r="R81" t="n">
-        <v>7122445</v>
+        <v>7122534</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9062,16 +9052,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9082,32 +9087,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126919794</v>
+        <v>126915969</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9117,13 +9122,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>656670</v>
+        <v>656832</v>
       </c>
       <c r="R82" t="n">
-        <v>7122632</v>
+        <v>7122445</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9167,12 +9172,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9183,32 +9188,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126916300</v>
+        <v>126919794</v>
       </c>
       <c r="B83" t="n">
-        <v>78772</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9218,10 +9223,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>656721</v>
+        <v>656670</v>
       </c>
       <c r="R83" t="n">
-        <v>7122598</v>
+        <v>7122632</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9268,12 +9273,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9284,10 +9289,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126918432</v>
+        <v>126916300</v>
       </c>
       <c r="B84" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9295,21 +9300,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9319,10 +9324,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>656876</v>
+        <v>656721</v>
       </c>
       <c r="R84" t="n">
-        <v>7122472</v>
+        <v>7122598</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9369,12 +9374,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9385,10 +9390,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126918691</v>
+        <v>126918432</v>
       </c>
       <c r="B85" t="n">
-        <v>80117</v>
+        <v>77992</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9396,21 +9401,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9420,10 +9425,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>656840</v>
+        <v>656876</v>
       </c>
       <c r="R85" t="n">
-        <v>7122313</v>
+        <v>7122472</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9470,12 +9475,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9486,7 +9491,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918101</v>
+        <v>126918691</v>
       </c>
       <c r="B86" t="n">
         <v>80117</v>
@@ -9517,17 +9522,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>656660</v>
+        <v>656840</v>
       </c>
       <c r="R86" t="n">
-        <v>7122590</v>
+        <v>7122313</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9571,12 +9576,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9587,10 +9592,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915973</v>
+        <v>126918101</v>
       </c>
       <c r="B87" t="n">
-        <v>78681</v>
+        <v>80117</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9598,37 +9603,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>656870</v>
+        <v>656660</v>
       </c>
       <c r="R87" t="n">
-        <v>7122229</v>
+        <v>7122590</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9672,12 +9677,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9688,10 +9693,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126916311</v>
+        <v>126919783</v>
       </c>
       <c r="B88" t="n">
-        <v>78681</v>
+        <v>79603</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9699,21 +9704,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9723,10 +9728,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>656790</v>
+        <v>656746</v>
       </c>
       <c r="R88" t="n">
-        <v>7122393</v>
+        <v>7122340</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9767,18 +9772,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9789,32 +9795,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126916319</v>
+        <v>126916290</v>
       </c>
       <c r="B89" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9824,10 +9830,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>656795</v>
+        <v>656517</v>
       </c>
       <c r="R89" t="n">
-        <v>7122394</v>
+        <v>7122763</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9860,11 +9866,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Flertal ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9895,10 +9896,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126919783</v>
+        <v>126915677</v>
       </c>
       <c r="B90" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9906,21 +9907,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9930,10 +9931,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>656746</v>
+        <v>656789</v>
       </c>
       <c r="R90" t="n">
-        <v>7122340</v>
+        <v>7122426</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9974,19 +9975,18 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9997,7 +9997,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126916290</v>
+        <v>126917800</v>
       </c>
       <c r="B91" t="n">
         <v>78773</v>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>656517</v>
+        <v>656842</v>
       </c>
       <c r="R91" t="n">
-        <v>7122763</v>
+        <v>7122270</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10082,12 +10082,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10098,32 +10098,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126915677</v>
+        <v>126918698</v>
       </c>
       <c r="B92" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>656789</v>
+        <v>656614</v>
       </c>
       <c r="R92" t="n">
-        <v>7122426</v>
+        <v>7122574</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10183,12 +10183,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10199,32 +10199,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126917800</v>
+        <v>126918696</v>
       </c>
       <c r="B93" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10234,10 +10234,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>656842</v>
+        <v>656642</v>
       </c>
       <c r="R93" t="n">
-        <v>7122270</v>
+        <v>7122586</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10284,12 +10284,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10300,32 +10300,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918698</v>
+        <v>126915973</v>
       </c>
       <c r="B94" t="n">
-        <v>98443</v>
+        <v>78681</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10335,13 +10335,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>656614</v>
+        <v>656870</v>
       </c>
       <c r="R94" t="n">
-        <v>7122574</v>
+        <v>7122229</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10385,12 +10385,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10401,32 +10401,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918696</v>
+        <v>126916311</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>78681</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656642</v>
+        <v>656790</v>
       </c>
       <c r="R95" t="n">
-        <v>7122586</v>
+        <v>7122393</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10486,12 +10486,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10502,10 +10502,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918400</v>
+        <v>126916307</v>
       </c>
       <c r="B96" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10513,21 +10513,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10537,10 +10537,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>656591</v>
+        <v>656532</v>
       </c>
       <c r="R96" t="n">
-        <v>7122782</v>
+        <v>7122751</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10587,12 +10587,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10603,45 +10603,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918456</v>
+        <v>126918449</v>
       </c>
       <c r="B97" t="n">
-        <v>80152</v>
+        <v>79984</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>656761</v>
+        <v>656939</v>
       </c>
       <c r="R97" t="n">
-        <v>7122534</v>
+        <v>7122290</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10682,22 +10685,23 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -10719,7 +10723,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126919780</v>
+        <v>126918400</v>
       </c>
       <c r="B98" t="n">
         <v>79632</v>
@@ -10754,10 +10758,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656724</v>
+        <v>656591</v>
       </c>
       <c r="R98" t="n">
-        <v>7122461</v>
+        <v>7122782</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10804,12 +10808,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10820,32 +10824,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126915968</v>
+        <v>126918456</v>
       </c>
       <c r="B99" t="n">
-        <v>80117</v>
+        <v>80152</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10855,13 +10859,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>656665</v>
+        <v>656761</v>
       </c>
       <c r="R99" t="n">
-        <v>7122588</v>
+        <v>7122534</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10901,16 +10905,31 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10921,7 +10940,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918006</v>
+        <v>126919780</v>
       </c>
       <c r="B100" t="n">
         <v>79632</v>
@@ -10952,14 +10971,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656933</v>
+        <v>656724</v>
       </c>
       <c r="R100" t="n">
-        <v>7122272</v>
+        <v>7122461</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11003,30 +11022,15 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11037,10 +11041,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126918017</v>
+        <v>126915968</v>
       </c>
       <c r="B101" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11048,37 +11052,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656803</v>
+        <v>656665</v>
       </c>
       <c r="R101" t="n">
-        <v>7122418</v>
+        <v>7122588</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11118,31 +11122,16 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11153,10 +11142,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126914187</v>
+        <v>126918006</v>
       </c>
       <c r="B102" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11164,37 +11153,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656898</v>
+        <v>656933</v>
       </c>
       <c r="R102" t="n">
-        <v>7122390</v>
+        <v>7122272</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11221,21 +11210,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11244,16 +11223,31 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11264,10 +11258,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126915971</v>
+        <v>126918017</v>
       </c>
       <c r="B103" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11275,37 +11269,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>656619</v>
+        <v>656803</v>
       </c>
       <c r="R103" t="n">
-        <v>7122605</v>
+        <v>7122418</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11345,16 +11339,31 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11365,48 +11374,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918700</v>
+        <v>126914187</v>
       </c>
       <c r="B104" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656657</v>
+        <v>656898</v>
       </c>
       <c r="R104" t="n">
-        <v>7122544</v>
+        <v>7122390</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11433,9 +11442,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11450,12 +11469,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11466,10 +11485,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126916307</v>
+        <v>126915971</v>
       </c>
       <c r="B105" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11477,21 +11496,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11501,13 +11520,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656532</v>
+        <v>656619</v>
       </c>
       <c r="R105" t="n">
-        <v>7122751</v>
+        <v>7122605</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11551,12 +11570,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11567,48 +11586,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126918449</v>
+        <v>126918408</v>
       </c>
       <c r="B106" t="n">
-        <v>79984</v>
+        <v>79603</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>385</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>656939</v>
+        <v>656757</v>
       </c>
       <c r="R106" t="n">
-        <v>7122290</v>
+        <v>7122638</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11649,24 +11665,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126918408</v>
+        <v>126915960</v>
       </c>
       <c r="B107" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11698,21 +11698,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11722,13 +11722,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>656757</v>
+        <v>656871</v>
       </c>
       <c r="R107" t="n">
-        <v>7122638</v>
+        <v>7122287</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11766,18 +11766,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11788,32 +11789,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126915960</v>
+        <v>126918700</v>
       </c>
       <c r="B108" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11823,13 +11824,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>656871</v>
+        <v>656657</v>
       </c>
       <c r="R108" t="n">
-        <v>7122287</v>
+        <v>7122544</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11867,19 +11868,18 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12118,10 +12118,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126916737</v>
+        <v>126918009</v>
       </c>
       <c r="B111" t="n">
-        <v>80117</v>
+        <v>78420</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12129,34 +12129,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>656677</v>
+        <v>656932</v>
       </c>
       <c r="R111" t="n">
-        <v>7122575</v>
+        <v>7122271</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12200,15 +12200,30 @@
       <c r="AG111" t="b">
         <v>0</v>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12219,10 +12234,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918433</v>
+        <v>126914190</v>
       </c>
       <c r="B112" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12230,37 +12245,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>656876</v>
+        <v>656890</v>
       </c>
       <c r="R112" t="n">
-        <v>7122472</v>
+        <v>7122423</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12287,9 +12302,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12304,12 +12329,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12320,32 +12345,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126919819</v>
+        <v>126918420</v>
       </c>
       <c r="B113" t="n">
-        <v>80117</v>
+        <v>79038</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12355,10 +12380,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>656821</v>
+        <v>656973</v>
       </c>
       <c r="R113" t="n">
-        <v>7122322</v>
+        <v>7122312</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12405,12 +12430,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12421,10 +12446,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126916739</v>
+        <v>126917827</v>
       </c>
       <c r="B114" t="n">
-        <v>78772</v>
+        <v>78420</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12432,21 +12457,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12456,10 +12481,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>656871</v>
+        <v>656736</v>
       </c>
       <c r="R114" t="n">
-        <v>7122392</v>
+        <v>7122322</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12506,12 +12531,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12522,10 +12547,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918009</v>
+        <v>126916737</v>
       </c>
       <c r="B115" t="n">
-        <v>78420</v>
+        <v>80117</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12533,34 +12558,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>656932</v>
+        <v>656677</v>
       </c>
       <c r="R115" t="n">
-        <v>7122271</v>
+        <v>7122575</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12604,30 +12629,15 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12638,10 +12648,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126914190</v>
+        <v>126918433</v>
       </c>
       <c r="B116" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12649,37 +12659,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>656890</v>
+        <v>656876</v>
       </c>
       <c r="R116" t="n">
-        <v>7122423</v>
+        <v>7122472</v>
       </c>
       <c r="S116" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12706,19 +12716,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12733,12 +12733,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12749,32 +12749,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918420</v>
+        <v>126919819</v>
       </c>
       <c r="B117" t="n">
-        <v>79038</v>
+        <v>80117</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12784,10 +12784,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>656973</v>
+        <v>656821</v>
       </c>
       <c r="R117" t="n">
-        <v>7122312</v>
+        <v>7122322</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12834,12 +12834,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12850,10 +12850,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126917827</v>
+        <v>126916739</v>
       </c>
       <c r="B118" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12861,21 +12861,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12885,10 +12885,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>656736</v>
+        <v>656871</v>
       </c>
       <c r="R118" t="n">
-        <v>7122322</v>
+        <v>7122392</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12935,12 +12935,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13779,10 +13779,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126915967</v>
+        <v>126917831</v>
       </c>
       <c r="B127" t="n">
-        <v>80117</v>
+        <v>78420</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13790,21 +13790,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13814,13 +13814,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>656638</v>
+        <v>656423</v>
       </c>
       <c r="R127" t="n">
-        <v>7122587</v>
+        <v>7122703</v>
       </c>
       <c r="S127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13864,12 +13864,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13880,10 +13880,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126918398</v>
+        <v>126915967</v>
       </c>
       <c r="B128" t="n">
-        <v>79632</v>
+        <v>80117</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13891,21 +13891,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13915,13 +13915,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>656669</v>
+        <v>656638</v>
       </c>
       <c r="R128" t="n">
-        <v>7122738</v>
+        <v>7122587</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13965,12 +13965,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13981,10 +13981,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126917806</v>
+        <v>126918398</v>
       </c>
       <c r="B129" t="n">
-        <v>80117</v>
+        <v>79632</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13992,21 +13992,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>656656</v>
+        <v>656669</v>
       </c>
       <c r="R129" t="n">
-        <v>7122558</v>
+        <v>7122738</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14066,12 +14066,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14082,10 +14082,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126916740</v>
+        <v>126918690</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14093,21 +14093,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14117,10 +14117,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>656621</v>
+        <v>656714</v>
       </c>
       <c r="R130" t="n">
-        <v>7122631</v>
+        <v>7122343</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14155,11 +14155,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>På bruten sälgstam</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14172,12 +14167,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14188,32 +14183,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126917831</v>
+        <v>126919838</v>
       </c>
       <c r="B131" t="n">
-        <v>78420</v>
+        <v>80152</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14223,10 +14218,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>656423</v>
+        <v>656821</v>
       </c>
       <c r="R131" t="n">
-        <v>7122703</v>
+        <v>7122315</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14273,12 +14268,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14289,7 +14284,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126918690</v>
+        <v>126917806</v>
       </c>
       <c r="B132" t="n">
         <v>80117</v>
@@ -14324,10 +14319,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>656714</v>
+        <v>656656</v>
       </c>
       <c r="R132" t="n">
-        <v>7122343</v>
+        <v>7122558</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14374,12 +14369,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14390,48 +14385,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126919838</v>
+        <v>126918093</v>
       </c>
       <c r="B133" t="n">
-        <v>80152</v>
+        <v>79632</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>656821</v>
+        <v>656895</v>
       </c>
       <c r="R133" t="n">
-        <v>7122315</v>
+        <v>7122420</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14475,12 +14470,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14491,10 +14486,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126918093</v>
+        <v>126916740</v>
       </c>
       <c r="B134" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14502,37 +14497,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>656895</v>
+        <v>656621</v>
       </c>
       <c r="R134" t="n">
-        <v>7122420</v>
+        <v>7122631</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14562,6 +14557,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På bruten sälgstam</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14576,12 +14576,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -15517,10 +15517,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126914185</v>
+        <v>126914181</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15528,21 +15528,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15552,13 +15552,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>656953</v>
+        <v>656884</v>
       </c>
       <c r="R144" t="n">
-        <v>7122354</v>
+        <v>7122247</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15628,7 +15628,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126914181</v>
+        <v>126918007</v>
       </c>
       <c r="B145" t="n">
         <v>78773</v>
@@ -15659,17 +15659,17 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>656884</v>
+        <v>656933</v>
       </c>
       <c r="R145" t="n">
-        <v>7122247</v>
+        <v>7122273</v>
       </c>
       <c r="S145" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15696,21 +15696,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -15719,16 +15709,31 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15739,10 +15744,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126918007</v>
+        <v>126918029</v>
       </c>
       <c r="B146" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15750,21 +15755,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15774,10 +15779,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>656933</v>
+        <v>656577</v>
       </c>
       <c r="R146" t="n">
-        <v>7122273</v>
+        <v>7122733</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15855,7 +15860,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126918029</v>
+        <v>126905615</v>
       </c>
       <c r="B147" t="n">
         <v>79603</v>
@@ -15886,14 +15891,14 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>656577</v>
+        <v>656822</v>
       </c>
       <c r="R147" t="n">
-        <v>7122733</v>
+        <v>7122398</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15937,30 +15942,15 @@
       <c r="AG147" t="b">
         <v>0</v>
       </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15971,10 +15961,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126905615</v>
+        <v>126914185</v>
       </c>
       <c r="B148" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15982,37 +15972,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>656822</v>
+        <v>656953</v>
       </c>
       <c r="R148" t="n">
-        <v>7122398</v>
+        <v>7122354</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16039,9 +16029,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16056,12 +16056,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16072,32 +16072,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126918454</v>
+        <v>126916750</v>
       </c>
       <c r="B149" t="n">
-        <v>92616</v>
+        <v>78420</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>656914</v>
+        <v>656863</v>
       </c>
       <c r="R149" t="n">
-        <v>7122277</v>
+        <v>7122416</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16157,48 +16157,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126916750</v>
+        <v>126918418</v>
       </c>
       <c r="B150" t="n">
-        <v>78420</v>
+        <v>80152</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16208,10 +16204,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>656863</v>
+        <v>656750</v>
       </c>
       <c r="R150" t="n">
-        <v>7122416</v>
+        <v>7122529</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16255,25 +16251,44 @@
       <c r="AG150" t="b">
         <v>0</v>
       </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr"/>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126919784</v>
+        <v>126914196</v>
       </c>
       <c r="B151" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16281,37 +16296,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>656794</v>
+        <v>656646</v>
       </c>
       <c r="R151" t="n">
-        <v>7122337</v>
+        <v>7122720</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16338,30 +16353,39 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -16372,32 +16396,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126920130</v>
+        <v>126918454</v>
       </c>
       <c r="B152" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16407,10 +16431,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>656722</v>
+        <v>656914</v>
       </c>
       <c r="R152" t="n">
-        <v>7122579</v>
+        <v>7122277</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16457,12 +16481,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16473,10 +16497,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126917797</v>
+        <v>126919784</v>
       </c>
       <c r="B153" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16484,21 +16508,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16508,10 +16532,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>656581</v>
+        <v>656794</v>
       </c>
       <c r="R153" t="n">
-        <v>7122603</v>
+        <v>7122337</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16552,18 +16576,19 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16574,7 +16599,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126917793</v>
+        <v>126920130</v>
       </c>
       <c r="B154" t="n">
         <v>78773</v>
@@ -16609,10 +16634,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>656447</v>
+        <v>656722</v>
       </c>
       <c r="R154" t="n">
-        <v>7122672</v>
+        <v>7122579</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16659,12 +16684,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16675,32 +16700,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126918418</v>
+        <v>126917797</v>
       </c>
       <c r="B155" t="n">
-        <v>80152</v>
+        <v>78773</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16710,10 +16735,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>656750</v>
+        <v>656581</v>
       </c>
       <c r="R155" t="n">
-        <v>7122529</v>
+        <v>7122603</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16757,30 +16782,15 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16791,10 +16801,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126914196</v>
+        <v>126917793</v>
       </c>
       <c r="B156" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16802,37 +16812,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>656646</v>
+        <v>656447</v>
       </c>
       <c r="R156" t="n">
-        <v>7122720</v>
+        <v>7122672</v>
       </c>
       <c r="S156" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16859,19 +16869,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16886,12 +16886,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16902,45 +16902,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126916320</v>
+        <v>126918028</v>
       </c>
       <c r="B157" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>656843</v>
+        <v>656576</v>
       </c>
       <c r="R157" t="n">
-        <v>7122356</v>
+        <v>7122734</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16984,15 +16984,30 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17114,32 +17129,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126916728</v>
+        <v>126916320</v>
       </c>
       <c r="B159" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17149,10 +17164,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>656908</v>
+        <v>656843</v>
       </c>
       <c r="R159" t="n">
-        <v>7122278</v>
+        <v>7122356</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17199,12 +17214,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17215,7 +17230,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126916273</v>
+        <v>126916728</v>
       </c>
       <c r="B160" t="n">
         <v>79632</v>
@@ -17250,10 +17265,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>656727</v>
+        <v>656908</v>
       </c>
       <c r="R160" t="n">
-        <v>7122571</v>
+        <v>7122278</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17300,12 +17315,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17316,60 +17331,48 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126915954</v>
+        <v>126916273</v>
       </c>
       <c r="B161" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>656828</v>
+        <v>656727</v>
       </c>
       <c r="R161" t="n">
-        <v>7122387</v>
+        <v>7122571</v>
       </c>
       <c r="S161" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17413,12 +17416,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17429,48 +17432,60 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126918028</v>
+        <v>126915954</v>
       </c>
       <c r="B162" t="n">
-        <v>78681</v>
+        <v>56849</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>656576</v>
+        <v>656828</v>
       </c>
       <c r="R162" t="n">
-        <v>7122734</v>
+        <v>7122387</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17510,31 +17525,16 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17545,7 +17545,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126917795</v>
+        <v>126920131</v>
       </c>
       <c r="B163" t="n">
         <v>78773</v>
@@ -17580,10 +17580,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>656507</v>
+        <v>656819</v>
       </c>
       <c r="R163" t="n">
-        <v>7122604</v>
+        <v>7122264</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17618,6 +17618,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På kolad tallraka.</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -17630,12 +17635,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17646,7 +17651,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126920131</v>
+        <v>126917794</v>
       </c>
       <c r="B164" t="n">
         <v>78773</v>
@@ -17681,10 +17686,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>656819</v>
+        <v>656498</v>
       </c>
       <c r="R164" t="n">
-        <v>7122264</v>
+        <v>7122598</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17719,11 +17724,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>På kolad tallraka.</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
@@ -17736,12 +17736,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17863,7 +17863,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126915091</v>
+        <v>126917795</v>
       </c>
       <c r="B166" t="n">
         <v>78773</v>
@@ -17894,14 +17894,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>656836</v>
+        <v>656507</v>
       </c>
       <c r="R166" t="n">
-        <v>7122254</v>
+        <v>7122604</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17948,12 +17948,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17964,7 +17964,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126916295</v>
+        <v>126915091</v>
       </c>
       <c r="B167" t="n">
         <v>78773</v>
@@ -17995,14 +17995,14 @@
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>656824</v>
+        <v>656836</v>
       </c>
       <c r="R167" t="n">
-        <v>7122248</v>
+        <v>7122254</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18049,12 +18049,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -18065,7 +18065,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126918022</v>
+        <v>126916295</v>
       </c>
       <c r="B168" t="n">
         <v>78773</v>
@@ -18096,14 +18096,14 @@
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>656755</v>
+        <v>656824</v>
       </c>
       <c r="R168" t="n">
-        <v>7122605</v>
+        <v>7122248</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18147,30 +18147,15 @@
       <c r="AG168" t="b">
         <v>0</v>
       </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18181,7 +18166,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126917794</v>
+        <v>126918022</v>
       </c>
       <c r="B169" t="n">
         <v>78773</v>
@@ -18212,14 +18197,14 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>656498</v>
+        <v>656755</v>
       </c>
       <c r="R169" t="n">
-        <v>7122598</v>
+        <v>7122605</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18263,15 +18248,30 @@
       <c r="AG169" t="b">
         <v>0</v>
       </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -18282,32 +18282,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126919835</v>
+        <v>126918697</v>
       </c>
       <c r="B170" t="n">
-        <v>78681</v>
+        <v>98443</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18317,10 +18317,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>656811</v>
+        <v>656625</v>
       </c>
       <c r="R170" t="n">
-        <v>7122322</v>
+        <v>7122578</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18355,11 +18355,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -18372,12 +18367,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -18388,32 +18383,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126917812</v>
+        <v>126919835</v>
       </c>
       <c r="B171" t="n">
-        <v>80153</v>
+        <v>78681</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18423,10 +18418,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>656710</v>
+        <v>656811</v>
       </c>
       <c r="R171" t="n">
-        <v>7122344</v>
+        <v>7122322</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18461,6 +18456,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
@@ -18473,12 +18473,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18489,45 +18489,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126917765</v>
+        <v>126918004</v>
       </c>
       <c r="B172" t="n">
-        <v>79632</v>
+        <v>91487</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>656447</v>
+        <v>656857</v>
       </c>
       <c r="R172" t="n">
-        <v>7122672</v>
+        <v>7122220</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18571,15 +18571,30 @@
       <c r="AG172" t="b">
         <v>0</v>
       </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -18590,32 +18605,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126916731</v>
+        <v>126918392</v>
       </c>
       <c r="B173" t="n">
-        <v>80146</v>
+        <v>75138</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18625,10 +18640,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>656616</v>
+        <v>656628</v>
       </c>
       <c r="R173" t="n">
-        <v>7122643</v>
+        <v>7122758</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18663,11 +18678,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -18680,12 +18690,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18696,45 +18706,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126918012</v>
+        <v>126917812</v>
       </c>
       <c r="B174" t="n">
-        <v>79632</v>
+        <v>80153</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>656942</v>
+        <v>656710</v>
       </c>
       <c r="R174" t="n">
-        <v>7122347</v>
+        <v>7122344</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18778,30 +18788,15 @@
       <c r="AG174" t="b">
         <v>0</v>
       </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18812,45 +18807,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126918004</v>
+        <v>126917765</v>
       </c>
       <c r="B175" t="n">
-        <v>91487</v>
+        <v>79632</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>656857</v>
+        <v>656447</v>
       </c>
       <c r="R175" t="n">
-        <v>7122220</v>
+        <v>7122672</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18894,30 +18889,15 @@
       <c r="AG175" t="b">
         <v>0</v>
       </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18928,32 +18908,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126918392</v>
+        <v>126916731</v>
       </c>
       <c r="B176" t="n">
-        <v>75138</v>
+        <v>80146</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18963,10 +18943,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>656628</v>
+        <v>656616</v>
       </c>
       <c r="R176" t="n">
-        <v>7122758</v>
+        <v>7122643</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19001,6 +18981,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19013,12 +18998,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -19029,10 +19014,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126916391</v>
+        <v>126918012</v>
       </c>
       <c r="B177" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19040,37 +19025,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>656635</v>
+        <v>656942</v>
       </c>
       <c r="R177" t="n">
-        <v>7122743</v>
+        <v>7122347</v>
       </c>
       <c r="S177" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19110,16 +19095,31 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -19130,7 +19130,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126916292</v>
+        <v>126916391</v>
       </c>
       <c r="B178" t="n">
         <v>78773</v>
@@ -19165,13 +19165,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>656647</v>
+        <v>656635</v>
       </c>
       <c r="R178" t="n">
-        <v>7122645</v>
+        <v>7122743</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19215,12 +19215,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -19231,32 +19231,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126918697</v>
+        <v>126916292</v>
       </c>
       <c r="B179" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19266,10 +19266,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>656625</v>
+        <v>656647</v>
       </c>
       <c r="R179" t="n">
-        <v>7122578</v>
+        <v>7122645</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19316,12 +19316,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -19665,10 +19665,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126918441</v>
+        <v>126919800</v>
       </c>
       <c r="B183" t="n">
-        <v>8447</v>
+        <v>80146</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19676,21 +19676,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19700,10 +19700,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>656596</v>
+        <v>656820</v>
       </c>
       <c r="R183" t="n">
-        <v>7122771</v>
+        <v>7122319</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19747,30 +19747,15 @@
       <c r="AG183" t="b">
         <v>0</v>
       </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19781,10 +19766,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126917796</v>
+        <v>126917817</v>
       </c>
       <c r="B184" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19792,21 +19777,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19816,10 +19801,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>656580</v>
+        <v>656842</v>
       </c>
       <c r="R184" t="n">
-        <v>7122596</v>
+        <v>7122270</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19882,10 +19867,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126916736</v>
+        <v>126915674</v>
       </c>
       <c r="B185" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19893,21 +19878,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19917,10 +19902,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>656871</v>
+        <v>656846</v>
       </c>
       <c r="R185" t="n">
-        <v>7122392</v>
+        <v>7122403</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19955,11 +19940,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>På kolad kärnved, högstubbe</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -19972,12 +19952,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -19988,48 +19968,48 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126914188</v>
+        <v>126917823</v>
       </c>
       <c r="B186" t="n">
-        <v>78773</v>
+        <v>80152</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>656907</v>
+        <v>656656</v>
       </c>
       <c r="R186" t="n">
-        <v>7122416</v>
+        <v>7122558</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20056,19 +20036,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20083,12 +20053,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -20099,45 +20069,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126919800</v>
+        <v>126918016</v>
       </c>
       <c r="B187" t="n">
-        <v>80146</v>
+        <v>91799</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6462</v>
+        <v>5467</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>656820</v>
+        <v>656879</v>
       </c>
       <c r="R187" t="n">
-        <v>7122319</v>
+        <v>7122412</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20181,15 +20151,30 @@
       <c r="AG187" t="b">
         <v>0</v>
       </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -20200,10 +20185,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126917817</v>
+        <v>126917796</v>
       </c>
       <c r="B188" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20211,21 +20196,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20235,10 +20220,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>656842</v>
+        <v>656580</v>
       </c>
       <c r="R188" t="n">
-        <v>7122270</v>
+        <v>7122596</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20301,10 +20286,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126915674</v>
+        <v>126916736</v>
       </c>
       <c r="B189" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20312,21 +20297,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20336,10 +20321,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>656846</v>
+        <v>656871</v>
       </c>
       <c r="R189" t="n">
-        <v>7122403</v>
+        <v>7122392</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20374,6 +20359,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>På kolad kärnved, högstubbe</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20386,12 +20376,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -20402,48 +20392,48 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126917823</v>
+        <v>126914188</v>
       </c>
       <c r="B190" t="n">
-        <v>80152</v>
+        <v>78773</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>656656</v>
+        <v>656907</v>
       </c>
       <c r="R190" t="n">
-        <v>7122558</v>
+        <v>7122416</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20470,9 +20460,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20487,12 +20487,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20503,45 +20503,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126918016</v>
+        <v>126918441</v>
       </c>
       <c r="B191" t="n">
-        <v>91799</v>
+        <v>8447</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>656879</v>
+        <v>656596</v>
       </c>
       <c r="R191" t="n">
-        <v>7122412</v>
+        <v>7122771</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20603,12 +20603,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20619,10 +20619,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126918103</v>
+        <v>126918653</v>
       </c>
       <c r="B192" t="n">
-        <v>80989</v>
+        <v>80118</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20630,37 +20630,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>656889</v>
+        <v>656729</v>
       </c>
       <c r="R192" t="n">
-        <v>7122426</v>
+        <v>7122537</v>
       </c>
       <c r="S192" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20698,19 +20698,18 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -20721,10 +20720,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126915953</v>
+        <v>126918413</v>
       </c>
       <c r="B193" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20732,45 +20731,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>656846</v>
+        <v>656867</v>
       </c>
       <c r="R193" t="n">
-        <v>7122377</v>
+        <v>7122465</v>
       </c>
       <c r="S193" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20814,12 +20805,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -20830,10 +20821,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918413</v>
+        <v>126918411</v>
       </c>
       <c r="B194" t="n">
-        <v>57817</v>
+        <v>79603</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20841,21 +20832,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20865,10 +20856,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>656867</v>
+        <v>656974</v>
       </c>
       <c r="R194" t="n">
-        <v>7122465</v>
+        <v>7122390</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20931,10 +20922,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918411</v>
+        <v>126918099</v>
       </c>
       <c r="B195" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20942,37 +20933,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>656974</v>
+        <v>656966</v>
       </c>
       <c r="R195" t="n">
-        <v>7122390</v>
+        <v>7122301</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21016,12 +21007,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21032,10 +21023,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126918099</v>
+        <v>126918103</v>
       </c>
       <c r="B196" t="n">
-        <v>78773</v>
+        <v>80989</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21043,21 +21034,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21067,10 +21058,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>656966</v>
+        <v>656889</v>
       </c>
       <c r="R196" t="n">
-        <v>7122301</v>
+        <v>7122426</v>
       </c>
       <c r="S196" t="n">
         <v>20</v>
@@ -21111,6 +21102,7 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -21234,10 +21226,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126918653</v>
+        <v>126918030</v>
       </c>
       <c r="B198" t="n">
-        <v>80118</v>
+        <v>78420</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21245,34 +21237,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>656729</v>
+        <v>656564</v>
       </c>
       <c r="R198" t="n">
-        <v>7122537</v>
+        <v>7122730</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21316,15 +21308,30 @@
       <c r="AG198" t="b">
         <v>0</v>
       </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21335,10 +21342,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126918030</v>
+        <v>126914189</v>
       </c>
       <c r="B199" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21346,37 +21353,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>656564</v>
+        <v>656908</v>
       </c>
       <c r="R199" t="n">
-        <v>7122730</v>
+        <v>7122416</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21403,11 +21410,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
@@ -21416,31 +21433,16 @@
       </c>
       <c r="AG199" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21451,10 +21453,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126914189</v>
+        <v>126919817</v>
       </c>
       <c r="B200" t="n">
-        <v>78772</v>
+        <v>80117</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21462,37 +21464,37 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>656908</v>
+        <v>656807</v>
       </c>
       <c r="R200" t="n">
-        <v>7122416</v>
+        <v>7122335</v>
       </c>
       <c r="S200" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21519,19 +21521,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21546,12 +21538,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21562,10 +21554,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126919817</v>
+        <v>126915953</v>
       </c>
       <c r="B201" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21573,37 +21565,45 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>656807</v>
+        <v>656846</v>
       </c>
       <c r="R201" t="n">
-        <v>7122335</v>
+        <v>7122377</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21647,12 +21647,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -1791,45 +1791,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918013</v>
+        <v>126918453</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656943</v>
+        <v>656917</v>
       </c>
       <c r="R13" t="n">
-        <v>7122347</v>
+        <v>7122456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,30 +1873,15 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1907,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918442</v>
+        <v>126916383</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>91295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,13 +1927,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656598</v>
+        <v>656948</v>
       </c>
       <c r="R14" t="n">
-        <v>7122760</v>
+        <v>7122441</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1988,31 +1973,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2346,45 +2316,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918453</v>
+        <v>126918013</v>
       </c>
       <c r="B18" t="n">
-        <v>92620</v>
+        <v>79607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656917</v>
+        <v>656943</v>
       </c>
       <c r="R18" t="n">
-        <v>7122456</v>
+        <v>7122347</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,15 +2398,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2447,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126916383</v>
+        <v>126918442</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2482,13 +2467,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656948</v>
+        <v>656598</v>
       </c>
       <c r="R19" t="n">
-        <v>7122441</v>
+        <v>7122760</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2528,16 +2513,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126916279</v>
+        <v>126918031</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,42 +4640,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>656878</v>
+        <v>656542</v>
       </c>
       <c r="R40" t="n">
-        <v>7122337</v>
+        <v>7122741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4710,11 +4702,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4723,16 +4710,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4743,10 +4745,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126918031</v>
+        <v>126917816</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4754,34 +4756,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656542</v>
+        <v>656764</v>
       </c>
       <c r="R41" t="n">
-        <v>7122741</v>
+        <v>7122303</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4825,30 +4827,15 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4859,7 +4846,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126917816</v>
+        <v>126920133</v>
       </c>
       <c r="B42" t="n">
         <v>78776</v>
@@ -4894,10 +4881,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656764</v>
+        <v>656724</v>
       </c>
       <c r="R42" t="n">
-        <v>7122303</v>
+        <v>7122581</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4944,12 +4931,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4960,10 +4947,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126920133</v>
+        <v>126915092</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4971,34 +4958,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656724</v>
+        <v>656867</v>
       </c>
       <c r="R43" t="n">
-        <v>7122581</v>
+        <v>7122430</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5045,12 +5032,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5061,7 +5048,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126915092</v>
+        <v>126915679</v>
       </c>
       <c r="B44" t="n">
         <v>80121</v>
@@ -5092,14 +5079,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656867</v>
+        <v>656688</v>
       </c>
       <c r="R44" t="n">
-        <v>7122430</v>
+        <v>7122595</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5133,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,7 +5149,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126915679</v>
+        <v>126905646</v>
       </c>
       <c r="B45" t="n">
         <v>80121</v>
@@ -5193,14 +5180,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656688</v>
+        <v>656789</v>
       </c>
       <c r="R45" t="n">
-        <v>7122595</v>
+        <v>7122441</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5234,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,10 +5250,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126905646</v>
+        <v>126916279</v>
       </c>
       <c r="B46" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,34 +5261,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656789</v>
+        <v>656878</v>
       </c>
       <c r="R46" t="n">
-        <v>7122441</v>
+        <v>7122337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,6 +5331,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -7267,10 +7267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918403</v>
+        <v>126917799</v>
       </c>
       <c r="B65" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7278,21 +7278,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656749</v>
+        <v>656764</v>
       </c>
       <c r="R65" t="n">
-        <v>7122643</v>
+        <v>7122303</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7352,12 +7352,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126917775</v>
+        <v>126918403</v>
       </c>
       <c r="B66" t="n">
-        <v>79042</v>
+        <v>79636</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656581</v>
+        <v>656749</v>
       </c>
       <c r="R66" t="n">
-        <v>7122603</v>
+        <v>7122643</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7453,12 +7453,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7469,10 +7469,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126919837</v>
+        <v>126917775</v>
       </c>
       <c r="B67" t="n">
-        <v>80156</v>
+        <v>79042</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7480,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656726</v>
+        <v>656581</v>
       </c>
       <c r="R67" t="n">
-        <v>7122533</v>
+        <v>7122603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7554,12 +7554,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7570,10 +7570,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126914197</v>
+        <v>126919837</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>80156</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,37 +7581,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656647</v>
+        <v>656726</v>
       </c>
       <c r="R68" t="n">
-        <v>7122722</v>
+        <v>7122533</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7638,19 +7638,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7665,12 +7655,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7787,48 +7777,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126917799</v>
+        <v>126914197</v>
       </c>
       <c r="B70" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>656764</v>
+        <v>656647</v>
       </c>
       <c r="R70" t="n">
-        <v>7122303</v>
+        <v>7122722</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7855,9 +7845,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7872,12 +7872,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7888,45 +7888,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126915087</v>
+        <v>126916855</v>
       </c>
       <c r="B71" t="n">
-        <v>80150</v>
+        <v>78685</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>656629</v>
+        <v>656803</v>
       </c>
       <c r="R71" t="n">
-        <v>7122746</v>
+        <v>7122276</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7956,11 +7956,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7969,16 +7979,36 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallåga</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7989,10 +8019,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918448</v>
+        <v>126915087</v>
       </c>
       <c r="B72" t="n">
-        <v>80056</v>
+        <v>80150</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,37 +8030,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656939</v>
+        <v>656629</v>
       </c>
       <c r="R72" t="n">
-        <v>7122290</v>
+        <v>7122746</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8071,34 +8098,18 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8109,10 +8120,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126914184</v>
+        <v>126918448</v>
       </c>
       <c r="B73" t="n">
-        <v>80025</v>
+        <v>80056</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8120,37 +8131,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656943</v>
+        <v>656939</v>
       </c>
       <c r="R73" t="n">
-        <v>7122285</v>
+        <v>7122290</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8177,39 +8191,45 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8220,32 +8240,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126920135</v>
+        <v>126914184</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>80025</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8255,13 +8275,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656718</v>
+        <v>656943</v>
       </c>
       <c r="R74" t="n">
-        <v>7122587</v>
+        <v>7122285</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8288,9 +8308,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8305,12 +8335,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8321,10 +8351,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126916735</v>
+        <v>126916732</v>
       </c>
       <c r="B75" t="n">
-        <v>78777</v>
+        <v>57658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8332,34 +8362,38 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656861</v>
+        <v>656599</v>
       </c>
       <c r="R75" t="n">
-        <v>7122418</v>
+        <v>7122660</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8392,6 +8426,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8422,7 +8461,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916291</v>
+        <v>126916735</v>
       </c>
       <c r="B76" t="n">
         <v>78777</v>
@@ -8457,10 +8496,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656585</v>
+        <v>656861</v>
       </c>
       <c r="R76" t="n">
-        <v>7122741</v>
+        <v>7122418</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8507,12 +8546,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8523,7 +8562,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126915678</v>
+        <v>126916291</v>
       </c>
       <c r="B77" t="n">
         <v>78777</v>
@@ -8558,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656958</v>
+        <v>656585</v>
       </c>
       <c r="R77" t="n">
-        <v>7122264</v>
+        <v>7122741</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8608,12 +8647,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8624,10 +8663,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126916732</v>
+        <v>126915678</v>
       </c>
       <c r="B78" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8635,38 +8674,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656599</v>
+        <v>656958</v>
       </c>
       <c r="R78" t="n">
-        <v>7122660</v>
+        <v>7122264</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8701,11 +8736,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8718,12 +8748,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8734,32 +8764,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126916855</v>
+        <v>126920135</v>
       </c>
       <c r="B79" t="n">
-        <v>78685</v>
+        <v>98447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8769,10 +8799,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656803</v>
+        <v>656718</v>
       </c>
       <c r="R79" t="n">
-        <v>7122276</v>
+        <v>7122587</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8802,21 +8832,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8825,36 +8845,16 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>Gammal tallåga</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallåga</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -10622,10 +10622,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126915968</v>
+        <v>126918400</v>
       </c>
       <c r="B97" t="n">
-        <v>80121</v>
+        <v>79636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10633,21 +10633,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>656665</v>
+        <v>656591</v>
       </c>
       <c r="R97" t="n">
-        <v>7122588</v>
+        <v>7122782</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10707,12 +10707,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10723,45 +10723,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918006</v>
+        <v>126918456</v>
       </c>
       <c r="B98" t="n">
-        <v>79636</v>
+        <v>80156</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>656933</v>
+        <v>656761</v>
       </c>
       <c r="R98" t="n">
-        <v>7122272</v>
+        <v>7122534</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10807,28 +10807,28 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10839,7 +10839,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918017</v>
+        <v>126919780</v>
       </c>
       <c r="B99" t="n">
         <v>79636</v>
@@ -10870,14 +10870,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>656803</v>
+        <v>656724</v>
       </c>
       <c r="R99" t="n">
-        <v>7122418</v>
+        <v>7122461</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10921,30 +10921,15 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10955,10 +10940,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126914187</v>
+        <v>126915968</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10966,37 +10951,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>656898</v>
+        <v>656665</v>
       </c>
       <c r="R100" t="n">
-        <v>7122390</v>
+        <v>7122588</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11023,19 +11008,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11050,12 +11025,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11066,10 +11041,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915971</v>
+        <v>126918006</v>
       </c>
       <c r="B101" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11077,37 +11052,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>656619</v>
+        <v>656933</v>
       </c>
       <c r="R101" t="n">
-        <v>7122605</v>
+        <v>7122272</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11147,16 +11122,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11167,10 +11157,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126916307</v>
+        <v>126918017</v>
       </c>
       <c r="B102" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11178,34 +11168,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>656532</v>
+        <v>656803</v>
       </c>
       <c r="R102" t="n">
-        <v>7122751</v>
+        <v>7122418</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11249,15 +11239,30 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11268,10 +11273,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126918400</v>
+        <v>126914187</v>
       </c>
       <c r="B103" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11279,37 +11284,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>656591</v>
+        <v>656898</v>
       </c>
       <c r="R103" t="n">
-        <v>7122782</v>
+        <v>7122390</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11336,9 +11341,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11353,12 +11368,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11369,32 +11384,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126918456</v>
+        <v>126915971</v>
       </c>
       <c r="B104" t="n">
-        <v>80156</v>
+        <v>78776</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11404,13 +11419,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>656761</v>
+        <v>656619</v>
       </c>
       <c r="R104" t="n">
-        <v>7122534</v>
+        <v>7122605</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11450,31 +11465,16 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11485,32 +11485,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126919780</v>
+        <v>126918700</v>
       </c>
       <c r="B105" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>656724</v>
+        <v>656657</v>
       </c>
       <c r="R105" t="n">
-        <v>7122461</v>
+        <v>7122544</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11570,12 +11570,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11586,32 +11586,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126918700</v>
+        <v>126918408</v>
       </c>
       <c r="B106" t="n">
-        <v>98447</v>
+        <v>79607</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11621,10 +11621,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>656657</v>
+        <v>656757</v>
       </c>
       <c r="R106" t="n">
-        <v>7122544</v>
+        <v>7122638</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11671,12 +11671,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11687,10 +11687,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126918408</v>
+        <v>126915960</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11698,21 +11698,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11722,13 +11722,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>656757</v>
+        <v>656871</v>
       </c>
       <c r="R107" t="n">
-        <v>7122638</v>
+        <v>7122287</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11766,18 +11766,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11788,10 +11789,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126915960</v>
+        <v>126916307</v>
       </c>
       <c r="B108" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11799,21 +11800,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11823,13 +11824,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>656871</v>
+        <v>656532</v>
       </c>
       <c r="R108" t="n">
-        <v>7122287</v>
+        <v>7122751</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11867,19 +11868,18 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12951,10 +12951,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126918409</v>
+        <v>126920121</v>
       </c>
       <c r="B119" t="n">
-        <v>78685</v>
+        <v>57661</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12962,21 +12962,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12986,10 +12986,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>656757</v>
+        <v>656620</v>
       </c>
       <c r="R119" t="n">
-        <v>7122638</v>
+        <v>7122729</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13024,6 +13024,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Äldre hack på tall</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13036,12 +13041,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13052,10 +13057,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126917777</v>
+        <v>126918409</v>
       </c>
       <c r="B120" t="n">
-        <v>92813</v>
+        <v>78685</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13063,21 +13068,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13087,10 +13092,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>656802</v>
+        <v>656757</v>
       </c>
       <c r="R120" t="n">
-        <v>7122279</v>
+        <v>7122638</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13137,12 +13142,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13153,10 +13158,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126918005</v>
+        <v>126917777</v>
       </c>
       <c r="B121" t="n">
-        <v>79636</v>
+        <v>92813</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13164,34 +13169,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>656873</v>
+        <v>656802</v>
       </c>
       <c r="R121" t="n">
-        <v>7122259</v>
+        <v>7122279</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13235,30 +13240,15 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13269,45 +13259,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126919836</v>
+        <v>126918005</v>
       </c>
       <c r="B122" t="n">
-        <v>80156</v>
+        <v>79636</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>656698</v>
+        <v>656873</v>
       </c>
       <c r="R122" t="n">
-        <v>7122588</v>
+        <v>7122259</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13351,15 +13341,30 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13370,10 +13375,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126915958</v>
+        <v>126919836</v>
       </c>
       <c r="B123" t="n">
-        <v>80150</v>
+        <v>80156</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13381,21 +13386,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13405,13 +13410,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>656674</v>
+        <v>656698</v>
       </c>
       <c r="R123" t="n">
-        <v>7122583</v>
+        <v>7122588</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13455,12 +13460,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13471,7 +13476,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126919796</v>
+        <v>126915958</v>
       </c>
       <c r="B124" t="n">
         <v>80150</v>
@@ -13506,13 +13511,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>656716</v>
+        <v>656674</v>
       </c>
       <c r="R124" t="n">
-        <v>7122559</v>
+        <v>7122583</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13556,12 +13561,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13572,32 +13577,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126920121</v>
+        <v>126919796</v>
       </c>
       <c r="B125" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13607,10 +13612,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>656620</v>
+        <v>656716</v>
       </c>
       <c r="R125" t="n">
-        <v>7122729</v>
+        <v>7122559</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13645,11 +13650,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Äldre hack på tall</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13662,12 +13662,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -16902,48 +16902,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126916320</v>
+        <v>126914195</v>
       </c>
       <c r="B157" t="n">
-        <v>92620</v>
+        <v>78424</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>656843</v>
+        <v>656646</v>
       </c>
       <c r="R157" t="n">
-        <v>7122356</v>
+        <v>7122721</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16970,9 +16970,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16987,12 +16997,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17003,60 +17013,48 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126915954</v>
+        <v>126916728</v>
       </c>
       <c r="B158" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>656828</v>
+        <v>656908</v>
       </c>
       <c r="R158" t="n">
-        <v>7122387</v>
+        <v>7122278</v>
       </c>
       <c r="S158" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17100,12 +17098,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17116,10 +17114,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126914193</v>
+        <v>126916273</v>
       </c>
       <c r="B159" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17127,37 +17125,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>656723</v>
+        <v>656727</v>
       </c>
       <c r="R159" t="n">
-        <v>7122565</v>
+        <v>7122571</v>
       </c>
       <c r="S159" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17184,19 +17182,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17211,12 +17199,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17227,10 +17215,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126917795</v>
+        <v>126918028</v>
       </c>
       <c r="B160" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17238,34 +17226,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>656507</v>
+        <v>656576</v>
       </c>
       <c r="R160" t="n">
-        <v>7122604</v>
+        <v>7122734</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17309,15 +17297,30 @@
       <c r="AG160" t="b">
         <v>0</v>
       </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17328,45 +17331,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126915091</v>
+        <v>126916320</v>
       </c>
       <c r="B161" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>656836</v>
+        <v>656843</v>
       </c>
       <c r="R161" t="n">
-        <v>7122254</v>
+        <v>7122356</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17413,12 +17416,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17429,48 +17432,60 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126920131</v>
+        <v>126915954</v>
       </c>
       <c r="B162" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>656819</v>
+        <v>656828</v>
       </c>
       <c r="R162" t="n">
-        <v>7122264</v>
+        <v>7122387</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17500,11 +17515,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På kolad tallraka.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17519,12 +17529,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17535,10 +17545,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126916295</v>
+        <v>126914193</v>
       </c>
       <c r="B163" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17546,37 +17556,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>656824</v>
+        <v>656723</v>
       </c>
       <c r="R163" t="n">
-        <v>7122248</v>
+        <v>7122565</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17603,9 +17613,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17620,12 +17640,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17636,7 +17656,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126918022</v>
+        <v>126917795</v>
       </c>
       <c r="B164" t="n">
         <v>78777</v>
@@ -17667,14 +17687,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>656755</v>
+        <v>656507</v>
       </c>
       <c r="R164" t="n">
-        <v>7122605</v>
+        <v>7122604</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17718,30 +17738,15 @@
       <c r="AG164" t="b">
         <v>0</v>
       </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17752,7 +17757,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126917794</v>
+        <v>126915091</v>
       </c>
       <c r="B165" t="n">
         <v>78777</v>
@@ -17783,14 +17788,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>656498</v>
+        <v>656836</v>
       </c>
       <c r="R165" t="n">
-        <v>7122598</v>
+        <v>7122254</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17837,12 +17842,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17853,10 +17858,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126914195</v>
+        <v>126920131</v>
       </c>
       <c r="B166" t="n">
-        <v>78424</v>
+        <v>78777</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17864,37 +17869,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>656646</v>
+        <v>656819</v>
       </c>
       <c r="R166" t="n">
-        <v>7122721</v>
+        <v>7122264</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17921,19 +17926,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>12:43</t>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På kolad tallraka.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17948,12 +17948,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17964,10 +17964,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126916728</v>
+        <v>126916295</v>
       </c>
       <c r="B167" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17975,21 +17975,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17999,10 +17999,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>656908</v>
+        <v>656824</v>
       </c>
       <c r="R167" t="n">
-        <v>7122278</v>
+        <v>7122248</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18049,12 +18049,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -18065,10 +18065,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126916273</v>
+        <v>126918022</v>
       </c>
       <c r="B168" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18076,34 +18076,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>656727</v>
+        <v>656755</v>
       </c>
       <c r="R168" t="n">
-        <v>7122571</v>
+        <v>7122605</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18147,15 +18147,30 @@
       <c r="AG168" t="b">
         <v>0</v>
       </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18166,10 +18181,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126918028</v>
+        <v>126917794</v>
       </c>
       <c r="B169" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18177,34 +18192,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>656576</v>
+        <v>656498</v>
       </c>
       <c r="R169" t="n">
-        <v>7122734</v>
+        <v>7122598</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18248,30 +18263,15 @@
       <c r="AG169" t="b">
         <v>0</v>
       </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -19332,10 +19332,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126918008</v>
+        <v>126917796</v>
       </c>
       <c r="B180" t="n">
-        <v>80993</v>
+        <v>78777</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19343,34 +19343,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>656933</v>
+        <v>656580</v>
       </c>
       <c r="R180" t="n">
-        <v>7122272</v>
+        <v>7122596</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19414,30 +19414,15 @@
       <c r="AG180" t="b">
         <v>0</v>
       </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -19448,10 +19433,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>126919833</v>
+        <v>126916736</v>
       </c>
       <c r="B181" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19459,21 +19444,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19483,10 +19468,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>656555</v>
+        <v>656871</v>
       </c>
       <c r="R181" t="n">
-        <v>7122664</v>
+        <v>7122392</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19521,6 +19506,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>På kolad kärnved, högstubbe</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
@@ -19533,12 +19523,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -19549,48 +19539,48 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126918441</v>
+        <v>126914188</v>
       </c>
       <c r="B182" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>656596</v>
+        <v>656907</v>
       </c>
       <c r="R182" t="n">
-        <v>7122771</v>
+        <v>7122416</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19617,11 +19607,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
@@ -19630,31 +19630,16 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19665,10 +19650,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126918015</v>
+        <v>126918008</v>
       </c>
       <c r="B183" t="n">
-        <v>92813</v>
+        <v>80993</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19676,21 +19661,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19700,10 +19685,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>656884</v>
+        <v>656933</v>
       </c>
       <c r="R183" t="n">
-        <v>7122406</v>
+        <v>7122272</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20301,10 +20286,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126917796</v>
+        <v>126919833</v>
       </c>
       <c r="B189" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20312,21 +20297,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20336,10 +20321,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>656580</v>
+        <v>656555</v>
       </c>
       <c r="R189" t="n">
-        <v>7122596</v>
+        <v>7122664</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20386,12 +20371,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -20402,10 +20387,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126916736</v>
+        <v>126918015</v>
       </c>
       <c r="B190" t="n">
-        <v>78777</v>
+        <v>92813</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20413,34 +20398,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>656871</v>
+        <v>656884</v>
       </c>
       <c r="R190" t="n">
-        <v>7122392</v>
+        <v>7122406</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20475,11 +20460,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>På kolad kärnved, högstubbe</t>
-        </is>
-      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20488,16 +20468,31 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20508,48 +20503,48 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126914188</v>
+        <v>126918441</v>
       </c>
       <c r="B191" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>656907</v>
+        <v>656596</v>
       </c>
       <c r="R191" t="n">
-        <v>7122416</v>
+        <v>7122771</v>
       </c>
       <c r="S191" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20576,21 +20571,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
@@ -20599,16 +20584,31 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20829,10 +20829,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918411</v>
+        <v>126918653</v>
       </c>
       <c r="B194" t="n">
-        <v>79607</v>
+        <v>80122</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20840,21 +20840,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20864,10 +20864,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>656974</v>
+        <v>656729</v>
       </c>
       <c r="R194" t="n">
-        <v>7122390</v>
+        <v>7122537</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20914,12 +20914,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20930,48 +20930,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126918099</v>
+        <v>126916318</v>
       </c>
       <c r="B195" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>656966</v>
+        <v>656775</v>
       </c>
       <c r="R195" t="n">
-        <v>7122301</v>
+        <v>7122386</v>
       </c>
       <c r="S195" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21015,12 +21015,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21031,10 +21031,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126918653</v>
+        <v>126918103</v>
       </c>
       <c r="B196" t="n">
-        <v>80122</v>
+        <v>80993</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21042,37 +21042,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2081</v>
+        <v>1049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>656729</v>
+        <v>656889</v>
       </c>
       <c r="R196" t="n">
-        <v>7122537</v>
+        <v>7122426</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21110,18 +21110,19 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -21132,48 +21133,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126916318</v>
+        <v>126914189</v>
       </c>
       <c r="B197" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>656775</v>
+        <v>656908</v>
       </c>
       <c r="R197" t="n">
-        <v>7122386</v>
+        <v>7122416</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21200,9 +21201,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21217,12 +21228,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21233,10 +21244,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126918103</v>
+        <v>126918030</v>
       </c>
       <c r="B198" t="n">
-        <v>80993</v>
+        <v>78424</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21244,37 +21255,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>656889</v>
+        <v>656564</v>
       </c>
       <c r="R198" t="n">
-        <v>7122426</v>
+        <v>7122730</v>
       </c>
       <c r="S198" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21312,19 +21323,33 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21335,10 +21360,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126914189</v>
+        <v>126919817</v>
       </c>
       <c r="B199" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21346,37 +21371,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>656908</v>
+        <v>656807</v>
       </c>
       <c r="R199" t="n">
-        <v>7122416</v>
+        <v>7122335</v>
       </c>
       <c r="S199" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21403,19 +21428,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21430,12 +21445,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21446,10 +21461,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126918030</v>
+        <v>126918411</v>
       </c>
       <c r="B200" t="n">
-        <v>78424</v>
+        <v>79607</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21457,34 +21472,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>656564</v>
+        <v>656974</v>
       </c>
       <c r="R200" t="n">
-        <v>7122730</v>
+        <v>7122390</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21528,30 +21543,15 @@
       <c r="AG200" t="b">
         <v>0</v>
       </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21562,10 +21562,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126919817</v>
+        <v>126918099</v>
       </c>
       <c r="B201" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21573,37 +21573,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>656807</v>
+        <v>656966</v>
       </c>
       <c r="R201" t="n">
-        <v>7122335</v>
+        <v>7122301</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21647,12 +21647,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126920134</v>
+        <v>126918642</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656826</v>
+        <v>656705</v>
       </c>
       <c r="R3" t="n">
-        <v>7122263</v>
+        <v>7122438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,6 +849,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -861,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917810</v>
+        <v>126920138</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656710</v>
+        <v>656779</v>
       </c>
       <c r="R4" t="n">
-        <v>7122344</v>
+        <v>7122366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +967,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126920132</v>
+        <v>126920134</v>
       </c>
       <c r="B5" t="n">
         <v>78776</v>
@@ -1013,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656728</v>
+        <v>656826</v>
       </c>
       <c r="R5" t="n">
-        <v>7122652</v>
+        <v>7122263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126920138</v>
+        <v>126917810</v>
       </c>
       <c r="B6" t="n">
-        <v>78685</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656779</v>
+        <v>656710</v>
       </c>
       <c r="R6" t="n">
-        <v>7122366</v>
+        <v>7122344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1169,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126918642</v>
+        <v>126920132</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>78776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656705</v>
+        <v>656728</v>
       </c>
       <c r="R7" t="n">
-        <v>7122438</v>
+        <v>7122652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,11 +1258,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1270,12 +1270,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2763,32 +2763,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126918020</v>
+        <v>126918025</v>
       </c>
       <c r="B22" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
         <v>656722</v>
       </c>
       <c r="R22" t="n">
-        <v>7122528</v>
+        <v>7122706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2844,21 +2844,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2879,45 +2864,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918025</v>
+        <v>126917768</v>
       </c>
       <c r="B23" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656722</v>
+        <v>656842</v>
       </c>
       <c r="R23" t="n">
-        <v>7122706</v>
+        <v>7122270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,12 +2949,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2980,7 +2965,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917768</v>
+        <v>126917766</v>
       </c>
       <c r="B24" t="n">
         <v>79636</v>
@@ -3015,10 +3000,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656842</v>
+        <v>656527</v>
       </c>
       <c r="R24" t="n">
-        <v>7122270</v>
+        <v>7122602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917766</v>
+        <v>126916302</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656527</v>
+        <v>656815</v>
       </c>
       <c r="R25" t="n">
-        <v>7122602</v>
+        <v>7122359</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3166,12 +3151,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3182,10 +3167,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126916302</v>
+        <v>126918659</v>
       </c>
       <c r="B26" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,21 +3178,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3202,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>656815</v>
+        <v>656834</v>
       </c>
       <c r="R26" t="n">
-        <v>7122359</v>
+        <v>7122225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,6 +3240,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3267,12 +3257,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3283,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918659</v>
+        <v>126918662</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,21 +3284,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656834</v>
+        <v>656760</v>
       </c>
       <c r="R27" t="n">
-        <v>7122225</v>
+        <v>7122309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,11 +3344,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,7 +3374,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918662</v>
+        <v>126920129</v>
       </c>
       <c r="B28" t="n">
         <v>78777</v>
@@ -3424,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656760</v>
+        <v>656727</v>
       </c>
       <c r="R28" t="n">
-        <v>7122309</v>
+        <v>7122637</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,12 +3459,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3490,45 +3475,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126920129</v>
+        <v>126918695</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656727</v>
+        <v>656654</v>
       </c>
       <c r="R29" t="n">
-        <v>7122637</v>
+        <v>7122550</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,18 +3566,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3591,7 +3589,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918695</v>
+        <v>126918701</v>
       </c>
       <c r="B30" t="n">
         <v>98447</v>
@@ -3619,29 +3617,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656654</v>
+        <v>656649</v>
       </c>
       <c r="R30" t="n">
-        <v>7122550</v>
+        <v>7122554</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,7 +3668,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3705,45 +3690,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918701</v>
+        <v>126918020</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>92813</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656649</v>
+        <v>656722</v>
       </c>
       <c r="R31" t="n">
-        <v>7122554</v>
+        <v>7122528</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,15 +3772,30 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126919828</v>
+        <v>126916309</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656650</v>
+        <v>656627</v>
       </c>
       <c r="R32" t="n">
-        <v>7122658</v>
+        <v>7122696</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126917826</v>
+        <v>126919828</v>
       </c>
       <c r="B33" t="n">
-        <v>77996</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>656423</v>
+        <v>656650</v>
       </c>
       <c r="R33" t="n">
-        <v>7122703</v>
+        <v>7122658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,32 +4008,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918652</v>
+        <v>126917826</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>77996</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>656722</v>
+        <v>656423</v>
       </c>
       <c r="R34" t="n">
-        <v>7122539</v>
+        <v>7122703</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,32 +4109,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126919815</v>
+        <v>126918652</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>656787</v>
+        <v>656722</v>
       </c>
       <c r="R35" t="n">
-        <v>7122330</v>
+        <v>7122539</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,11 +4182,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4199,12 +4194,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4215,10 +4210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126914183</v>
+        <v>126919815</v>
       </c>
       <c r="B36" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4226,21 +4221,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4250,13 +4245,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>656891</v>
+        <v>656787</v>
       </c>
       <c r="R36" t="n">
-        <v>7122271</v>
+        <v>7122330</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4283,19 +4278,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:43</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Liten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4310,12 +4300,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4326,10 +4316,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126916309</v>
+        <v>126914183</v>
       </c>
       <c r="B37" t="n">
-        <v>78685</v>
+        <v>78776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4337,21 +4327,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4361,13 +4351,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>656627</v>
+        <v>656891</v>
       </c>
       <c r="R37" t="n">
-        <v>7122696</v>
+        <v>7122271</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4394,9 +4384,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4411,12 +4411,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918031</v>
+        <v>126916279</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,34 +4640,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>656542</v>
+        <v>656878</v>
       </c>
       <c r="R40" t="n">
-        <v>7122741</v>
+        <v>7122337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4702,6 +4710,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4710,31 +4723,16 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4745,10 +4743,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126917816</v>
+        <v>126918031</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4756,34 +4754,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656764</v>
+        <v>656542</v>
       </c>
       <c r="R41" t="n">
-        <v>7122303</v>
+        <v>7122741</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4827,15 +4825,30 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4846,7 +4859,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126920133</v>
+        <v>126917816</v>
       </c>
       <c r="B42" t="n">
         <v>78776</v>
@@ -4881,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656724</v>
+        <v>656764</v>
       </c>
       <c r="R42" t="n">
-        <v>7122581</v>
+        <v>7122303</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4931,12 +4944,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4947,10 +4960,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126915092</v>
+        <v>126920133</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4958,34 +4971,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656867</v>
+        <v>656724</v>
       </c>
       <c r="R43" t="n">
-        <v>7122430</v>
+        <v>7122581</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5032,12 +5045,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5048,7 +5061,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126915679</v>
+        <v>126915092</v>
       </c>
       <c r="B44" t="n">
         <v>80121</v>
@@ -5079,14 +5092,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656688</v>
+        <v>656867</v>
       </c>
       <c r="R44" t="n">
-        <v>7122595</v>
+        <v>7122430</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5133,12 +5146,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5149,7 +5162,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126905646</v>
+        <v>126915679</v>
       </c>
       <c r="B45" t="n">
         <v>80121</v>
@@ -5180,14 +5193,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656789</v>
+        <v>656688</v>
       </c>
       <c r="R45" t="n">
-        <v>7122441</v>
+        <v>7122595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5234,12 +5247,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5250,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126916279</v>
+        <v>126905646</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5261,42 +5274,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656878</v>
+        <v>656789</v>
       </c>
       <c r="R46" t="n">
-        <v>7122337</v>
+        <v>7122441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5331,11 +5336,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5480,32 +5480,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126915676</v>
+        <v>126919798</v>
       </c>
       <c r="B48" t="n">
-        <v>78777</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>656642</v>
+        <v>656706</v>
       </c>
       <c r="R48" t="n">
-        <v>7122633</v>
+        <v>7122542</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,6 +5553,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På mossbelupen liggande sälg</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5565,12 +5570,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5581,10 +5586,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126918440</v>
+        <v>126918431</v>
       </c>
       <c r="B49" t="n">
-        <v>78777</v>
+        <v>78424</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5592,21 +5597,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5616,10 +5621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>656962</v>
+        <v>656876</v>
       </c>
       <c r="R49" t="n">
-        <v>7122294</v>
+        <v>7122472</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5682,32 +5687,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919798</v>
+        <v>126918445</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>41365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>215713</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5717,10 +5722,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>656706</v>
+        <v>656978</v>
       </c>
       <c r="R50" t="n">
-        <v>7122542</v>
+        <v>7122381</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5755,11 +5760,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På mossbelupen liggande sälg</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5772,12 +5772,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5788,10 +5788,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126918431</v>
+        <v>126915676</v>
       </c>
       <c r="B51" t="n">
-        <v>78424</v>
+        <v>78777</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,21 +5799,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>656876</v>
+        <v>656642</v>
       </c>
       <c r="R51" t="n">
-        <v>7122472</v>
+        <v>7122633</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5873,12 +5873,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5889,10 +5889,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126918445</v>
+        <v>126918440</v>
       </c>
       <c r="B52" t="n">
-        <v>41365</v>
+        <v>78777</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5900,21 +5900,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>215713</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5924,10 +5924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>656978</v>
+        <v>656962</v>
       </c>
       <c r="R52" t="n">
-        <v>7122381</v>
+        <v>7122294</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,48 +5990,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126916389</v>
+        <v>126915093</v>
       </c>
       <c r="B53" t="n">
-        <v>92813</v>
+        <v>57765</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>656885</v>
+        <v>656892</v>
       </c>
       <c r="R53" t="n">
-        <v>7122464</v>
+        <v>7122431</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6075,12 +6075,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6091,10 +6091,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126918096</v>
+        <v>126916389</v>
       </c>
       <c r="B54" t="n">
-        <v>80122</v>
+        <v>92813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6102,37 +6102,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>656703</v>
+        <v>656885</v>
       </c>
       <c r="R54" t="n">
-        <v>7122538</v>
+        <v>7122464</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6176,12 +6176,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915094</v>
+        <v>126918096</v>
       </c>
       <c r="B55" t="n">
-        <v>78685</v>
+        <v>80122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6203,37 +6203,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>656850</v>
+        <v>656703</v>
       </c>
       <c r="R55" t="n">
-        <v>7122254</v>
+        <v>7122538</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6277,12 +6277,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6293,10 +6293,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919826</v>
+        <v>126915094</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6304,34 +6304,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>656575</v>
+        <v>656850</v>
       </c>
       <c r="R56" t="n">
-        <v>7122664</v>
+        <v>7122254</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6378,12 +6378,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6394,10 +6394,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126918021</v>
+        <v>126919826</v>
       </c>
       <c r="B57" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6405,34 +6405,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>656754</v>
+        <v>656575</v>
       </c>
       <c r="R57" t="n">
-        <v>7122604</v>
+        <v>7122664</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6476,30 +6476,15 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6510,45 +6495,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126918417</v>
+        <v>126918021</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>78776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>656750</v>
+        <v>656754</v>
       </c>
       <c r="R58" t="n">
-        <v>7122529</v>
+        <v>7122604</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6594,28 +6579,28 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6626,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126917776</v>
+        <v>126918417</v>
       </c>
       <c r="B59" t="n">
-        <v>79042</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6637,21 +6622,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6661,10 +6646,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656736</v>
+        <v>656750</v>
       </c>
       <c r="R59" t="n">
-        <v>7122322</v>
+        <v>7122529</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6708,15 +6693,30 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6727,32 +6727,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126916301</v>
+        <v>126917776</v>
       </c>
       <c r="B60" t="n">
-        <v>78776</v>
+        <v>79042</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656717</v>
+        <v>656736</v>
       </c>
       <c r="R60" t="n">
-        <v>7122549</v>
+        <v>7122322</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6812,12 +6812,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6828,7 +6828,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918694</v>
+        <v>126916301</v>
       </c>
       <c r="B61" t="n">
         <v>78776</v>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656559</v>
+        <v>656717</v>
       </c>
       <c r="R61" t="n">
-        <v>7122606</v>
+        <v>7122549</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6913,12 +6913,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6929,10 +6929,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126919830</v>
+        <v>126918694</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656689</v>
+        <v>656559</v>
       </c>
       <c r="R62" t="n">
-        <v>7122578</v>
+        <v>7122606</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7002,11 +7002,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7019,12 +7014,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7035,10 +7030,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126916850</v>
+        <v>126919830</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7046,21 +7041,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656628</v>
+        <v>656689</v>
       </c>
       <c r="R63" t="n">
-        <v>7122610</v>
+        <v>7122578</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7103,19 +7098,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:33</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7126,36 +7116,16 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Brandhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Brandhögstubbe</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7166,45 +7136,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126915093</v>
+        <v>126916850</v>
       </c>
       <c r="B64" t="n">
-        <v>57765</v>
+        <v>78776</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656892</v>
+        <v>656628</v>
       </c>
       <c r="R64" t="n">
-        <v>7122431</v>
+        <v>7122610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7234,11 +7204,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7247,16 +7227,36 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Brandhögstubbe</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7267,10 +7267,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126917799</v>
+        <v>126918403</v>
       </c>
       <c r="B65" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7278,21 +7278,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656764</v>
+        <v>656749</v>
       </c>
       <c r="R65" t="n">
-        <v>7122303</v>
+        <v>7122643</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7352,12 +7352,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918403</v>
+        <v>126917775</v>
       </c>
       <c r="B66" t="n">
-        <v>79636</v>
+        <v>79042</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656749</v>
+        <v>656581</v>
       </c>
       <c r="R66" t="n">
-        <v>7122643</v>
+        <v>7122603</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7453,12 +7453,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7469,10 +7469,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917775</v>
+        <v>126919837</v>
       </c>
       <c r="B67" t="n">
-        <v>79042</v>
+        <v>80156</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7480,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656581</v>
+        <v>656726</v>
       </c>
       <c r="R67" t="n">
-        <v>7122603</v>
+        <v>7122533</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7554,12 +7554,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7570,10 +7570,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126919837</v>
+        <v>126914197</v>
       </c>
       <c r="B68" t="n">
-        <v>80156</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,37 +7581,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656726</v>
+        <v>656647</v>
       </c>
       <c r="R68" t="n">
-        <v>7122533</v>
+        <v>7122722</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7638,9 +7638,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7655,12 +7665,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7777,48 +7787,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126914197</v>
+        <v>126917799</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>656647</v>
+        <v>656764</v>
       </c>
       <c r="R70" t="n">
-        <v>7122722</v>
+        <v>7122303</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7845,19 +7855,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7872,12 +7872,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7888,32 +7888,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126916855</v>
+        <v>126920135</v>
       </c>
       <c r="B71" t="n">
-        <v>78685</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>656803</v>
+        <v>656718</v>
       </c>
       <c r="R71" t="n">
-        <v>7122276</v>
+        <v>7122587</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7956,21 +7956,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7979,36 +7969,16 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Gammal tallåga</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallåga</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8019,45 +7989,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126915087</v>
+        <v>126916855</v>
       </c>
       <c r="B72" t="n">
-        <v>80150</v>
+        <v>78685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656629</v>
+        <v>656803</v>
       </c>
       <c r="R72" t="n">
-        <v>7122746</v>
+        <v>7122276</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8087,11 +8057,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8100,16 +8080,36 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallåga</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8120,10 +8120,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126918448</v>
+        <v>126915087</v>
       </c>
       <c r="B73" t="n">
-        <v>80056</v>
+        <v>80150</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,37 +8131,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656939</v>
+        <v>656629</v>
       </c>
       <c r="R73" t="n">
-        <v>7122290</v>
+        <v>7122746</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8202,34 +8199,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8240,10 +8221,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126914184</v>
+        <v>126918448</v>
       </c>
       <c r="B74" t="n">
-        <v>80025</v>
+        <v>80056</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8251,37 +8232,40 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656943</v>
+        <v>656939</v>
       </c>
       <c r="R74" t="n">
-        <v>7122285</v>
+        <v>7122290</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8308,39 +8292,45 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8351,52 +8341,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126916732</v>
+        <v>126914184</v>
       </c>
       <c r="B75" t="n">
-        <v>57658</v>
+        <v>80025</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656599</v>
+        <v>656943</v>
       </c>
       <c r="R75" t="n">
-        <v>7122660</v>
+        <v>7122285</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8423,14 +8409,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8445,12 +8436,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8461,10 +8452,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126916735</v>
+        <v>126916732</v>
       </c>
       <c r="B76" t="n">
-        <v>78777</v>
+        <v>57658</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8472,34 +8463,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656861</v>
+        <v>656599</v>
       </c>
       <c r="R76" t="n">
-        <v>7122418</v>
+        <v>7122660</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8532,6 +8527,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8562,7 +8562,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126916291</v>
+        <v>126916735</v>
       </c>
       <c r="B77" t="n">
         <v>78777</v>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656585</v>
+        <v>656861</v>
       </c>
       <c r="R77" t="n">
-        <v>7122741</v>
+        <v>7122418</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8647,12 +8647,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8663,7 +8663,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126915678</v>
+        <v>126916291</v>
       </c>
       <c r="B78" t="n">
         <v>78777</v>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656958</v>
+        <v>656585</v>
       </c>
       <c r="R78" t="n">
-        <v>7122264</v>
+        <v>7122741</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8748,12 +8748,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8764,32 +8764,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126920135</v>
+        <v>126915678</v>
       </c>
       <c r="B79" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656718</v>
+        <v>656958</v>
       </c>
       <c r="R79" t="n">
-        <v>7122587</v>
+        <v>7122264</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8849,12 +8849,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -16902,48 +16902,48 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126914195</v>
+        <v>126916320</v>
       </c>
       <c r="B157" t="n">
-        <v>78424</v>
+        <v>92620</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>656646</v>
+        <v>656843</v>
       </c>
       <c r="R157" t="n">
-        <v>7122721</v>
+        <v>7122356</v>
       </c>
       <c r="S157" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16970,19 +16970,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16997,12 +16987,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17013,48 +17003,60 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126916728</v>
+        <v>126915954</v>
       </c>
       <c r="B158" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>656908</v>
+        <v>656828</v>
       </c>
       <c r="R158" t="n">
-        <v>7122278</v>
+        <v>7122387</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17098,12 +17100,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17114,10 +17116,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126916273</v>
+        <v>126914193</v>
       </c>
       <c r="B159" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17125,37 +17127,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>656727</v>
+        <v>656723</v>
       </c>
       <c r="R159" t="n">
-        <v>7122571</v>
+        <v>7122565</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17182,9 +17184,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17199,12 +17211,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17215,10 +17227,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126918028</v>
+        <v>126917795</v>
       </c>
       <c r="B160" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17226,34 +17238,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>656576</v>
+        <v>656507</v>
       </c>
       <c r="R160" t="n">
-        <v>7122734</v>
+        <v>7122604</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17297,30 +17309,15 @@
       <c r="AG160" t="b">
         <v>0</v>
       </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17331,45 +17328,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126916320</v>
+        <v>126915091</v>
       </c>
       <c r="B161" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>656843</v>
+        <v>656836</v>
       </c>
       <c r="R161" t="n">
-        <v>7122356</v>
+        <v>7122254</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17416,12 +17413,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17432,60 +17429,48 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126915954</v>
+        <v>126920131</v>
       </c>
       <c r="B162" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>656828</v>
+        <v>656819</v>
       </c>
       <c r="R162" t="n">
-        <v>7122387</v>
+        <v>7122264</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17515,6 +17500,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>På kolad tallraka.</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17529,12 +17519,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17545,10 +17535,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126914193</v>
+        <v>126916295</v>
       </c>
       <c r="B163" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17556,37 +17546,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>656723</v>
+        <v>656824</v>
       </c>
       <c r="R163" t="n">
-        <v>7122565</v>
+        <v>7122248</v>
       </c>
       <c r="S163" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17613,19 +17603,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17640,12 +17620,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17656,7 +17636,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126917795</v>
+        <v>126918022</v>
       </c>
       <c r="B164" t="n">
         <v>78777</v>
@@ -17687,14 +17667,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>656507</v>
+        <v>656755</v>
       </c>
       <c r="R164" t="n">
-        <v>7122604</v>
+        <v>7122605</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17738,15 +17718,30 @@
       <c r="AG164" t="b">
         <v>0</v>
       </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17757,7 +17752,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126915091</v>
+        <v>126917794</v>
       </c>
       <c r="B165" t="n">
         <v>78777</v>
@@ -17788,14 +17783,14 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>656836</v>
+        <v>656498</v>
       </c>
       <c r="R165" t="n">
-        <v>7122254</v>
+        <v>7122598</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17842,12 +17837,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17858,10 +17853,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126920131</v>
+        <v>126914195</v>
       </c>
       <c r="B166" t="n">
-        <v>78777</v>
+        <v>78424</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17869,37 +17864,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>656819</v>
+        <v>656646</v>
       </c>
       <c r="R166" t="n">
-        <v>7122264</v>
+        <v>7122721</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17926,14 +17921,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>På kolad tallraka.</t>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17948,12 +17948,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17964,10 +17964,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126916295</v>
+        <v>126916728</v>
       </c>
       <c r="B167" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17975,21 +17975,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17999,10 +17999,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>656824</v>
+        <v>656908</v>
       </c>
       <c r="R167" t="n">
-        <v>7122248</v>
+        <v>7122278</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18049,12 +18049,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -18065,10 +18065,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126918022</v>
+        <v>126916273</v>
       </c>
       <c r="B168" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18076,34 +18076,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>656755</v>
+        <v>656727</v>
       </c>
       <c r="R168" t="n">
-        <v>7122605</v>
+        <v>7122571</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18147,30 +18147,15 @@
       <c r="AG168" t="b">
         <v>0</v>
       </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18181,10 +18166,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126917794</v>
+        <v>126918028</v>
       </c>
       <c r="B169" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18192,34 +18177,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>656498</v>
+        <v>656576</v>
       </c>
       <c r="R169" t="n">
-        <v>7122598</v>
+        <v>7122734</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18263,15 +18248,30 @@
       <c r="AG169" t="b">
         <v>0</v>
       </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -20829,10 +20829,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918653</v>
+        <v>126918411</v>
       </c>
       <c r="B194" t="n">
-        <v>80122</v>
+        <v>79607</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20840,21 +20840,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20864,10 +20864,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>656729</v>
+        <v>656974</v>
       </c>
       <c r="R194" t="n">
-        <v>7122537</v>
+        <v>7122390</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20914,12 +20914,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20930,48 +20930,48 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126916318</v>
+        <v>126918099</v>
       </c>
       <c r="B195" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>656775</v>
+        <v>656966</v>
       </c>
       <c r="R195" t="n">
-        <v>7122386</v>
+        <v>7122301</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21015,12 +21015,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21031,10 +21031,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126918103</v>
+        <v>126918653</v>
       </c>
       <c r="B196" t="n">
-        <v>80993</v>
+        <v>80122</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21042,37 +21042,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1049</v>
+        <v>2081</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>656889</v>
+        <v>656729</v>
       </c>
       <c r="R196" t="n">
-        <v>7122426</v>
+        <v>7122537</v>
       </c>
       <c r="S196" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21110,19 +21110,18 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -21133,48 +21132,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126914189</v>
+        <v>126916318</v>
       </c>
       <c r="B197" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>656908</v>
+        <v>656775</v>
       </c>
       <c r="R197" t="n">
-        <v>7122416</v>
+        <v>7122386</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21201,19 +21200,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21228,12 +21217,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21244,10 +21233,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126918030</v>
+        <v>126918103</v>
       </c>
       <c r="B198" t="n">
-        <v>78424</v>
+        <v>80993</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21255,37 +21244,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>656564</v>
+        <v>656889</v>
       </c>
       <c r="R198" t="n">
-        <v>7122730</v>
+        <v>7122426</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21323,33 +21312,19 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO198" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21360,10 +21335,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126919817</v>
+        <v>126914189</v>
       </c>
       <c r="B199" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21371,37 +21346,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>656807</v>
+        <v>656908</v>
       </c>
       <c r="R199" t="n">
-        <v>7122335</v>
+        <v>7122416</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21428,9 +21403,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21445,12 +21430,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21461,10 +21446,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126918411</v>
+        <v>126918030</v>
       </c>
       <c r="B200" t="n">
-        <v>79607</v>
+        <v>78424</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21472,34 +21457,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>656974</v>
+        <v>656564</v>
       </c>
       <c r="R200" t="n">
-        <v>7122390</v>
+        <v>7122730</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21543,15 +21528,30 @@
       <c r="AG200" t="b">
         <v>0</v>
       </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21562,10 +21562,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126918099</v>
+        <v>126919817</v>
       </c>
       <c r="B201" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21573,37 +21573,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>656966</v>
+        <v>656807</v>
       </c>
       <c r="R201" t="n">
-        <v>7122301</v>
+        <v>7122335</v>
       </c>
       <c r="S201" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21647,12 +21647,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -1791,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918442</v>
+        <v>126918453</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656598</v>
+        <v>656917</v>
       </c>
       <c r="R13" t="n">
-        <v>7122760</v>
+        <v>7122456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,21 +1872,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1907,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918453</v>
+        <v>126916383</v>
       </c>
       <c r="B14" t="n">
-        <v>92620</v>
+        <v>91295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,13 +1927,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656917</v>
+        <v>656948</v>
       </c>
       <c r="R14" t="n">
-        <v>7122456</v>
+        <v>7122441</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,12 +1977,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2008,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916383</v>
+        <v>126918442</v>
       </c>
       <c r="B15" t="n">
-        <v>91295</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2019,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2043,13 +2028,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656948</v>
+        <v>656598</v>
       </c>
       <c r="R15" t="n">
-        <v>7122441</v>
+        <v>7122760</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,16 +2074,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126915952</v>
+        <v>126917832</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>78424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,45 +2236,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656836</v>
+        <v>656438</v>
       </c>
       <c r="R17" t="n">
-        <v>7122343</v>
+        <v>7122610</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2318,12 +2310,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2334,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918641</v>
+        <v>126914186</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>78776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2345,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2369,13 +2361,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656495</v>
+        <v>656923</v>
       </c>
       <c r="R18" t="n">
-        <v>7122596</v>
+        <v>7122382</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2402,14 +2394,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,12 +2421,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2440,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126917832</v>
+        <v>126914182</v>
       </c>
       <c r="B19" t="n">
-        <v>78424</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,13 +2472,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656438</v>
+        <v>656885</v>
       </c>
       <c r="R19" t="n">
-        <v>7122610</v>
+        <v>7122248</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2508,9 +2505,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,12 +2532,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2541,10 +2548,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126914186</v>
+        <v>126915952</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,37 +2559,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656923</v>
+        <v>656836</v>
       </c>
       <c r="R20" t="n">
-        <v>7122382</v>
+        <v>7122343</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,19 +2624,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,12 +2641,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2652,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126914182</v>
+        <v>126918641</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,21 +2668,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,13 +2692,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656885</v>
+        <v>656495</v>
       </c>
       <c r="R21" t="n">
-        <v>7122248</v>
+        <v>7122596</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,19 +2725,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:41</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,12 +2747,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2763,45 +2763,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126918025</v>
+        <v>126917766</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656722</v>
+        <v>656527</v>
       </c>
       <c r="R22" t="n">
-        <v>7122706</v>
+        <v>7122602</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,12 +2848,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2864,10 +2864,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918020</v>
+        <v>126916302</v>
       </c>
       <c r="B23" t="n">
-        <v>92813</v>
+        <v>78776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,34 +2875,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656722</v>
+        <v>656815</v>
       </c>
       <c r="R23" t="n">
-        <v>7122528</v>
+        <v>7122359</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2946,30 +2946,15 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2980,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917768</v>
+        <v>126918659</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,21 +2976,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3015,10 +3000,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656842</v>
+        <v>656834</v>
       </c>
       <c r="R24" t="n">
-        <v>7122270</v>
+        <v>7122225</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3053,6 +3038,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3065,12 +3055,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3081,45 +3071,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917766</v>
+        <v>126918695</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656527</v>
+        <v>656654</v>
       </c>
       <c r="R25" t="n">
-        <v>7122602</v>
+        <v>7122550</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3160,18 +3162,19 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3182,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126916302</v>
+        <v>126918662</v>
       </c>
       <c r="B26" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,21 +3196,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3217,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>656815</v>
+        <v>656760</v>
       </c>
       <c r="R26" t="n">
-        <v>7122359</v>
+        <v>7122309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3267,12 +3270,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3283,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918659</v>
+        <v>126920129</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,21 +3297,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656834</v>
+        <v>656727</v>
       </c>
       <c r="R27" t="n">
-        <v>7122225</v>
+        <v>7122637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,11 +3359,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3373,12 +3371,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3389,57 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918695</v>
+        <v>126918025</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656654</v>
+        <v>656722</v>
       </c>
       <c r="R28" t="n">
-        <v>7122550</v>
+        <v>7122706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,19 +3466,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3503,45 +3488,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918701</v>
+        <v>126918020</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>92813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656649</v>
+        <v>656722</v>
       </c>
       <c r="R29" t="n">
-        <v>7122554</v>
+        <v>7122528</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,15 +3570,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918662</v>
+        <v>126917768</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656760</v>
+        <v>656842</v>
       </c>
       <c r="R30" t="n">
-        <v>7122309</v>
+        <v>7122270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,12 +3689,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3705,32 +3705,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126920129</v>
+        <v>126918701</v>
       </c>
       <c r="B31" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656727</v>
+        <v>656649</v>
       </c>
       <c r="R31" t="n">
-        <v>7122637</v>
+        <v>7122554</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,12 +3790,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126916309</v>
+        <v>126917826</v>
       </c>
       <c r="B33" t="n">
-        <v>78685</v>
+        <v>77996</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>656627</v>
+        <v>656423</v>
       </c>
       <c r="R33" t="n">
-        <v>7122696</v>
+        <v>7122703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,12 +3992,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4008,32 +4008,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126917826</v>
+        <v>126918652</v>
       </c>
       <c r="B34" t="n">
-        <v>77996</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>656423</v>
+        <v>656722</v>
       </c>
       <c r="R34" t="n">
-        <v>7122703</v>
+        <v>7122539</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4093,12 +4093,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4109,32 +4109,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126918652</v>
+        <v>126919815</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>656722</v>
+        <v>656787</v>
       </c>
       <c r="R35" t="n">
-        <v>7122539</v>
+        <v>7122330</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,6 +4182,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Liten</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4194,12 +4199,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4210,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919815</v>
+        <v>126916309</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>78685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4221,21 +4226,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4245,10 +4250,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>656787</v>
+        <v>656627</v>
       </c>
       <c r="R36" t="n">
-        <v>7122330</v>
+        <v>7122696</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4283,11 +4288,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Liten</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4300,12 +4300,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918031</v>
+        <v>126915092</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,34 +4640,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>656542</v>
+        <v>656867</v>
       </c>
       <c r="R40" t="n">
-        <v>7122741</v>
+        <v>7122430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,30 +4711,15 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4745,10 +4730,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126917816</v>
+        <v>126915679</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4756,21 +4741,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4780,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>656764</v>
+        <v>656688</v>
       </c>
       <c r="R41" t="n">
-        <v>7122303</v>
+        <v>7122595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4830,12 +4815,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4846,10 +4831,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126916279</v>
+        <v>126905646</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4857,42 +4842,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Baksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>656878</v>
+        <v>656789</v>
       </c>
       <c r="R42" t="n">
-        <v>7122337</v>
+        <v>7122441</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4927,11 +4904,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4944,12 +4916,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4960,10 +4932,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126915092</v>
+        <v>126918031</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4971,34 +4943,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>656867</v>
+        <v>656542</v>
       </c>
       <c r="R43" t="n">
-        <v>7122430</v>
+        <v>7122741</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5042,15 +5014,30 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5061,10 +5048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126915679</v>
+        <v>126917816</v>
       </c>
       <c r="B44" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,21 +5059,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5096,10 +5083,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656688</v>
+        <v>656764</v>
       </c>
       <c r="R44" t="n">
-        <v>7122595</v>
+        <v>7122303</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5146,12 +5133,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5162,10 +5149,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126905646</v>
+        <v>126920133</v>
       </c>
       <c r="B45" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,34 +5160,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Baksjön, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656789</v>
+        <v>656724</v>
       </c>
       <c r="R45" t="n">
-        <v>7122441</v>
+        <v>7122581</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5247,12 +5234,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5263,10 +5250,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126920133</v>
+        <v>126916279</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,34 +5261,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656724</v>
+        <v>656878</v>
       </c>
       <c r="R46" t="n">
-        <v>7122581</v>
+        <v>7122337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,6 +5331,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5348,12 +5348,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5990,48 +5990,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126916389</v>
+        <v>126915093</v>
       </c>
       <c r="B53" t="n">
-        <v>92813</v>
+        <v>57765</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>656885</v>
+        <v>656892</v>
       </c>
       <c r="R53" t="n">
-        <v>7122464</v>
+        <v>7122431</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6075,12 +6075,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6091,10 +6091,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126919830</v>
+        <v>126916389</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6102,21 +6102,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6126,13 +6126,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>656689</v>
+        <v>656885</v>
       </c>
       <c r="R54" t="n">
-        <v>7122578</v>
+        <v>7122464</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6162,11 +6162,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6181,12 +6176,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6197,7 +6192,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919826</v>
+        <v>126919830</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6232,10 +6227,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>656575</v>
+        <v>656689</v>
       </c>
       <c r="R55" t="n">
-        <v>7122664</v>
+        <v>7122578</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6268,6 +6263,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918096</v>
+        <v>126919826</v>
       </c>
       <c r="B56" t="n">
-        <v>80122</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6309,37 +6309,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>656703</v>
+        <v>656575</v>
       </c>
       <c r="R56" t="n">
-        <v>7122538</v>
+        <v>7122664</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6383,12 +6383,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6399,10 +6399,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126915094</v>
+        <v>126918096</v>
       </c>
       <c r="B57" t="n">
-        <v>78685</v>
+        <v>80122</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6410,37 +6410,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>656850</v>
+        <v>656703</v>
       </c>
       <c r="R57" t="n">
-        <v>7122254</v>
+        <v>7122538</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6484,12 +6484,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6500,45 +6500,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126918417</v>
+        <v>126915094</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>78685</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>656750</v>
+        <v>656850</v>
       </c>
       <c r="R58" t="n">
-        <v>7122529</v>
+        <v>7122254</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6582,30 +6582,15 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6616,7 +6601,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126918021</v>
+        <v>126916301</v>
       </c>
       <c r="B59" t="n">
         <v>78776</v>
@@ -6647,14 +6632,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>656754</v>
+        <v>656717</v>
       </c>
       <c r="R59" t="n">
-        <v>7122604</v>
+        <v>7122549</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6698,30 +6683,15 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6732,45 +6702,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126915093</v>
+        <v>126916850</v>
       </c>
       <c r="B60" t="n">
-        <v>57765</v>
+        <v>78776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>656892</v>
+        <v>656628</v>
       </c>
       <c r="R60" t="n">
-        <v>7122431</v>
+        <v>7122610</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6800,11 +6770,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6813,16 +6793,36 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Brandhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Brandhögstubbe</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6833,10 +6833,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126917776</v>
+        <v>126918417</v>
       </c>
       <c r="B61" t="n">
-        <v>79042</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6844,21 +6844,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>656736</v>
+        <v>656750</v>
       </c>
       <c r="R61" t="n">
-        <v>7122322</v>
+        <v>7122529</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6915,15 +6915,30 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6934,7 +6949,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126916301</v>
+        <v>126918021</v>
       </c>
       <c r="B62" t="n">
         <v>78776</v>
@@ -6965,14 +6980,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>656717</v>
+        <v>656754</v>
       </c>
       <c r="R62" t="n">
-        <v>7122549</v>
+        <v>7122604</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7016,15 +7031,30 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7035,32 +7065,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918694</v>
+        <v>126917776</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>79042</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7070,10 +7100,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>656559</v>
+        <v>656736</v>
       </c>
       <c r="R63" t="n">
-        <v>7122606</v>
+        <v>7122322</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7120,12 +7150,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7136,7 +7166,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126916850</v>
+        <v>126918694</v>
       </c>
       <c r="B64" t="n">
         <v>78776</v>
@@ -7171,10 +7201,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>656628</v>
+        <v>656559</v>
       </c>
       <c r="R64" t="n">
-        <v>7122610</v>
+        <v>7122606</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7204,21 +7234,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7227,36 +7247,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>Brandhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Brandhögstubbe</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7267,32 +7267,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126919837</v>
+        <v>126918403</v>
       </c>
       <c r="B65" t="n">
-        <v>80156</v>
+        <v>79636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>656726</v>
+        <v>656749</v>
       </c>
       <c r="R65" t="n">
-        <v>7122533</v>
+        <v>7122643</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7352,12 +7352,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918658</v>
+        <v>126919837</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>656664</v>
+        <v>656726</v>
       </c>
       <c r="R66" t="n">
-        <v>7122576</v>
+        <v>7122533</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7441,11 +7441,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7458,12 +7453,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7474,32 +7469,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126918403</v>
+        <v>126917775</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>79042</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7509,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>656749</v>
+        <v>656581</v>
       </c>
       <c r="R67" t="n">
-        <v>7122643</v>
+        <v>7122603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7559,12 +7554,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7575,32 +7570,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917775</v>
+        <v>126918658</v>
       </c>
       <c r="B68" t="n">
-        <v>79042</v>
+        <v>57661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7610,10 +7605,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>656581</v>
+        <v>656664</v>
       </c>
       <c r="R68" t="n">
-        <v>7122603</v>
+        <v>7122576</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7648,6 +7643,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918448</v>
+        <v>126915087</v>
       </c>
       <c r="B71" t="n">
-        <v>80056</v>
+        <v>80150</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7899,37 +7899,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Balsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>656939</v>
+        <v>656629</v>
       </c>
       <c r="R71" t="n">
-        <v>7122290</v>
+        <v>7122746</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7970,34 +7967,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8008,48 +7989,52 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126914184</v>
+        <v>126916732</v>
       </c>
       <c r="B72" t="n">
-        <v>80025</v>
+        <v>57658</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>656943</v>
+        <v>656599</v>
       </c>
       <c r="R72" t="n">
-        <v>7122285</v>
+        <v>7122660</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8076,19 +8061,14 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:48</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8103,12 +8083,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8119,45 +8099,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126915087</v>
+        <v>126916291</v>
       </c>
       <c r="B73" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Balsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>656629</v>
+        <v>656585</v>
       </c>
       <c r="R73" t="n">
-        <v>7122746</v>
+        <v>7122741</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8204,12 +8184,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Miriam Schenk, Lise Mortensen, Nicklas Gustavsson, Gunilla R Burke, Jennica Andersson, Elke Blöhbaum</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8220,10 +8200,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126916732</v>
+        <v>126916735</v>
       </c>
       <c r="B74" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8231,38 +8211,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>656599</v>
+        <v>656861</v>
       </c>
       <c r="R74" t="n">
-        <v>7122660</v>
+        <v>7122418</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8295,11 +8271,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Hackhål</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8330,7 +8301,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126916735</v>
+        <v>126915678</v>
       </c>
       <c r="B75" t="n">
         <v>78777</v>
@@ -8365,10 +8336,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>656861</v>
+        <v>656958</v>
       </c>
       <c r="R75" t="n">
-        <v>7122418</v>
+        <v>7122264</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8415,12 +8386,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8431,10 +8402,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126915678</v>
+        <v>126916855</v>
       </c>
       <c r="B76" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8442,21 +8413,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8466,10 +8437,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>656958</v>
+        <v>656803</v>
       </c>
       <c r="R76" t="n">
-        <v>7122264</v>
+        <v>7122276</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8499,11 +8470,21 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8512,16 +8493,36 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal tallåga</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8532,45 +8533,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126920135</v>
+        <v>126918448</v>
       </c>
       <c r="B77" t="n">
-        <v>98448</v>
+        <v>80056</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>656718</v>
+        <v>656939</v>
       </c>
       <c r="R77" t="n">
-        <v>7122587</v>
+        <v>7122290</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8611,18 +8615,34 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8633,32 +8653,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126916855</v>
+        <v>126914184</v>
       </c>
       <c r="B78" t="n">
-        <v>78685</v>
+        <v>80025</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8668,13 +8688,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>656803</v>
+        <v>656943</v>
       </c>
       <c r="R78" t="n">
-        <v>7122276</v>
+        <v>7122285</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8703,7 +8723,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8713,7 +8733,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8724,36 +8744,16 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>Gammal tallåga</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal tallåga</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8764,32 +8764,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126916291</v>
+        <v>126920135</v>
       </c>
       <c r="B79" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>656585</v>
+        <v>656718</v>
       </c>
       <c r="R79" t="n">
-        <v>7122741</v>
+        <v>7122587</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8849,12 +8849,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8865,32 +8865,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126916319</v>
+        <v>126915973</v>
       </c>
       <c r="B80" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>656795</v>
+        <v>656870</v>
       </c>
       <c r="R80" t="n">
-        <v>7122394</v>
+        <v>7122229</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8936,11 +8936,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Flertal ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8955,12 +8950,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8971,32 +8966,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126915973</v>
+        <v>126918698</v>
       </c>
       <c r="B81" t="n">
-        <v>78685</v>
+        <v>98448</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9006,13 +9001,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>656870</v>
+        <v>656614</v>
       </c>
       <c r="R81" t="n">
-        <v>7122229</v>
+        <v>7122574</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9056,12 +9051,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9072,32 +9067,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126916311</v>
+        <v>126918696</v>
       </c>
       <c r="B82" t="n">
-        <v>78685</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9107,10 +9102,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>656790</v>
+        <v>656642</v>
       </c>
       <c r="R82" t="n">
-        <v>7122393</v>
+        <v>7122586</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9157,12 +9152,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9173,10 +9168,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126915969</v>
+        <v>126919783</v>
       </c>
       <c r="B83" t="n">
-        <v>80121</v>
+        <v>79607</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9184,21 +9179,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9208,13 +9203,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>656832</v>
+        <v>656746</v>
       </c>
       <c r="R83" t="n">
-        <v>7122445</v>
+        <v>7122340</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9252,18 +9247,19 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9274,32 +9270,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126919794</v>
+        <v>126916290</v>
       </c>
       <c r="B84" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9309,10 +9305,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>656670</v>
+        <v>656517</v>
       </c>
       <c r="R84" t="n">
-        <v>7122632</v>
+        <v>7122763</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9359,12 +9355,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9375,10 +9371,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126918432</v>
+        <v>126915677</v>
       </c>
       <c r="B85" t="n">
-        <v>77996</v>
+        <v>78777</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9386,21 +9382,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9410,10 +9406,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>656876</v>
+        <v>656789</v>
       </c>
       <c r="R85" t="n">
-        <v>7122472</v>
+        <v>7122426</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9460,12 +9456,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9476,10 +9472,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126918691</v>
+        <v>126917800</v>
       </c>
       <c r="B86" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9487,21 +9483,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9511,10 +9507,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>656840</v>
+        <v>656842</v>
       </c>
       <c r="R86" t="n">
-        <v>7122313</v>
+        <v>7122270</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9561,12 +9557,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9577,48 +9573,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126918101</v>
+        <v>126916319</v>
       </c>
       <c r="B87" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>656660</v>
+        <v>656795</v>
       </c>
       <c r="R87" t="n">
-        <v>7122590</v>
+        <v>7122394</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9648,6 +9644,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Flertal ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9662,12 +9663,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9678,10 +9679,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126918457</v>
+        <v>126916311</v>
       </c>
       <c r="B88" t="n">
-        <v>75142</v>
+        <v>78685</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9689,21 +9690,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9713,10 +9714,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>656761</v>
+        <v>656790</v>
       </c>
       <c r="R88" t="n">
-        <v>7122534</v>
+        <v>7122393</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9760,30 +9761,15 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9794,10 +9780,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126916300</v>
+        <v>126915969</v>
       </c>
       <c r="B89" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9805,21 +9791,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9829,13 +9815,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>656721</v>
+        <v>656832</v>
       </c>
       <c r="R89" t="n">
-        <v>7122598</v>
+        <v>7122445</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9879,12 +9865,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9895,32 +9881,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126918698</v>
+        <v>126919794</v>
       </c>
       <c r="B90" t="n">
-        <v>98448</v>
+        <v>80150</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9930,10 +9916,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>656614</v>
+        <v>656670</v>
       </c>
       <c r="R90" t="n">
-        <v>7122574</v>
+        <v>7122632</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9980,12 +9966,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9996,32 +9982,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918696</v>
+        <v>126918432</v>
       </c>
       <c r="B91" t="n">
-        <v>98448</v>
+        <v>77996</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10031,10 +10017,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>656642</v>
+        <v>656876</v>
       </c>
       <c r="R91" t="n">
-        <v>7122586</v>
+        <v>7122472</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,12 +10067,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10097,10 +10083,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126919783</v>
+        <v>126918691</v>
       </c>
       <c r="B92" t="n">
-        <v>79607</v>
+        <v>80121</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10108,21 +10094,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10132,10 +10118,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>656746</v>
+        <v>656840</v>
       </c>
       <c r="R92" t="n">
-        <v>7122340</v>
+        <v>7122313</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10176,19 +10162,18 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eleonor Johansson, kristina stenmarck, Jennica Andersson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Carl Jansson, Beke Regelin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10199,10 +10184,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126916290</v>
+        <v>126918101</v>
       </c>
       <c r="B93" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10210,37 +10195,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>656517</v>
+        <v>656660</v>
       </c>
       <c r="R93" t="n">
-        <v>7122763</v>
+        <v>7122590</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10284,12 +10269,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10300,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126915677</v>
+        <v>126918457</v>
       </c>
       <c r="B94" t="n">
-        <v>78777</v>
+        <v>75142</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10311,21 +10296,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10335,10 +10320,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>656789</v>
+        <v>656761</v>
       </c>
       <c r="R94" t="n">
-        <v>7122426</v>
+        <v>7122534</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10382,15 +10367,30 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10401,10 +10401,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126917800</v>
+        <v>126916300</v>
       </c>
       <c r="B95" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10412,21 +10412,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>656842</v>
+        <v>656721</v>
       </c>
       <c r="R95" t="n">
-        <v>7122270</v>
+        <v>7122598</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10486,12 +10486,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -18282,45 +18282,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126918004</v>
+        <v>126919835</v>
       </c>
       <c r="B170" t="n">
-        <v>91491</v>
+        <v>78685</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>656857</v>
+        <v>656811</v>
       </c>
       <c r="R170" t="n">
-        <v>7122220</v>
+        <v>7122322</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18355,6 +18355,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -18363,31 +18368,16 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -18398,10 +18388,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126918012</v>
+        <v>126918392</v>
       </c>
       <c r="B171" t="n">
-        <v>79636</v>
+        <v>75142</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18409,34 +18399,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>656942</v>
+        <v>656628</v>
       </c>
       <c r="R171" t="n">
-        <v>7122347</v>
+        <v>7122758</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18480,30 +18470,15 @@
       <c r="AG171" t="b">
         <v>0</v>
       </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18514,10 +18489,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126919835</v>
+        <v>126918012</v>
       </c>
       <c r="B172" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18525,34 +18500,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>656811</v>
+        <v>656942</v>
       </c>
       <c r="R172" t="n">
-        <v>7122322</v>
+        <v>7122347</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18587,11 +18562,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
@@ -18600,16 +18570,31 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -18620,32 +18605,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126917765</v>
+        <v>126918697</v>
       </c>
       <c r="B173" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18655,10 +18640,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>656447</v>
+        <v>656625</v>
       </c>
       <c r="R173" t="n">
-        <v>7122672</v>
+        <v>7122578</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18705,12 +18690,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18721,32 +18706,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126917812</v>
+        <v>126916292</v>
       </c>
       <c r="B174" t="n">
-        <v>80157</v>
+        <v>78777</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18756,10 +18741,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>656710</v>
+        <v>656647</v>
       </c>
       <c r="R174" t="n">
-        <v>7122344</v>
+        <v>7122645</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18806,12 +18791,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18822,32 +18807,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126916731</v>
+        <v>126916391</v>
       </c>
       <c r="B175" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18857,13 +18842,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>656616</v>
+        <v>656635</v>
       </c>
       <c r="R175" t="n">
-        <v>7122643</v>
+        <v>7122743</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18893,11 +18878,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18912,12 +18892,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18928,45 +18908,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126918392</v>
+        <v>126918004</v>
       </c>
       <c r="B176" t="n">
-        <v>75142</v>
+        <v>91491</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>656628</v>
+        <v>656857</v>
       </c>
       <c r="R176" t="n">
-        <v>7122758</v>
+        <v>7122220</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19010,15 +18990,30 @@
       <c r="AG176" t="b">
         <v>0</v>
       </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -19029,32 +19024,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126918697</v>
+        <v>126917765</v>
       </c>
       <c r="B177" t="n">
-        <v>98448</v>
+        <v>79636</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19064,10 +19059,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>656625</v>
+        <v>656447</v>
       </c>
       <c r="R177" t="n">
-        <v>7122578</v>
+        <v>7122672</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19114,12 +19109,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -19130,32 +19125,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126916292</v>
+        <v>126917812</v>
       </c>
       <c r="B178" t="n">
-        <v>78777</v>
+        <v>80157</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19165,10 +19160,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>656647</v>
+        <v>656710</v>
       </c>
       <c r="R178" t="n">
-        <v>7122645</v>
+        <v>7122344</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19215,12 +19210,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -19231,32 +19226,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126916391</v>
+        <v>126916731</v>
       </c>
       <c r="B179" t="n">
-        <v>78777</v>
+        <v>80150</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19266,13 +19261,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>656635</v>
+        <v>656616</v>
       </c>
       <c r="R179" t="n">
-        <v>7122743</v>
+        <v>7122643</v>
       </c>
       <c r="S179" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19302,6 +19297,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19316,12 +19316,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>kristina stenmarck, Jennica Andersson</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -19332,10 +19332,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126918008</v>
+        <v>126918015</v>
       </c>
       <c r="B180" t="n">
-        <v>80993</v>
+        <v>92813</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19343,21 +19343,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19367,10 +19367,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>656933</v>
+        <v>656884</v>
       </c>
       <c r="R180" t="n">
-        <v>7122272</v>
+        <v>7122406</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19564,10 +19564,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126917817</v>
+        <v>126918008</v>
       </c>
       <c r="B182" t="n">
-        <v>78776</v>
+        <v>80993</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19575,34 +19575,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>656842</v>
+        <v>656933</v>
       </c>
       <c r="R182" t="n">
-        <v>7122270</v>
+        <v>7122272</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19646,15 +19646,30 @@
       <c r="AG182" t="b">
         <v>0</v>
       </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19665,32 +19680,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126918441</v>
+        <v>126919833</v>
       </c>
       <c r="B183" t="n">
-        <v>8450</v>
+        <v>78685</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19700,10 +19715,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>656596</v>
+        <v>656555</v>
       </c>
       <c r="R183" t="n">
-        <v>7122771</v>
+        <v>7122664</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19747,30 +19762,15 @@
       <c r="AG183" t="b">
         <v>0</v>
       </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19781,32 +19781,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126916736</v>
+        <v>126919800</v>
       </c>
       <c r="B184" t="n">
-        <v>78777</v>
+        <v>80150</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19816,10 +19816,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>656871</v>
+        <v>656820</v>
       </c>
       <c r="R184" t="n">
-        <v>7122392</v>
+        <v>7122319</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19854,11 +19854,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>På kolad kärnved, högstubbe</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -19871,12 +19866,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -19887,32 +19882,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126917796</v>
+        <v>126917823</v>
       </c>
       <c r="B185" t="n">
-        <v>78777</v>
+        <v>80156</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19922,10 +19917,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>656580</v>
+        <v>656656</v>
       </c>
       <c r="R185" t="n">
-        <v>7122596</v>
+        <v>7122558</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19988,10 +19983,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>126914188</v>
+        <v>126917817</v>
       </c>
       <c r="B186" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19999,37 +19994,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>656907</v>
+        <v>656842</v>
       </c>
       <c r="R186" t="n">
-        <v>7122416</v>
+        <v>7122270</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20056,19 +20051,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20083,12 +20068,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -20099,10 +20084,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126918015</v>
+        <v>126915674</v>
       </c>
       <c r="B187" t="n">
-        <v>92813</v>
+        <v>79636</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20110,34 +20095,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>656884</v>
+        <v>656846</v>
       </c>
       <c r="R187" t="n">
-        <v>7122406</v>
+        <v>7122403</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20181,30 +20166,15 @@
       <c r="AG187" t="b">
         <v>0</v>
       </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -20215,32 +20185,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126919833</v>
+        <v>126918441</v>
       </c>
       <c r="B188" t="n">
-        <v>78685</v>
+        <v>8450</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20250,10 +20220,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>656555</v>
+        <v>656596</v>
       </c>
       <c r="R188" t="n">
-        <v>7122664</v>
+        <v>7122771</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20297,15 +20267,30 @@
       <c r="AG188" t="b">
         <v>0</v>
       </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -20316,32 +20301,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126919800</v>
+        <v>126917796</v>
       </c>
       <c r="B189" t="n">
-        <v>80150</v>
+        <v>78777</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20351,10 +20336,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>656820</v>
+        <v>656580</v>
       </c>
       <c r="R189" t="n">
-        <v>7122319</v>
+        <v>7122596</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20401,12 +20386,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -20417,32 +20402,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126917823</v>
+        <v>126916736</v>
       </c>
       <c r="B190" t="n">
-        <v>80156</v>
+        <v>78777</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20452,10 +20437,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>656656</v>
+        <v>656871</v>
       </c>
       <c r="R190" t="n">
-        <v>7122558</v>
+        <v>7122392</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20490,6 +20475,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>På kolad kärnved, högstubbe</t>
+        </is>
+      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
@@ -20502,12 +20492,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke, kristina stenmarck, Carl Jansson, Elin Kannerby, Torbjörn Söderquist, Beke Regelin, Jennica Andersson, Miriam Schenk, Nicklas Gustavsson, Mattias Dalkvist, Lise Mortensen, Lisa Requin, Anders Heggestad, Peder Winding</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20518,10 +20508,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126915674</v>
+        <v>126914188</v>
       </c>
       <c r="B191" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20529,37 +20519,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>656846</v>
+        <v>656907</v>
       </c>
       <c r="R191" t="n">
-        <v>7122403</v>
+        <v>7122416</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20586,9 +20576,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20603,12 +20603,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20720,48 +20720,48 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126914189</v>
+        <v>126916318</v>
       </c>
       <c r="B193" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Skog, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>656908</v>
+        <v>656775</v>
       </c>
       <c r="R193" t="n">
-        <v>7122416</v>
+        <v>7122386</v>
       </c>
       <c r="S193" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20788,19 +20788,9 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20815,12 +20805,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -20831,10 +20821,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126918030</v>
+        <v>126918653</v>
       </c>
       <c r="B194" t="n">
-        <v>78424</v>
+        <v>80122</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20842,34 +20832,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>656564</v>
+        <v>656729</v>
       </c>
       <c r="R194" t="n">
-        <v>7122730</v>
+        <v>7122537</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20913,30 +20903,15 @@
       <c r="AG194" t="b">
         <v>0</v>
       </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20947,10 +20922,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126915953</v>
+        <v>126918103</v>
       </c>
       <c r="B195" t="n">
-        <v>57661</v>
+        <v>80993</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20958,45 +20933,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>656846</v>
+        <v>656889</v>
       </c>
       <c r="R195" t="n">
-        <v>7122377</v>
+        <v>7122426</v>
       </c>
       <c r="S195" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21034,18 +21001,19 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21056,10 +21024,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126918413</v>
+        <v>126919817</v>
       </c>
       <c r="B196" t="n">
-        <v>57821</v>
+        <v>80121</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21067,21 +21035,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21091,10 +21059,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>656867</v>
+        <v>656807</v>
       </c>
       <c r="R196" t="n">
-        <v>7122465</v>
+        <v>7122335</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21141,12 +21109,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
+          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -21157,48 +21125,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126916318</v>
+        <v>126918099</v>
       </c>
       <c r="B197" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Backsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>656775</v>
+        <v>656966</v>
       </c>
       <c r="R197" t="n">
-        <v>7122386</v>
+        <v>7122301</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21242,12 +21210,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21258,10 +21226,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126918653</v>
+        <v>126914189</v>
       </c>
       <c r="B198" t="n">
-        <v>80122</v>
+        <v>78776</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21269,37 +21237,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Skog, Ås lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>656729</v>
+        <v>656908</v>
       </c>
       <c r="R198" t="n">
-        <v>7122537</v>
+        <v>7122416</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21326,9 +21294,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21343,12 +21321,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Gunilla R Burke, Nicklas Gustavsson, Carl Jansson, Miriam Schenk, Beke Regelin, Anders Heggestad, Lise Mortensen, Peder Winding, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21359,10 +21337,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126918103</v>
+        <v>126918030</v>
       </c>
       <c r="B199" t="n">
-        <v>80993</v>
+        <v>78424</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21370,37 +21348,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>656889</v>
+        <v>656564</v>
       </c>
       <c r="R199" t="n">
-        <v>7122426</v>
+        <v>7122730</v>
       </c>
       <c r="S199" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21438,19 +21416,33 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21461,10 +21453,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126919817</v>
+        <v>126915953</v>
       </c>
       <c r="B200" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21472,37 +21464,45 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>656807</v>
+        <v>656846</v>
       </c>
       <c r="R200" t="n">
-        <v>7122335</v>
+        <v>7122377</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21546,12 +21546,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Elin Kannerby, Hedda Bring, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Eleonor Johansson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21562,10 +21562,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126918099</v>
+        <v>126918413</v>
       </c>
       <c r="B201" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21573,37 +21573,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Backsjökullen, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>656966</v>
+        <v>656867</v>
       </c>
       <c r="R201" t="n">
-        <v>7122301</v>
+        <v>7122465</v>
       </c>
       <c r="S201" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21647,12 +21647,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Mattias Dalkvist, Gunilla R Burke, Lisa Requin</t>
+          <t>Peder Winding, kristina stenmarck, Gunilla R Burke, Carl Jansson, Lisa Requin, Lise Mortensen, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY204"/>
+  <dimension ref="A1:AY205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21964,6 +21964,136 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>132794181</v>
+      </c>
+      <c r="B205" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Baksjökullen, Åsele, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>656843</v>
+      </c>
+      <c r="R205" t="n">
+        <v>7122337</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>250725-1039</t>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28996-2024 artfynd.xlsx
+++ b/artfynd/A 28996-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY249"/>
+  <dimension ref="A1:AZ249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915094</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916307</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916309</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916311</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916855</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918014</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918028</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918409</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918452</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919833</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919834</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919835</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920138</t>
         </is>
       </c>
     </row>
@@ -2271,6 +2346,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918008</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2489,6 +2574,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918103</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2605,6 +2695,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918004</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2721,6 +2816,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918024</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2923,6 +3028,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916389</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3024,6 +3134,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917777</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3140,6 +3255,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918015</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3254,6 +3374,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918020</t>
         </is>
       </c>
     </row>
@@ -3386,6 +3511,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132794181</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3487,6 +3617,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918096</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3588,6 +3723,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918653</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3689,6 +3829,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915680</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3790,6 +3935,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916317</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3891,6 +4041,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916318</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3997,6 +4152,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916319</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4098,6 +4258,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916320</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4199,6 +4364,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4300,6 +4470,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918453</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4401,6 +4576,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918454</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4502,6 +4682,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916383</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4618,6 +4803,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918016</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4715,6 +4905,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62983761</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4826,6 +5021,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914185</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4932,6 +5132,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916740</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5048,6 +5253,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918031</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5149,6 +5359,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918715</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5250,6 +5465,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919823</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5351,6 +5571,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919826</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5452,6 +5677,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919828</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5558,6 +5788,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919830</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5659,6 +5894,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919831</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5760,6 +6000,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126950499</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5861,6 +6106,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917774</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5962,6 +6212,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917775</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6063,6 +6318,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917776</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6164,6 +6424,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918420</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6275,6 +6540,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914190</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6386,6 +6656,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914195</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6487,6 +6762,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916399</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6584,6 +6864,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916750</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6685,6 +6970,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917827</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6786,6 +7076,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917831</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6887,6 +7182,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917832</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7003,6 +7303,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918002</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7119,6 +7424,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918009</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7235,6 +7545,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918023</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7351,6 +7666,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918030</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7452,6 +7772,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918429</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7553,6 +7878,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918431</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7654,6 +7984,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918390</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7755,6 +8090,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918392</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7871,6 +8211,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918457</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7982,6 +8327,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914182</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8093,6 +8443,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914183</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8204,6 +8559,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914186</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8315,6 +8675,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914187</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8426,6 +8791,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914189</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8537,6 +8907,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914192</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8648,6 +9023,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914196</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8749,6 +9129,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915971</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8850,6 +9235,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916300</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8951,6 +9341,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916301</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9052,6 +9447,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916302</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9153,6 +9553,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916395</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9254,6 +9659,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916738</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9355,6 +9765,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916739</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9486,6 +9901,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916850</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9587,6 +10007,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917815</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9688,6 +10113,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917816</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9789,6 +10219,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917817</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9905,6 +10340,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918021</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10006,6 +10446,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918694</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10107,6 +10552,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920132</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10208,6 +10658,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920133</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10309,6 +10764,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920134</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10410,6 +10870,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126950483</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10511,6 +10976,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915674</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10612,6 +11082,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916273</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10713,6 +11188,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916384</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10814,6 +11294,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916385</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10915,6 +11400,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916728</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11016,6 +11506,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917765</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11117,6 +11612,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917766</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11218,6 +11718,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917767</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11319,6 +11824,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917768</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11435,6 +11945,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918005</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11551,6 +12066,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918006</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11667,6 +12187,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918010</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11783,6 +12308,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918012</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11899,6 +12429,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918017</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12000,6 +12535,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918093</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12101,6 +12641,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918398</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12202,6 +12747,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918400</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12303,6 +12853,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918402</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12404,6 +12959,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918403</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12505,6 +13065,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918426</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12606,6 +13171,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918433</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12707,6 +13277,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918437</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12808,6 +13383,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919780</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12909,6 +13489,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126950481</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13020,6 +13605,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914184</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13119,6 +13709,11 @@
       <c r="AY119" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916396</t>
         </is>
       </c>
     </row>
@@ -13241,6 +13836,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918448</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13342,6 +13942,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126905646</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13443,6 +14048,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915092</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13544,6 +14154,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915679</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13645,6 +14260,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915967</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13746,6 +14366,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915968</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13847,6 +14472,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915969</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13948,6 +14578,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916297</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14049,6 +14684,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916393</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14150,6 +14790,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916737</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14251,6 +14896,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917806</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14352,6 +15002,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917809</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14453,6 +15108,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917810</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14569,6 +15229,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918019</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14670,6 +15335,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918101</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14771,6 +15441,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918682</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14872,6 +15547,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918685</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14973,6 +15653,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918688</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15074,6 +15759,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918690</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15175,6 +15865,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918691</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15281,6 +15976,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919815</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15382,6 +16082,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919817</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15483,6 +16188,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919819</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15584,6 +16294,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915087</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15685,6 +16400,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915958</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15791,6 +16511,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916731</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15907,6 +16632,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918417</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16008,6 +16738,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918652</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16109,6 +16844,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919794</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16210,6 +16950,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919796</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16316,6 +17061,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919798</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16417,6 +17167,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919800</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16519,6 +17274,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916398</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16620,6 +17380,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917823</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16736,6 +17501,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918418</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16852,6 +17622,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918456</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16953,6 +17728,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919836</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17054,6 +17834,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919837</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17155,6 +17940,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919838</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17256,6 +18046,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917812</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17357,6 +18152,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918102</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17458,6 +18258,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917826</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17559,6 +18364,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918427</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17658,6 +18468,11 @@
       <c r="AY163" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918432</t>
         </is>
       </c>
     </row>
@@ -17770,6 +18585,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916732</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17879,6 +18699,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915952</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17988,6 +18813,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915953</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18102,6 +18932,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916279</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18208,6 +19043,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918641</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18314,6 +19154,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918642</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18420,6 +19265,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918658</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18526,6 +19376,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918659</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18632,6 +19487,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920121</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18745,6 +19605,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915954</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18856,6 +19721,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126906851</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18957,6 +19827,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918693</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19058,6 +19933,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918413</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19159,6 +20039,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915093</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19270,6 +20155,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914197</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19369,6 +20259,11 @@
       <c r="AY179" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917801</t>
         </is>
       </c>
     </row>
@@ -19497,6 +20392,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918026</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19613,6 +20513,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918441</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19729,6 +20634,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918442</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19830,6 +20740,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918445</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19931,6 +20846,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917818</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20045,6 +20965,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918695</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20146,6 +21071,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918696</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20247,6 +21177,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918697</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20348,6 +21283,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918698</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20449,6 +21389,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918700</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20550,6 +21495,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918701</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20651,6 +21601,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920135</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20752,6 +21707,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918391</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20863,6 +21823,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914181</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20974,6 +21939,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914188</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21075,6 +22045,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915089</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21176,6 +22151,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915091</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21277,6 +22257,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915676</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21378,6 +22363,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915677</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21479,6 +22469,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915678</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21581,6 +22576,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915960</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21683,6 +22683,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915961</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21784,6 +22789,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916290</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21885,6 +22895,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916291</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21986,6 +23001,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916292</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22087,6 +23107,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916293</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22188,6 +23213,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916294</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22289,6 +23319,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916295</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22390,6 +23425,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916390</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22491,6 +23531,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916391</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22592,6 +23637,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916392</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22693,6 +23743,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916734</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22794,6 +23849,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916735</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22900,6 +23960,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126916736</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23001,6 +24066,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917793</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23102,6 +24172,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917794</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23203,6 +24278,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917795</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23304,6 +24384,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917796</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23405,6 +24490,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917797</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23506,6 +24596,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917798</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23607,6 +24702,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917799</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23708,6 +24808,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917800</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23824,6 +24929,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918003</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23940,6 +25050,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918007</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24056,6 +25171,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918011</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24172,6 +25292,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918022</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24273,6 +25398,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918098</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24374,6 +25504,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918099</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24475,6 +25610,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918425</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24576,6 +25716,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918430</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24677,6 +25822,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918436</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24778,6 +25928,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918440</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24879,6 +26034,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918662</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24980,6 +26140,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918676</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25081,6 +26246,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919810</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25187,6 +26357,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919813</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25288,6 +26463,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920129</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25389,6 +26569,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920130</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25495,6 +26680,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126920131</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25596,6 +26786,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126905615</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25707,6 +26902,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914193</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25823,6 +27023,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918013</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25939,6 +27144,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918029</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26040,6 +27250,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918408</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26141,6 +27356,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918411</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26243,6 +27463,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919783</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26345,6 +27570,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919784</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26447,6 +27677,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919787</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26548,6 +27783,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918414</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26649,8 +27889,263 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918415</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>